--- a/Versão5/PRO/Ontologia_Crono.xlsx
+++ b/Versão5/PRO/Ontologia_Crono.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\CRON\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\PRO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{948A5FF1-3A22-42A0-9503-3D77725AD3C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A965300-C02F-4101-9D8E-705746691BCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="4" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="26" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3007" uniqueCount="517">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3101" uniqueCount="521">
   <si>
     <t>Key</t>
   </si>
@@ -2326,12 +2326,6 @@
     <t>Evento agendado tipo exame ou testes.</t>
   </si>
   <si>
-    <t>CategoriaRvt</t>
-  </si>
-  <si>
-    <t>ClasseIfc</t>
-  </si>
-  <si>
     <t>ABNT</t>
   </si>
   <si>
@@ -2794,25 +2788,43 @@
     <t>Una fecha de calendario para un evento que sucedió o sucederá.</t>
   </si>
   <si>
+    <t>Projeto</t>
+  </si>
+  <si>
+    <t>Cronologia</t>
+  </si>
+  <si>
+    <t>Evento.Projetual</t>
+  </si>
+  <si>
+    <t>Cronologias</t>
+  </si>
+  <si>
+    <t>Cronológico</t>
+  </si>
+  <si>
+    <t>Evento relacionado ao projeto acontecido.</t>
+  </si>
+  <si>
+    <t>A calendar date for an event that happened or will happen.</t>
+  </si>
+  <si>
+    <t>Event related to the project that happened.</t>
+  </si>
+  <si>
+    <t>Atributo IFC</t>
+  </si>
+  <si>
+    <t>Classe IFC</t>
+  </si>
+  <si>
+    <t>Categoria Rvt</t>
+  </si>
+  <si>
+    <t>Parâmetro Rvt</t>
+  </si>
+  <si>
     <t>[ - ]</t>
-  </si>
-  <si>
-    <t>Projeto</t>
-  </si>
-  <si>
-    <t>Cronologia</t>
-  </si>
-  <si>
-    <t>Evento.Projetual</t>
-  </si>
-  <si>
-    <t>Cronologias</t>
-  </si>
-  <si>
-    <t>Cronológico</t>
-  </si>
-  <si>
-    <t>Evento relacionado ao projeto acontecido.</t>
   </si>
 </sst>
 </file>
@@ -3387,15 +3399,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="16">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
+  <dxfs count="17">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3520,6 +3524,22 @@
         <i/>
         <strike val="0"/>
         <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
       </font>
     </dxf>
     <dxf>
@@ -3859,15 +3879,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{612B613C-8B96-43A0-BB50-A45AC26373E3}">
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultColWidth="3.28515625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="3.3046875" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" style="12" customWidth="1"/>
-    <col min="2" max="2" width="39.85546875" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" style="56" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="3.28515625" style="12"/>
+    <col min="1" max="1" width="9.69140625" style="12" customWidth="1"/>
+    <col min="2" max="2" width="39.84375" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.3828125" style="56" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="3.3046875" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="49.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="13" t="s">
         <v>137</v>
       </c>
@@ -3875,10 +3895,10 @@
         <v>69</v>
       </c>
       <c r="C1" s="54" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="14" t="s">
         <v>146</v>
       </c>
@@ -3886,10 +3906,10 @@
         <v>165</v>
       </c>
       <c r="C2" s="55" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="14" t="s">
         <v>147</v>
       </c>
@@ -3897,10 +3917,10 @@
         <v>244</v>
       </c>
       <c r="C3" s="55" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="14" t="s">
         <v>138</v>
       </c>
@@ -3908,10 +3928,10 @@
         <v>148</v>
       </c>
       <c r="C4" s="55" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="14" t="s">
         <v>139</v>
       </c>
@@ -3920,10 +3940,10 @@
         <v>BIMProp</v>
       </c>
       <c r="C5" s="55" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="14" t="s">
         <v>140</v>
       </c>
@@ -3932,10 +3952,10 @@
         <v>BIMData</v>
       </c>
       <c r="C6" s="55" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="14" t="s">
         <v>141</v>
       </c>
@@ -3943,21 +3963,21 @@
         <v>149</v>
       </c>
       <c r="C7" s="55" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" customFormat="1" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" customFormat="1" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="16" t="s">
         <v>142</v>
       </c>
       <c r="B8" s="16" t="s">
+        <v>357</v>
+      </c>
+      <c r="C8" s="55" t="s">
         <v>359</v>
       </c>
-      <c r="C8" s="55" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="14" t="s">
         <v>150</v>
       </c>
@@ -3965,10 +3985,10 @@
         <v>151</v>
       </c>
       <c r="C9" s="55" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="14" t="s">
         <v>152</v>
       </c>
@@ -3976,10 +3996,10 @@
         <v>38</v>
       </c>
       <c r="C10" s="55" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="14" t="s">
         <v>143</v>
       </c>
@@ -3987,10 +4007,10 @@
         <v>38</v>
       </c>
       <c r="C11" s="55" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="14" t="s">
         <v>144</v>
       </c>
@@ -3998,10 +4018,10 @@
         <v>38</v>
       </c>
       <c r="C12" s="55" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="14" t="s">
         <v>153</v>
       </c>
@@ -4009,10 +4029,10 @@
         <v>38</v>
       </c>
       <c r="C13" s="55" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="14" t="s">
         <v>154</v>
       </c>
@@ -4020,10 +4040,10 @@
         <v>38</v>
       </c>
       <c r="C14" s="55" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="14" t="s">
         <v>155</v>
       </c>
@@ -4031,10 +4051,10 @@
         <v>38</v>
       </c>
       <c r="C15" s="55" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="14" t="s">
         <v>156</v>
       </c>
@@ -4042,10 +4062,10 @@
         <v>38</v>
       </c>
       <c r="C16" s="55" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="14" t="s">
         <v>145</v>
       </c>
@@ -4053,57 +4073,57 @@
         <v>162</v>
       </c>
       <c r="C17" s="55" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="14" t="s">
         <v>157</v>
       </c>
       <c r="B18" s="17">
         <f ca="1">NOW()</f>
-        <v>46244.605173032411</v>
+        <v>46253.796016435183</v>
       </c>
       <c r="C18" s="55" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" s="58" customFormat="1" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" s="58" customFormat="1" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="16" t="s">
+        <v>362</v>
+      </c>
+      <c r="B19" s="57" t="s">
+        <v>363</v>
+      </c>
+      <c r="C19" s="55" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" s="58" customFormat="1" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="16" t="s">
         <v>364</v>
-      </c>
-      <c r="B19" s="57" t="s">
-        <v>365</v>
-      </c>
-      <c r="C19" s="55" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" s="58" customFormat="1" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="16" t="s">
-        <v>366</v>
       </c>
       <c r="B20" s="57" t="str">
         <f>_xlfn.TRANSLATE(B19,"pt","es")</f>
         <v>Traducciones integradas al español e inglés - Las traducciones deben revisarse constantemente</v>
       </c>
       <c r="C20" s="55" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" s="58" customFormat="1" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" s="58" customFormat="1" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="16" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B21" s="57" t="str">
         <f>_xlfn.TRANSLATE(B19,"pt","en")</f>
         <v>Built-in Spanish and English Translations - Translations must be constantly reviewed</v>
       </c>
       <c r="C21" s="55" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="14" t="s">
         <v>158</v>
       </c>
@@ -4111,10 +4131,10 @@
         <v>38</v>
       </c>
       <c r="C22" s="55" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="14" t="s">
         <v>159</v>
       </c>
@@ -4122,10 +4142,10 @@
         <v>38</v>
       </c>
       <c r="C23" s="55" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="16" t="s">
         <v>160</v>
       </c>
@@ -4133,10 +4153,10 @@
         <v>163</v>
       </c>
       <c r="C24" s="55" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="16" t="s">
         <v>161</v>
       </c>
@@ -4144,19 +4164,19 @@
         <v>164</v>
       </c>
       <c r="C25" s="55" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" customFormat="1" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" customFormat="1" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="16" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B26" s="18" t="str">
         <f>_xlfn.TRANSLATE(B24,"pt","en")</f>
         <v>Formalize Concepts of Time Elements</v>
       </c>
       <c r="C26" s="55" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
   </sheetData>
@@ -4166,35 +4186,37 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A7B04F8-6372-42A9-A10C-B0C4EF342E07}">
-  <dimension ref="A1:AA46"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.95" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AC46"/>
+  <sheetFormatPr defaultColWidth="6.61328125" defaultRowHeight="7" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.42578125" style="70" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" customWidth="1"/>
-    <col min="7" max="11" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="64.5703125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="50.42578125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="5.140625" style="59" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="6.28515625" style="59" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="6.7109375" style="59" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="7.85546875" style="59" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="8.5703125" style="59" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.28515625" style="59" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="6.7109375" style="59" customWidth="1"/>
-    <col min="25" max="25" width="4.85546875" style="59" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="4.28515625" style="59" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="67.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.4609375" style="70" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.23046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.07421875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.3046875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.53515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="6.4609375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.07421875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.3046875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.53515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="40.69140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="37.61328125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="32.921875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.69140625" style="59" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.07421875" style="59" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5" style="59" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="7" style="59" customWidth="1"/>
+    <col min="23" max="23" width="6.84375" style="59" customWidth="1"/>
+    <col min="24" max="24" width="7.07421875" style="59" customWidth="1"/>
+    <col min="25" max="25" width="6.53515625" style="59" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6.3828125" style="59" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="5.3828125" style="59" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="6" style="59" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="3" style="59" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" ht="32.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="68" t="s">
         <v>166</v>
       </c>
@@ -4246,52 +4268,58 @@
       <c r="Q1" s="23" t="s">
         <v>176</v>
       </c>
-      <c r="R1" s="23" t="s">
+      <c r="R1" s="52" t="s">
+        <v>355</v>
+      </c>
+      <c r="S1" s="23" t="s">
         <v>177</v>
       </c>
-      <c r="S1" s="23" t="s">
+      <c r="T1" s="23" t="s">
         <v>167</v>
       </c>
-      <c r="T1" s="23" t="s">
+      <c r="U1" s="23" t="s">
         <v>178</v>
       </c>
-      <c r="U1" s="24" t="s">
+      <c r="V1" s="24" t="s">
         <v>169</v>
       </c>
-      <c r="V1" s="23" t="s">
+      <c r="W1" s="23" t="s">
         <v>168</v>
       </c>
-      <c r="W1" s="63" t="s">
+      <c r="X1" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="X1" s="23" t="s">
+      <c r="Y1" s="23" t="s">
+        <v>518</v>
+      </c>
+      <c r="Z1" s="23" t="s">
+        <v>519</v>
+      </c>
+      <c r="AA1" s="23" t="s">
+        <v>517</v>
+      </c>
+      <c r="AB1" s="23" t="s">
+        <v>516</v>
+      </c>
+      <c r="AC1" s="23" t="s">
         <v>354</v>
       </c>
-      <c r="Y1" s="23" t="s">
-        <v>355</v>
-      </c>
-      <c r="Z1" s="23" t="s">
-        <v>356</v>
-      </c>
-      <c r="AA1" s="52" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="69">
         <v>2</v>
       </c>
       <c r="B2" s="65" t="s">
+        <v>494</v>
+      </c>
+      <c r="C2" s="26" t="s">
+        <v>495</v>
+      </c>
+      <c r="D2" s="26" t="s">
         <v>496</v>
       </c>
-      <c r="C2" s="26" t="s">
-        <v>497</v>
-      </c>
-      <c r="D2" s="26" t="s">
-        <v>498</v>
-      </c>
       <c r="E2" s="27" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="F2" s="25" t="s">
         <v>49</v>
@@ -4328,61 +4356,67 @@
         <v>Era</v>
       </c>
       <c r="P2" s="61" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="Q2" s="61" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="R2" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="S2" s="53" t="str">
-        <f t="shared" ref="S2:U28" si="2">SUBSTITUTE(C2, "_", " ")</f>
+        <v>443</v>
+      </c>
+      <c r="S2" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="T2" s="53" t="str">
+        <f t="shared" ref="T2:V28" si="2">SUBSTITUTE(C2, "_", " ")</f>
         <v>Temporais</v>
       </c>
-      <c r="T2" s="53" t="str">
+      <c r="U2" s="53" t="str">
         <f t="shared" si="2"/>
         <v>Eventos</v>
       </c>
-      <c r="U2" s="60" t="str">
+      <c r="V2" s="60" t="str">
         <f t="shared" si="2"/>
         <v>Macroeventos</v>
       </c>
-      <c r="V2" s="53" t="s">
+      <c r="W2" s="53" t="s">
         <v>179</v>
       </c>
-      <c r="W2" s="64" t="str">
-        <f t="shared" ref="W2:W45" si="3">CONCATENATE("Key-CRONO-",A2)</f>
+      <c r="X2" s="64" t="str">
+        <f t="shared" ref="X2:X45" si="3">CONCATENATE("Key-CRONO-",A2)</f>
         <v>Key-CRONO-2</v>
       </c>
-      <c r="X2" s="53" t="s">
-        <v>510</v>
-      </c>
       <c r="Y2" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="Z2" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="AA2" s="53" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>520</v>
+      </c>
+      <c r="AB2" s="53" t="s">
+        <v>520</v>
+      </c>
+      <c r="AC2" s="53" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="69">
         <v>3</v>
       </c>
       <c r="B3" s="65" t="s">
+        <v>494</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>495</v>
+      </c>
+      <c r="D3" s="26" t="s">
         <v>496</v>
       </c>
-      <c r="C3" s="26" t="s">
-        <v>497</v>
-      </c>
-      <c r="D3" s="26" t="s">
-        <v>498</v>
-      </c>
       <c r="E3" s="27" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="F3" s="25" t="s">
         <v>50</v>
@@ -4419,61 +4453,67 @@
         <v>Época</v>
       </c>
       <c r="P3" s="61" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="Q3" s="61" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="R3" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="S3" s="53" t="str">
+        <v>444</v>
+      </c>
+      <c r="S3" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="T3" s="53" t="str">
         <f t="shared" si="2"/>
         <v>Temporais</v>
       </c>
-      <c r="T3" s="53" t="str">
+      <c r="U3" s="53" t="str">
         <f t="shared" si="2"/>
         <v>Eventos</v>
       </c>
-      <c r="U3" s="60" t="str">
+      <c r="V3" s="60" t="str">
         <f t="shared" si="2"/>
         <v>Macroeventos</v>
       </c>
-      <c r="V3" s="53" t="s">
+      <c r="W3" s="53" t="s">
         <v>179</v>
       </c>
-      <c r="W3" s="64" t="str">
+      <c r="X3" s="64" t="str">
         <f t="shared" si="3"/>
         <v>Key-CRONO-3</v>
       </c>
-      <c r="X3" s="53" t="s">
-        <v>510</v>
-      </c>
       <c r="Y3" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="Z3" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="AA3" s="53" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>520</v>
+      </c>
+      <c r="AB3" s="53" t="s">
+        <v>520</v>
+      </c>
+      <c r="AC3" s="53" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="4" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="69">
         <v>4</v>
       </c>
       <c r="B4" s="65" t="s">
+        <v>494</v>
+      </c>
+      <c r="C4" s="26" t="s">
+        <v>495</v>
+      </c>
+      <c r="D4" s="26" t="s">
         <v>496</v>
       </c>
-      <c r="C4" s="26" t="s">
-        <v>497</v>
-      </c>
-      <c r="D4" s="26" t="s">
-        <v>498</v>
-      </c>
       <c r="E4" s="27" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="F4" s="25" t="s">
         <v>181</v>
@@ -4510,61 +4550,67 @@
         <v>Século</v>
       </c>
       <c r="P4" s="61" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="Q4" s="61" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="R4" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="S4" s="53" t="str">
+        <v>480</v>
+      </c>
+      <c r="S4" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="T4" s="53" t="str">
         <f t="shared" si="2"/>
         <v>Temporais</v>
       </c>
-      <c r="T4" s="53" t="str">
+      <c r="U4" s="53" t="str">
         <f t="shared" si="2"/>
         <v>Eventos</v>
       </c>
-      <c r="U4" s="60" t="str">
+      <c r="V4" s="60" t="str">
         <f t="shared" si="2"/>
         <v>Macroeventos</v>
       </c>
-      <c r="V4" s="53" t="s">
+      <c r="W4" s="53" t="s">
         <v>179</v>
       </c>
-      <c r="W4" s="64" t="str">
+      <c r="X4" s="64" t="str">
         <f t="shared" si="3"/>
         <v>Key-CRONO-4</v>
       </c>
-      <c r="X4" s="53" t="s">
-        <v>510</v>
-      </c>
       <c r="Y4" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="Z4" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="AA4" s="53" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>520</v>
+      </c>
+      <c r="AB4" s="53" t="s">
+        <v>520</v>
+      </c>
+      <c r="AC4" s="53" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="69">
         <v>5</v>
       </c>
       <c r="B5" s="65" t="s">
+        <v>494</v>
+      </c>
+      <c r="C5" s="26" t="s">
+        <v>495</v>
+      </c>
+      <c r="D5" s="26" t="s">
         <v>496</v>
       </c>
-      <c r="C5" s="26" t="s">
-        <v>497</v>
-      </c>
-      <c r="D5" s="26" t="s">
-        <v>498</v>
-      </c>
       <c r="E5" s="27" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="F5" s="25" t="s">
         <v>316</v>
@@ -4601,61 +4647,67 @@
         <v>Quinquagenário</v>
       </c>
       <c r="P5" s="61" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="Q5" s="61" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="R5" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="S5" s="53" t="str">
+        <v>445</v>
+      </c>
+      <c r="S5" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="T5" s="53" t="str">
         <f t="shared" si="2"/>
         <v>Temporais</v>
       </c>
-      <c r="T5" s="53" t="str">
+      <c r="U5" s="53" t="str">
         <f t="shared" si="2"/>
         <v>Eventos</v>
       </c>
-      <c r="U5" s="60" t="str">
+      <c r="V5" s="60" t="str">
         <f t="shared" si="2"/>
         <v>Macroeventos</v>
       </c>
-      <c r="V5" s="53" t="s">
+      <c r="W5" s="53" t="s">
         <v>179</v>
       </c>
-      <c r="W5" s="64" t="str">
+      <c r="X5" s="64" t="str">
         <f t="shared" si="3"/>
         <v>Key-CRONO-5</v>
       </c>
-      <c r="X5" s="53" t="s">
-        <v>510</v>
-      </c>
       <c r="Y5" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="Z5" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="AA5" s="53" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>520</v>
+      </c>
+      <c r="AB5" s="53" t="s">
+        <v>520</v>
+      </c>
+      <c r="AC5" s="53" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="6" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="69">
         <v>6</v>
       </c>
       <c r="B6" s="65" t="s">
+        <v>494</v>
+      </c>
+      <c r="C6" s="26" t="s">
+        <v>495</v>
+      </c>
+      <c r="D6" s="26" t="s">
         <v>496</v>
       </c>
-      <c r="C6" s="26" t="s">
-        <v>497</v>
-      </c>
-      <c r="D6" s="26" t="s">
-        <v>498</v>
-      </c>
       <c r="E6" s="27" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="F6" s="25" t="s">
         <v>180</v>
@@ -4692,61 +4744,67 @@
         <v>Década</v>
       </c>
       <c r="P6" s="61" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="Q6" s="61" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="R6" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="S6" s="53" t="str">
+        <v>446</v>
+      </c>
+      <c r="S6" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="T6" s="53" t="str">
         <f t="shared" si="2"/>
         <v>Temporais</v>
       </c>
-      <c r="T6" s="53" t="str">
+      <c r="U6" s="53" t="str">
         <f t="shared" si="2"/>
         <v>Eventos</v>
       </c>
-      <c r="U6" s="60" t="str">
+      <c r="V6" s="60" t="str">
         <f t="shared" si="2"/>
         <v>Macroeventos</v>
       </c>
-      <c r="V6" s="53" t="s">
+      <c r="W6" s="53" t="s">
         <v>179</v>
       </c>
-      <c r="W6" s="64" t="str">
+      <c r="X6" s="64" t="str">
         <f t="shared" si="3"/>
         <v>Key-CRONO-6</v>
       </c>
-      <c r="X6" s="53" t="s">
-        <v>510</v>
-      </c>
       <c r="Y6" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="Z6" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="AA6" s="53" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>520</v>
+      </c>
+      <c r="AB6" s="53" t="s">
+        <v>520</v>
+      </c>
+      <c r="AC6" s="53" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="7" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="69">
         <v>7</v>
       </c>
       <c r="B7" s="65" t="s">
+        <v>494</v>
+      </c>
+      <c r="C7" s="26" t="s">
+        <v>495</v>
+      </c>
+      <c r="D7" s="26" t="s">
         <v>496</v>
       </c>
-      <c r="C7" s="26" t="s">
-        <v>497</v>
-      </c>
-      <c r="D7" s="26" t="s">
-        <v>498</v>
-      </c>
       <c r="E7" s="27" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="F7" s="25" t="s">
         <v>314</v>
@@ -4783,61 +4841,67 @@
         <v>Quinquênio</v>
       </c>
       <c r="P7" s="61" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="Q7" s="61" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="R7" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="S7" s="53" t="str">
+        <v>447</v>
+      </c>
+      <c r="S7" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="T7" s="53" t="str">
         <f t="shared" si="2"/>
         <v>Temporais</v>
       </c>
-      <c r="T7" s="53" t="str">
+      <c r="U7" s="53" t="str">
         <f t="shared" si="2"/>
         <v>Eventos</v>
       </c>
-      <c r="U7" s="60" t="str">
+      <c r="V7" s="60" t="str">
         <f t="shared" si="2"/>
         <v>Macroeventos</v>
       </c>
-      <c r="V7" s="53" t="s">
+      <c r="W7" s="53" t="s">
         <v>179</v>
       </c>
-      <c r="W7" s="64" t="str">
+      <c r="X7" s="64" t="str">
         <f t="shared" si="3"/>
         <v>Key-CRONO-7</v>
       </c>
-      <c r="X7" s="53" t="s">
-        <v>510</v>
-      </c>
       <c r="Y7" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="Z7" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="AA7" s="53" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>520</v>
+      </c>
+      <c r="AB7" s="53" t="s">
+        <v>520</v>
+      </c>
+      <c r="AC7" s="53" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="69">
         <v>8</v>
       </c>
       <c r="B8" s="65" t="s">
+        <v>494</v>
+      </c>
+      <c r="C8" s="26" t="s">
+        <v>495</v>
+      </c>
+      <c r="D8" s="26" t="s">
         <v>496</v>
       </c>
-      <c r="C8" s="26" t="s">
-        <v>497</v>
-      </c>
-      <c r="D8" s="26" t="s">
-        <v>498</v>
-      </c>
       <c r="E8" s="27" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="F8" s="25" t="s">
         <v>313</v>
@@ -4874,61 +4938,67 @@
         <v>Lustro</v>
       </c>
       <c r="P8" s="61" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="Q8" s="61" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="R8" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="S8" s="53" t="str">
+        <v>447</v>
+      </c>
+      <c r="S8" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="T8" s="53" t="str">
         <f t="shared" si="2"/>
         <v>Temporais</v>
       </c>
-      <c r="T8" s="53" t="str">
+      <c r="U8" s="53" t="str">
         <f t="shared" si="2"/>
         <v>Eventos</v>
       </c>
-      <c r="U8" s="60" t="str">
+      <c r="V8" s="60" t="str">
         <f t="shared" si="2"/>
         <v>Macroeventos</v>
       </c>
-      <c r="V8" s="53" t="s">
+      <c r="W8" s="53" t="s">
         <v>179</v>
       </c>
-      <c r="W8" s="64" t="str">
+      <c r="X8" s="64" t="str">
         <f t="shared" si="3"/>
         <v>Key-CRONO-8</v>
       </c>
-      <c r="X8" s="53" t="s">
-        <v>510</v>
-      </c>
       <c r="Y8" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="Z8" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="AA8" s="53" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>520</v>
+      </c>
+      <c r="AB8" s="53" t="s">
+        <v>520</v>
+      </c>
+      <c r="AC8" s="53" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="69">
         <v>9</v>
       </c>
       <c r="B9" s="65" t="s">
+        <v>494</v>
+      </c>
+      <c r="C9" s="26" t="s">
+        <v>495</v>
+      </c>
+      <c r="D9" s="26" t="s">
         <v>496</v>
       </c>
-      <c r="C9" s="26" t="s">
-        <v>497</v>
-      </c>
-      <c r="D9" s="26" t="s">
-        <v>498</v>
-      </c>
       <c r="E9" s="27" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="F9" s="25" t="s">
         <v>315</v>
@@ -4965,64 +5035,70 @@
         <v>Biênio</v>
       </c>
       <c r="P9" s="61" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="Q9" s="61" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="R9" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="S9" s="53" t="str">
-        <f t="shared" ref="S9" si="9">SUBSTITUTE(C9, "_", " ")</f>
+        <v>448</v>
+      </c>
+      <c r="S9" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="T9" s="53" t="str">
+        <f t="shared" ref="T9" si="9">SUBSTITUTE(C9, "_", " ")</f>
         <v>Temporais</v>
       </c>
-      <c r="T9" s="53" t="str">
-        <f t="shared" ref="T9" si="10">SUBSTITUTE(D9, "_", " ")</f>
+      <c r="U9" s="53" t="str">
+        <f t="shared" ref="U9" si="10">SUBSTITUTE(D9, "_", " ")</f>
         <v>Eventos</v>
       </c>
-      <c r="U9" s="60" t="str">
-        <f t="shared" ref="U9" si="11">SUBSTITUTE(E9, "_", " ")</f>
+      <c r="V9" s="60" t="str">
+        <f t="shared" ref="V9" si="11">SUBSTITUTE(E9, "_", " ")</f>
         <v>Macroeventos</v>
       </c>
-      <c r="V9" s="53" t="s">
+      <c r="W9" s="53" t="s">
         <v>179</v>
       </c>
-      <c r="W9" s="64" t="str">
+      <c r="X9" s="64" t="str">
         <f t="shared" si="3"/>
         <v>Key-CRONO-9</v>
       </c>
-      <c r="X9" s="53" t="s">
-        <v>510</v>
-      </c>
       <c r="Y9" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="Z9" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="AA9" s="53" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>520</v>
+      </c>
+      <c r="AB9" s="53" t="s">
+        <v>520</v>
+      </c>
+      <c r="AC9" s="53" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="69">
         <v>10</v>
       </c>
       <c r="B10" s="65" t="s">
+        <v>494</v>
+      </c>
+      <c r="C10" s="26" t="s">
+        <v>495</v>
+      </c>
+      <c r="D10" s="26" t="s">
         <v>496</v>
       </c>
-      <c r="C10" s="26" t="s">
-        <v>497</v>
-      </c>
-      <c r="D10" s="26" t="s">
-        <v>498</v>
-      </c>
       <c r="E10" s="27" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="F10" s="25" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="G10" s="66" t="s">
         <v>1</v>
@@ -5056,61 +5132,67 @@
         <v>Bienal</v>
       </c>
       <c r="P10" s="61" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="Q10" s="61" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="R10" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="S10" s="53" t="str">
+        <v>448</v>
+      </c>
+      <c r="S10" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="T10" s="53" t="str">
         <f t="shared" si="2"/>
         <v>Temporais</v>
       </c>
-      <c r="T10" s="53" t="str">
+      <c r="U10" s="53" t="str">
         <f t="shared" si="2"/>
         <v>Eventos</v>
       </c>
-      <c r="U10" s="60" t="str">
+      <c r="V10" s="60" t="str">
         <f t="shared" si="2"/>
         <v>Macroeventos</v>
       </c>
-      <c r="V10" s="53" t="s">
+      <c r="W10" s="53" t="s">
         <v>179</v>
       </c>
-      <c r="W10" s="64" t="str">
+      <c r="X10" s="64" t="str">
         <f t="shared" si="3"/>
         <v>Key-CRONO-10</v>
       </c>
-      <c r="X10" s="53" t="s">
-        <v>510</v>
-      </c>
       <c r="Y10" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="Z10" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="AA10" s="53" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>520</v>
+      </c>
+      <c r="AB10" s="53" t="s">
+        <v>520</v>
+      </c>
+      <c r="AC10" s="53" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="69">
         <v>11</v>
       </c>
       <c r="B11" s="65" t="s">
+        <v>494</v>
+      </c>
+      <c r="C11" s="26" t="s">
+        <v>495</v>
+      </c>
+      <c r="D11" s="26" t="s">
         <v>496</v>
       </c>
-      <c r="C11" s="26" t="s">
-        <v>497</v>
-      </c>
-      <c r="D11" s="26" t="s">
-        <v>498</v>
-      </c>
       <c r="E11" s="27" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="F11" s="25" t="s">
         <v>51</v>
@@ -5147,61 +5229,67 @@
         <v>Ano</v>
       </c>
       <c r="P11" s="61" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="Q11" s="61" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="R11" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="S11" s="53" t="str">
+        <v>449</v>
+      </c>
+      <c r="S11" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="T11" s="53" t="str">
         <f t="shared" si="2"/>
         <v>Temporais</v>
       </c>
-      <c r="T11" s="53" t="str">
+      <c r="U11" s="53" t="str">
         <f t="shared" si="2"/>
         <v>Eventos</v>
       </c>
-      <c r="U11" s="60" t="str">
+      <c r="V11" s="60" t="str">
         <f t="shared" si="2"/>
         <v>Calendários</v>
       </c>
-      <c r="V11" s="53" t="s">
+      <c r="W11" s="53" t="s">
         <v>179</v>
       </c>
-      <c r="W11" s="64" t="str">
+      <c r="X11" s="64" t="str">
         <f t="shared" si="3"/>
         <v>Key-CRONO-11</v>
       </c>
-      <c r="X11" s="53" t="s">
-        <v>510</v>
-      </c>
       <c r="Y11" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="Z11" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="AA11" s="53" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>520</v>
+      </c>
+      <c r="AB11" s="53" t="s">
+        <v>520</v>
+      </c>
+      <c r="AC11" s="53" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="12" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="69">
         <v>12</v>
       </c>
       <c r="B12" s="65" t="s">
+        <v>494</v>
+      </c>
+      <c r="C12" s="26" t="s">
+        <v>495</v>
+      </c>
+      <c r="D12" s="26" t="s">
         <v>496</v>
       </c>
-      <c r="C12" s="26" t="s">
-        <v>497</v>
-      </c>
-      <c r="D12" s="26" t="s">
-        <v>498</v>
-      </c>
       <c r="E12" s="27" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="F12" s="25" t="s">
         <v>312</v>
@@ -5238,64 +5326,70 @@
         <v>Semestre</v>
       </c>
       <c r="P12" s="61" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="Q12" s="61" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="R12" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="S12" s="53" t="str">
+        <v>450</v>
+      </c>
+      <c r="S12" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="T12" s="53" t="str">
         <f t="shared" si="2"/>
         <v>Temporais</v>
       </c>
-      <c r="T12" s="53" t="str">
+      <c r="U12" s="53" t="str">
         <f t="shared" si="2"/>
         <v>Eventos</v>
       </c>
-      <c r="U12" s="60" t="str">
+      <c r="V12" s="60" t="str">
         <f t="shared" si="2"/>
         <v>Calendários</v>
       </c>
-      <c r="V12" s="53" t="s">
+      <c r="W12" s="53" t="s">
         <v>179</v>
       </c>
-      <c r="W12" s="64" t="str">
+      <c r="X12" s="64" t="str">
         <f t="shared" si="3"/>
         <v>Key-CRONO-12</v>
       </c>
-      <c r="X12" s="53" t="s">
-        <v>510</v>
-      </c>
       <c r="Y12" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="Z12" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="AA12" s="53" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>520</v>
+      </c>
+      <c r="AB12" s="53" t="s">
+        <v>520</v>
+      </c>
+      <c r="AC12" s="53" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="69">
         <v>13</v>
       </c>
       <c r="B13" s="65" t="s">
+        <v>494</v>
+      </c>
+      <c r="C13" s="26" t="s">
+        <v>495</v>
+      </c>
+      <c r="D13" s="26" t="s">
         <v>496</v>
       </c>
-      <c r="C13" s="26" t="s">
-        <v>497</v>
-      </c>
-      <c r="D13" s="26" t="s">
-        <v>498</v>
-      </c>
       <c r="E13" s="27" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="F13" s="25" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="G13" s="66" t="s">
         <v>1</v>
@@ -5329,61 +5423,67 @@
         <v>Quadrimestre</v>
       </c>
       <c r="P13" s="61" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="Q13" s="61" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="R13" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="S13" s="53" t="str">
+        <v>451</v>
+      </c>
+      <c r="S13" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="T13" s="53" t="str">
         <f t="shared" si="2"/>
         <v>Temporais</v>
       </c>
-      <c r="T13" s="53" t="str">
+      <c r="U13" s="53" t="str">
         <f t="shared" si="2"/>
         <v>Eventos</v>
       </c>
-      <c r="U13" s="60" t="str">
+      <c r="V13" s="60" t="str">
         <f t="shared" si="2"/>
         <v>Calendários</v>
       </c>
-      <c r="V13" s="53" t="s">
+      <c r="W13" s="53" t="s">
         <v>179</v>
       </c>
-      <c r="W13" s="64" t="str">
+      <c r="X13" s="64" t="str">
         <f t="shared" si="3"/>
         <v>Key-CRONO-13</v>
       </c>
-      <c r="X13" s="53" t="s">
-        <v>510</v>
-      </c>
       <c r="Y13" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="Z13" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="AA13" s="53" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>520</v>
+      </c>
+      <c r="AB13" s="53" t="s">
+        <v>520</v>
+      </c>
+      <c r="AC13" s="53" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="69">
         <v>14</v>
       </c>
       <c r="B14" s="65" t="s">
+        <v>494</v>
+      </c>
+      <c r="C14" s="26" t="s">
+        <v>495</v>
+      </c>
+      <c r="D14" s="26" t="s">
         <v>496</v>
       </c>
-      <c r="C14" s="26" t="s">
-        <v>497</v>
-      </c>
-      <c r="D14" s="26" t="s">
-        <v>498</v>
-      </c>
       <c r="E14" s="27" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="F14" s="25" t="s">
         <v>311</v>
@@ -5420,61 +5520,67 @@
         <v>Trimestre</v>
       </c>
       <c r="P14" s="61" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="Q14" s="61" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="R14" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="S14" s="53" t="str">
+        <v>452</v>
+      </c>
+      <c r="S14" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="T14" s="53" t="str">
         <f t="shared" si="2"/>
         <v>Temporais</v>
       </c>
-      <c r="T14" s="53" t="str">
+      <c r="U14" s="53" t="str">
         <f t="shared" si="2"/>
         <v>Eventos</v>
       </c>
-      <c r="U14" s="60" t="str">
+      <c r="V14" s="60" t="str">
         <f t="shared" si="2"/>
         <v>Calendários</v>
       </c>
-      <c r="V14" s="53" t="s">
+      <c r="W14" s="53" t="s">
         <v>179</v>
       </c>
-      <c r="W14" s="64" t="str">
+      <c r="X14" s="64" t="str">
         <f t="shared" si="3"/>
         <v>Key-CRONO-14</v>
       </c>
-      <c r="X14" s="53" t="s">
-        <v>510</v>
-      </c>
       <c r="Y14" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="Z14" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="AA14" s="53" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>520</v>
+      </c>
+      <c r="AB14" s="53" t="s">
+        <v>520</v>
+      </c>
+      <c r="AC14" s="53" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="69">
         <v>15</v>
       </c>
       <c r="B15" s="65" t="s">
+        <v>494</v>
+      </c>
+      <c r="C15" s="26" t="s">
+        <v>495</v>
+      </c>
+      <c r="D15" s="26" t="s">
         <v>496</v>
       </c>
-      <c r="C15" s="26" t="s">
-        <v>497</v>
-      </c>
-      <c r="D15" s="26" t="s">
-        <v>498</v>
-      </c>
       <c r="E15" s="27" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="F15" s="25" t="s">
         <v>52</v>
@@ -5511,61 +5617,67 @@
         <v>Mês</v>
       </c>
       <c r="P15" s="61" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="Q15" s="61" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="R15" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="S15" s="53" t="str">
+        <v>453</v>
+      </c>
+      <c r="S15" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="T15" s="53" t="str">
         <f t="shared" si="2"/>
         <v>Temporais</v>
       </c>
-      <c r="T15" s="53" t="str">
+      <c r="U15" s="53" t="str">
         <f t="shared" si="2"/>
         <v>Eventos</v>
       </c>
-      <c r="U15" s="60" t="str">
+      <c r="V15" s="60" t="str">
         <f t="shared" si="2"/>
         <v>Calendários</v>
       </c>
-      <c r="V15" s="53" t="s">
+      <c r="W15" s="53" t="s">
         <v>179</v>
       </c>
-      <c r="W15" s="64" t="str">
+      <c r="X15" s="64" t="str">
         <f t="shared" si="3"/>
         <v>Key-CRONO-15</v>
       </c>
-      <c r="X15" s="53" t="s">
-        <v>510</v>
-      </c>
       <c r="Y15" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="Z15" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="AA15" s="53" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>520</v>
+      </c>
+      <c r="AB15" s="53" t="s">
+        <v>520</v>
+      </c>
+      <c r="AC15" s="53" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="69">
         <v>16</v>
       </c>
       <c r="B16" s="65" t="s">
+        <v>494</v>
+      </c>
+      <c r="C16" s="26" t="s">
+        <v>495</v>
+      </c>
+      <c r="D16" s="26" t="s">
         <v>496</v>
       </c>
-      <c r="C16" s="26" t="s">
-        <v>497</v>
-      </c>
-      <c r="D16" s="26" t="s">
-        <v>498</v>
-      </c>
       <c r="E16" s="27" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="F16" s="25" t="s">
         <v>53</v>
@@ -5602,61 +5714,67 @@
         <v>Semana</v>
       </c>
       <c r="P16" s="61" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="Q16" s="61" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="R16" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="S16" s="53" t="str">
+        <v>454</v>
+      </c>
+      <c r="S16" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="T16" s="53" t="str">
         <f t="shared" si="2"/>
         <v>Temporais</v>
       </c>
-      <c r="T16" s="53" t="str">
+      <c r="U16" s="53" t="str">
         <f t="shared" si="2"/>
         <v>Eventos</v>
       </c>
-      <c r="U16" s="60" t="str">
+      <c r="V16" s="60" t="str">
         <f t="shared" si="2"/>
         <v>Calendários</v>
       </c>
-      <c r="V16" s="53" t="s">
+      <c r="W16" s="53" t="s">
         <v>179</v>
       </c>
-      <c r="W16" s="64" t="str">
+      <c r="X16" s="64" t="str">
         <f t="shared" si="3"/>
         <v>Key-CRONO-16</v>
       </c>
-      <c r="X16" s="53" t="s">
-        <v>510</v>
-      </c>
       <c r="Y16" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="Z16" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="AA16" s="53" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="17" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>520</v>
+      </c>
+      <c r="AB16" s="53" t="s">
+        <v>520</v>
+      </c>
+      <c r="AC16" s="53" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="17" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="69">
         <v>17</v>
       </c>
       <c r="B17" s="65" t="s">
+        <v>494</v>
+      </c>
+      <c r="C17" s="26" t="s">
+        <v>495</v>
+      </c>
+      <c r="D17" s="26" t="s">
         <v>496</v>
       </c>
-      <c r="C17" s="26" t="s">
-        <v>497</v>
-      </c>
-      <c r="D17" s="26" t="s">
-        <v>498</v>
-      </c>
       <c r="E17" s="27" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="F17" s="25" t="s">
         <v>54</v>
@@ -5693,64 +5811,70 @@
         <v>Dia</v>
       </c>
       <c r="P17" s="61" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="Q17" s="61" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="R17" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="S17" s="53" t="str">
-        <f t="shared" ref="S17" si="16">SUBSTITUTE(C17, "_", " ")</f>
+        <v>455</v>
+      </c>
+      <c r="S17" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="T17" s="53" t="str">
+        <f t="shared" ref="T17" si="16">SUBSTITUTE(C17, "_", " ")</f>
         <v>Temporais</v>
       </c>
-      <c r="T17" s="53" t="str">
-        <f t="shared" ref="T17" si="17">SUBSTITUTE(D17, "_", " ")</f>
+      <c r="U17" s="53" t="str">
+        <f t="shared" ref="U17" si="17">SUBSTITUTE(D17, "_", " ")</f>
         <v>Eventos</v>
       </c>
-      <c r="U17" s="60" t="str">
-        <f t="shared" ref="U17" si="18">SUBSTITUTE(E17, "_", " ")</f>
+      <c r="V17" s="60" t="str">
+        <f t="shared" ref="V17" si="18">SUBSTITUTE(E17, "_", " ")</f>
         <v>Calendários</v>
       </c>
-      <c r="V17" s="53" t="s">
+      <c r="W17" s="53" t="s">
         <v>179</v>
       </c>
-      <c r="W17" s="64" t="str">
-        <f t="shared" ref="W17" si="19">CONCATENATE("Key-CRONO-",A17)</f>
+      <c r="X17" s="64" t="str">
+        <f t="shared" ref="X17" si="19">CONCATENATE("Key-CRONO-",A17)</f>
         <v>Key-CRONO-17</v>
       </c>
-      <c r="X17" s="53" t="s">
-        <v>510</v>
-      </c>
       <c r="Y17" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="Z17" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="AA17" s="53" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="18" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>520</v>
+      </c>
+      <c r="AB17" s="53" t="s">
+        <v>520</v>
+      </c>
+      <c r="AC17" s="53" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="18" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="69">
         <v>18</v>
       </c>
       <c r="B18" s="65" t="s">
+        <v>494</v>
+      </c>
+      <c r="C18" s="26" t="s">
+        <v>495</v>
+      </c>
+      <c r="D18" s="26" t="s">
         <v>496</v>
       </c>
-      <c r="C18" s="26" t="s">
-        <v>497</v>
-      </c>
-      <c r="D18" s="26" t="s">
-        <v>498</v>
-      </c>
       <c r="E18" s="27" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="F18" s="25" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="G18" s="66" t="s">
         <v>1</v>
@@ -5784,62 +5908,67 @@
         <v>Data</v>
       </c>
       <c r="P18" s="61" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="Q18" s="61" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="R18" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="S18" s="53" t="str">
+        <v>514</v>
+      </c>
+      <c r="S18" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="T18" s="53" t="str">
         <f t="shared" si="2"/>
         <v>Temporais</v>
       </c>
-      <c r="T18" s="53" t="str">
+      <c r="U18" s="53" t="str">
         <f t="shared" si="2"/>
         <v>Eventos</v>
       </c>
-      <c r="U18" s="60" t="str">
+      <c r="V18" s="60" t="str">
         <f t="shared" si="2"/>
         <v>Calendários</v>
       </c>
-      <c r="V18" s="53" t="s">
+      <c r="W18" s="53" t="s">
         <v>179</v>
       </c>
-      <c r="W18" s="64" t="str">
+      <c r="X18" s="64" t="str">
         <f t="shared" si="3"/>
         <v>Key-CRONO-18</v>
       </c>
-      <c r="X18" s="53" t="s">
-        <v>510</v>
-      </c>
       <c r="Y18" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="Z18" s="53" t="s">
-        <v>510</v>
-      </c>
-      <c r="AA18" s="53" t="str">
-        <f>_xlfn.TRANSLATE(Q18,"es","en")</f>
-        <v>A calendar date for an event that happened or will happen.</v>
-      </c>
-    </row>
-    <row r="19" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>520</v>
+      </c>
+      <c r="AA18" s="53" t="s">
+        <v>520</v>
+      </c>
+      <c r="AB18" s="53" t="s">
+        <v>520</v>
+      </c>
+      <c r="AC18" s="53" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="19" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="69">
         <v>19</v>
       </c>
       <c r="B19" s="65" t="s">
+        <v>494</v>
+      </c>
+      <c r="C19" s="26" t="s">
+        <v>495</v>
+      </c>
+      <c r="D19" s="26" t="s">
         <v>496</v>
       </c>
-      <c r="C19" s="26" t="s">
-        <v>497</v>
-      </c>
-      <c r="D19" s="26" t="s">
-        <v>498</v>
-      </c>
       <c r="E19" s="27" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="F19" s="25" t="s">
         <v>247</v>
@@ -5879,58 +6008,64 @@
         <v>331</v>
       </c>
       <c r="Q19" s="61" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="R19" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="S19" s="53" t="str">
+        <v>456</v>
+      </c>
+      <c r="S19" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="T19" s="53" t="str">
         <f t="shared" si="2"/>
         <v>Temporais</v>
       </c>
-      <c r="T19" s="53" t="str">
+      <c r="U19" s="53" t="str">
         <f t="shared" si="2"/>
         <v>Eventos</v>
       </c>
-      <c r="U19" s="60" t="str">
+      <c r="V19" s="60" t="str">
         <f t="shared" si="2"/>
         <v>Calendários</v>
       </c>
-      <c r="V19" s="53" t="s">
+      <c r="W19" s="53" t="s">
         <v>179</v>
       </c>
-      <c r="W19" s="64" t="str">
+      <c r="X19" s="64" t="str">
         <f t="shared" si="3"/>
         <v>Key-CRONO-19</v>
       </c>
-      <c r="X19" s="53" t="s">
-        <v>510</v>
-      </c>
       <c r="Y19" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="Z19" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="AA19" s="53" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="20" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>520</v>
+      </c>
+      <c r="AB19" s="53" t="s">
+        <v>520</v>
+      </c>
+      <c r="AC19" s="53" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="20" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="69">
         <v>20</v>
       </c>
       <c r="B20" s="65" t="s">
+        <v>494</v>
+      </c>
+      <c r="C20" s="26" t="s">
+        <v>495</v>
+      </c>
+      <c r="D20" s="26" t="s">
         <v>496</v>
       </c>
-      <c r="C20" s="26" t="s">
-        <v>497</v>
-      </c>
-      <c r="D20" s="26" t="s">
-        <v>498</v>
-      </c>
       <c r="E20" s="27" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="F20" s="25" t="s">
         <v>55</v>
@@ -5967,61 +6102,67 @@
         <v>Hora</v>
       </c>
       <c r="P20" s="61" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="Q20" s="61" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="R20" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="S20" s="53" t="str">
+        <v>457</v>
+      </c>
+      <c r="S20" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="T20" s="53" t="str">
         <f t="shared" si="2"/>
         <v>Temporais</v>
       </c>
-      <c r="T20" s="53" t="str">
+      <c r="U20" s="53" t="str">
         <f t="shared" si="2"/>
         <v>Eventos</v>
       </c>
-      <c r="U20" s="60" t="str">
+      <c r="V20" s="60" t="str">
         <f t="shared" si="2"/>
         <v>Horários</v>
       </c>
-      <c r="V20" s="53" t="s">
+      <c r="W20" s="53" t="s">
         <v>179</v>
       </c>
-      <c r="W20" s="64" t="str">
+      <c r="X20" s="64" t="str">
         <f t="shared" si="3"/>
         <v>Key-CRONO-20</v>
       </c>
-      <c r="X20" s="53" t="s">
-        <v>510</v>
-      </c>
       <c r="Y20" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="Z20" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="AA20" s="53" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="21" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>520</v>
+      </c>
+      <c r="AB20" s="53" t="s">
+        <v>520</v>
+      </c>
+      <c r="AC20" s="53" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="21" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="69">
         <v>21</v>
       </c>
       <c r="B21" s="65" t="s">
+        <v>494</v>
+      </c>
+      <c r="C21" s="26" t="s">
+        <v>495</v>
+      </c>
+      <c r="D21" s="26" t="s">
         <v>496</v>
       </c>
-      <c r="C21" s="26" t="s">
-        <v>497</v>
-      </c>
-      <c r="D21" s="26" t="s">
-        <v>498</v>
-      </c>
       <c r="E21" s="27" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="F21" s="25" t="s">
         <v>56</v>
@@ -6058,61 +6199,67 @@
         <v>Minuto</v>
       </c>
       <c r="P21" s="61" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="Q21" s="61" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="R21" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="S21" s="53" t="str">
+        <v>458</v>
+      </c>
+      <c r="S21" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="T21" s="53" t="str">
         <f t="shared" si="2"/>
         <v>Temporais</v>
       </c>
-      <c r="T21" s="53" t="str">
+      <c r="U21" s="53" t="str">
         <f t="shared" si="2"/>
         <v>Eventos</v>
       </c>
-      <c r="U21" s="60" t="str">
+      <c r="V21" s="60" t="str">
         <f t="shared" si="2"/>
         <v>Horários</v>
       </c>
-      <c r="V21" s="53" t="s">
+      <c r="W21" s="53" t="s">
         <v>179</v>
       </c>
-      <c r="W21" s="64" t="str">
+      <c r="X21" s="64" t="str">
         <f t="shared" si="3"/>
         <v>Key-CRONO-21</v>
       </c>
-      <c r="X21" s="53" t="s">
-        <v>510</v>
-      </c>
       <c r="Y21" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="Z21" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="AA21" s="53" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="22" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>520</v>
+      </c>
+      <c r="AB21" s="53" t="s">
+        <v>520</v>
+      </c>
+      <c r="AC21" s="53" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="22" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="69">
         <v>22</v>
       </c>
       <c r="B22" s="65" t="s">
+        <v>494</v>
+      </c>
+      <c r="C22" s="26" t="s">
+        <v>495</v>
+      </c>
+      <c r="D22" s="26" t="s">
         <v>496</v>
       </c>
-      <c r="C22" s="26" t="s">
-        <v>497</v>
-      </c>
-      <c r="D22" s="26" t="s">
-        <v>498</v>
-      </c>
       <c r="E22" s="27" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="F22" s="25" t="s">
         <v>57</v>
@@ -6149,61 +6296,67 @@
         <v>Segundo</v>
       </c>
       <c r="P22" s="61" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="Q22" s="61" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="R22" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="S22" s="53" t="str">
+        <v>459</v>
+      </c>
+      <c r="S22" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="T22" s="53" t="str">
         <f t="shared" si="2"/>
         <v>Temporais</v>
       </c>
-      <c r="T22" s="53" t="str">
+      <c r="U22" s="53" t="str">
         <f t="shared" si="2"/>
         <v>Eventos</v>
       </c>
-      <c r="U22" s="60" t="str">
+      <c r="V22" s="60" t="str">
         <f t="shared" si="2"/>
         <v>Horários</v>
       </c>
-      <c r="V22" s="53" t="s">
+      <c r="W22" s="53" t="s">
         <v>179</v>
       </c>
-      <c r="W22" s="64" t="str">
+      <c r="X22" s="64" t="str">
         <f t="shared" si="3"/>
         <v>Key-CRONO-22</v>
       </c>
-      <c r="X22" s="53" t="s">
-        <v>510</v>
-      </c>
       <c r="Y22" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="Z22" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="AA22" s="53" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="23" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>520</v>
+      </c>
+      <c r="AB22" s="53" t="s">
+        <v>520</v>
+      </c>
+      <c r="AC22" s="53" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="23" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="69">
         <v>23</v>
       </c>
       <c r="B23" s="65" t="s">
+        <v>494</v>
+      </c>
+      <c r="C23" s="26" t="s">
+        <v>495</v>
+      </c>
+      <c r="D23" s="26" t="s">
         <v>496</v>
       </c>
-      <c r="C23" s="26" t="s">
-        <v>497</v>
-      </c>
-      <c r="D23" s="26" t="s">
-        <v>498</v>
-      </c>
       <c r="E23" s="27" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="F23" s="25" t="s">
         <v>58</v>
@@ -6246,55 +6399,61 @@
         <v>332</v>
       </c>
       <c r="R23" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="S23" s="53" t="str">
+        <v>460</v>
+      </c>
+      <c r="S23" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="T23" s="53" t="str">
         <f t="shared" si="2"/>
         <v>Temporais</v>
       </c>
-      <c r="T23" s="53" t="str">
+      <c r="U23" s="53" t="str">
         <f t="shared" si="2"/>
         <v>Eventos</v>
       </c>
-      <c r="U23" s="60" t="str">
+      <c r="V23" s="60" t="str">
         <f t="shared" si="2"/>
         <v>Horários</v>
       </c>
-      <c r="V23" s="53" t="s">
+      <c r="W23" s="53" t="s">
         <v>179</v>
       </c>
-      <c r="W23" s="64" t="str">
+      <c r="X23" s="64" t="str">
         <f t="shared" si="3"/>
         <v>Key-CRONO-23</v>
       </c>
-      <c r="X23" s="53" t="s">
-        <v>510</v>
-      </c>
       <c r="Y23" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="Z23" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="AA23" s="53" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="24" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>520</v>
+      </c>
+      <c r="AB23" s="53" t="s">
+        <v>520</v>
+      </c>
+      <c r="AC23" s="53" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="24" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="69">
         <v>24</v>
       </c>
       <c r="B24" s="65" t="s">
+        <v>494</v>
+      </c>
+      <c r="C24" s="26" t="s">
+        <v>495</v>
+      </c>
+      <c r="D24" s="26" t="s">
         <v>496</v>
       </c>
-      <c r="C24" s="26" t="s">
-        <v>497</v>
-      </c>
-      <c r="D24" s="26" t="s">
-        <v>498</v>
-      </c>
       <c r="E24" s="27" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="F24" s="25" t="s">
         <v>59</v>
@@ -6334,58 +6493,64 @@
         <v>317</v>
       </c>
       <c r="Q24" s="61" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="R24" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="S24" s="53" t="str">
+        <v>439</v>
+      </c>
+      <c r="S24" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="T24" s="53" t="str">
         <f t="shared" si="2"/>
         <v>Temporais</v>
       </c>
-      <c r="T24" s="53" t="str">
+      <c r="U24" s="53" t="str">
         <f t="shared" si="2"/>
         <v>Eventos</v>
       </c>
-      <c r="U24" s="60" t="str">
+      <c r="V24" s="60" t="str">
         <f t="shared" si="2"/>
         <v>Microeventos</v>
       </c>
-      <c r="V24" s="53" t="s">
+      <c r="W24" s="53" t="s">
         <v>179</v>
       </c>
-      <c r="W24" s="64" t="str">
+      <c r="X24" s="64" t="str">
         <f t="shared" si="3"/>
         <v>Key-CRONO-24</v>
       </c>
-      <c r="X24" s="53" t="s">
-        <v>510</v>
-      </c>
       <c r="Y24" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="Z24" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="AA24" s="53" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="25" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>520</v>
+      </c>
+      <c r="AB24" s="53" t="s">
+        <v>520</v>
+      </c>
+      <c r="AC24" s="53" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="25" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="69">
         <v>25</v>
       </c>
       <c r="B25" s="65" t="s">
+        <v>494</v>
+      </c>
+      <c r="C25" s="26" t="s">
+        <v>495</v>
+      </c>
+      <c r="D25" s="26" t="s">
         <v>496</v>
       </c>
-      <c r="C25" s="26" t="s">
-        <v>497</v>
-      </c>
-      <c r="D25" s="26" t="s">
-        <v>498</v>
-      </c>
       <c r="E25" s="27" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="F25" s="25" t="s">
         <v>60</v>
@@ -6425,58 +6590,64 @@
         <v>333</v>
       </c>
       <c r="Q25" s="61" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="R25" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="S25" s="53" t="str">
+        <v>461</v>
+      </c>
+      <c r="S25" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="T25" s="53" t="str">
         <f t="shared" si="2"/>
         <v>Temporais</v>
       </c>
-      <c r="T25" s="53" t="str">
+      <c r="U25" s="53" t="str">
         <f t="shared" si="2"/>
         <v>Eventos</v>
       </c>
-      <c r="U25" s="60" t="str">
+      <c r="V25" s="60" t="str">
         <f t="shared" si="2"/>
         <v>Microeventos</v>
       </c>
-      <c r="V25" s="53" t="s">
+      <c r="W25" s="53" t="s">
         <v>179</v>
       </c>
-      <c r="W25" s="64" t="str">
+      <c r="X25" s="64" t="str">
         <f t="shared" si="3"/>
         <v>Key-CRONO-25</v>
       </c>
-      <c r="X25" s="53" t="s">
-        <v>510</v>
-      </c>
       <c r="Y25" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="Z25" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="AA25" s="53" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="26" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>520</v>
+      </c>
+      <c r="AB25" s="53" t="s">
+        <v>520</v>
+      </c>
+      <c r="AC25" s="53" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="26" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="69">
         <v>26</v>
       </c>
       <c r="B26" s="65" t="s">
+        <v>494</v>
+      </c>
+      <c r="C26" s="26" t="s">
+        <v>495</v>
+      </c>
+      <c r="D26" s="26" t="s">
         <v>496</v>
       </c>
-      <c r="C26" s="26" t="s">
-        <v>497</v>
-      </c>
-      <c r="D26" s="26" t="s">
-        <v>498</v>
-      </c>
       <c r="E26" s="27" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="F26" s="25" t="s">
         <v>254</v>
@@ -6516,58 +6687,64 @@
         <v>334</v>
       </c>
       <c r="Q26" s="61" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="R26" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="S26" s="53" t="str">
+        <v>462</v>
+      </c>
+      <c r="S26" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="T26" s="53" t="str">
         <f t="shared" si="2"/>
         <v>Temporais</v>
       </c>
-      <c r="T26" s="53" t="str">
+      <c r="U26" s="53" t="str">
         <f t="shared" si="2"/>
         <v>Eventos</v>
       </c>
-      <c r="U26" s="60" t="str">
+      <c r="V26" s="60" t="str">
         <f t="shared" si="2"/>
         <v>Cronometrados</v>
       </c>
-      <c r="V26" s="53" t="s">
+      <c r="W26" s="53" t="s">
         <v>179</v>
       </c>
-      <c r="W26" s="64" t="str">
+      <c r="X26" s="64" t="str">
         <f t="shared" si="3"/>
         <v>Key-CRONO-26</v>
       </c>
-      <c r="X26" s="53" t="s">
-        <v>510</v>
-      </c>
       <c r="Y26" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="Z26" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="AA26" s="53" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="27" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>520</v>
+      </c>
+      <c r="AB26" s="53" t="s">
+        <v>520</v>
+      </c>
+      <c r="AC26" s="53" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="27" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="69">
         <v>27</v>
       </c>
       <c r="B27" s="65" t="s">
+        <v>494</v>
+      </c>
+      <c r="C27" s="26" t="s">
+        <v>495</v>
+      </c>
+      <c r="D27" s="26" t="s">
         <v>496</v>
       </c>
-      <c r="C27" s="26" t="s">
-        <v>497</v>
-      </c>
-      <c r="D27" s="26" t="s">
-        <v>498</v>
-      </c>
       <c r="E27" s="27" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="F27" s="25" t="s">
         <v>321</v>
@@ -6607,58 +6784,64 @@
         <v>335</v>
       </c>
       <c r="Q27" s="61" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="R27" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="S27" s="53" t="str">
+        <v>463</v>
+      </c>
+      <c r="S27" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="T27" s="53" t="str">
         <f t="shared" si="2"/>
         <v>Temporais</v>
       </c>
-      <c r="T27" s="53" t="str">
+      <c r="U27" s="53" t="str">
         <f t="shared" si="2"/>
         <v>Eventos</v>
       </c>
-      <c r="U27" s="60" t="str">
+      <c r="V27" s="60" t="str">
         <f t="shared" si="2"/>
         <v>Cronometrados</v>
       </c>
-      <c r="V27" s="53" t="s">
+      <c r="W27" s="53" t="s">
         <v>179</v>
       </c>
-      <c r="W27" s="64" t="str">
+      <c r="X27" s="64" t="str">
         <f t="shared" si="3"/>
         <v>Key-CRONO-27</v>
       </c>
-      <c r="X27" s="53" t="s">
-        <v>510</v>
-      </c>
       <c r="Y27" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="Z27" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="AA27" s="53" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="28" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>520</v>
+      </c>
+      <c r="AB27" s="53" t="s">
+        <v>520</v>
+      </c>
+      <c r="AC27" s="53" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="28" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="69">
         <v>28</v>
       </c>
       <c r="B28" s="65" t="s">
+        <v>494</v>
+      </c>
+      <c r="C28" s="26" t="s">
+        <v>495</v>
+      </c>
+      <c r="D28" s="26" t="s">
         <v>496</v>
       </c>
-      <c r="C28" s="26" t="s">
-        <v>497</v>
-      </c>
-      <c r="D28" s="26" t="s">
-        <v>498</v>
-      </c>
       <c r="E28" s="27" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="F28" s="25" t="s">
         <v>255</v>
@@ -6698,58 +6881,64 @@
         <v>336</v>
       </c>
       <c r="Q28" s="61" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="R28" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="S28" s="53" t="str">
+        <v>464</v>
+      </c>
+      <c r="S28" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="T28" s="53" t="str">
         <f t="shared" si="2"/>
         <v>Temporais</v>
       </c>
-      <c r="T28" s="53" t="str">
+      <c r="U28" s="53" t="str">
         <f t="shared" si="2"/>
         <v>Eventos</v>
       </c>
-      <c r="U28" s="60" t="str">
+      <c r="V28" s="60" t="str">
         <f t="shared" si="2"/>
         <v>Cronometrados</v>
       </c>
-      <c r="V28" s="53" t="s">
+      <c r="W28" s="53" t="s">
         <v>179</v>
       </c>
-      <c r="W28" s="64" t="str">
+      <c r="X28" s="64" t="str">
         <f t="shared" si="3"/>
         <v>Key-CRONO-28</v>
       </c>
-      <c r="X28" s="53" t="s">
-        <v>510</v>
-      </c>
       <c r="Y28" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="Z28" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="AA28" s="53" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="29" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>520</v>
+      </c>
+      <c r="AB28" s="53" t="s">
+        <v>520</v>
+      </c>
+      <c r="AC28" s="53" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="29" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="69">
         <v>29</v>
       </c>
       <c r="B29" s="65" t="s">
+        <v>494</v>
+      </c>
+      <c r="C29" s="26" t="s">
+        <v>495</v>
+      </c>
+      <c r="D29" s="26" t="s">
         <v>496</v>
       </c>
-      <c r="C29" s="26" t="s">
-        <v>497</v>
-      </c>
-      <c r="D29" s="26" t="s">
-        <v>498</v>
-      </c>
       <c r="E29" s="27" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="F29" s="25" t="s">
         <v>61</v>
@@ -6789,58 +6978,64 @@
         <v>337</v>
       </c>
       <c r="Q29" s="61" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R29" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="S29" s="53" t="str">
-        <f t="shared" ref="S29:U44" si="21">SUBSTITUTE(C29, "_", " ")</f>
+        <v>465</v>
+      </c>
+      <c r="S29" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="T29" s="53" t="str">
+        <f t="shared" ref="T29:V44" si="21">SUBSTITUTE(C29, "_", " ")</f>
         <v>Temporais</v>
       </c>
-      <c r="T29" s="53" t="str">
+      <c r="U29" s="53" t="str">
         <f t="shared" si="21"/>
         <v>Eventos</v>
       </c>
-      <c r="U29" s="60" t="str">
+      <c r="V29" s="60" t="str">
         <f t="shared" si="21"/>
         <v>Cronometrados</v>
       </c>
-      <c r="V29" s="53" t="s">
+      <c r="W29" s="53" t="s">
         <v>179</v>
       </c>
-      <c r="W29" s="64" t="str">
+      <c r="X29" s="64" t="str">
         <f t="shared" si="3"/>
         <v>Key-CRONO-29</v>
       </c>
-      <c r="X29" s="53" t="s">
-        <v>510</v>
-      </c>
       <c r="Y29" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="Z29" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="AA29" s="53" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="30" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>520</v>
+      </c>
+      <c r="AB29" s="53" t="s">
+        <v>520</v>
+      </c>
+      <c r="AC29" s="53" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="30" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="69">
         <v>30</v>
       </c>
       <c r="B30" s="65" t="s">
+        <v>494</v>
+      </c>
+      <c r="C30" s="26" t="s">
+        <v>495</v>
+      </c>
+      <c r="D30" s="26" t="s">
         <v>496</v>
       </c>
-      <c r="C30" s="26" t="s">
+      <c r="E30" s="26" t="s">
         <v>497</v>
-      </c>
-      <c r="D30" s="26" t="s">
-        <v>498</v>
-      </c>
-      <c r="E30" s="26" t="s">
-        <v>499</v>
       </c>
       <c r="F30" s="25" t="s">
         <v>62</v>
@@ -6880,58 +7075,64 @@
         <v>338</v>
       </c>
       <c r="Q30" s="61" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="R30" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="S30" s="53" t="str">
+        <v>466</v>
+      </c>
+      <c r="S30" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="T30" s="53" t="str">
         <f t="shared" si="21"/>
         <v>Temporais</v>
       </c>
-      <c r="T30" s="53" t="str">
+      <c r="U30" s="53" t="str">
         <f t="shared" si="21"/>
         <v>Eventos</v>
       </c>
-      <c r="U30" s="60" t="str">
+      <c r="V30" s="60" t="str">
         <f t="shared" si="21"/>
         <v>Etapas</v>
       </c>
-      <c r="V30" s="53" t="s">
+      <c r="W30" s="53" t="s">
         <v>179</v>
       </c>
-      <c r="W30" s="64" t="str">
+      <c r="X30" s="64" t="str">
         <f t="shared" si="3"/>
         <v>Key-CRONO-30</v>
       </c>
-      <c r="X30" s="53" t="s">
-        <v>510</v>
-      </c>
       <c r="Y30" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="Z30" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="AA30" s="53" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="31" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>520</v>
+      </c>
+      <c r="AB30" s="53" t="s">
+        <v>520</v>
+      </c>
+      <c r="AC30" s="53" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="31" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="69">
         <v>31</v>
       </c>
       <c r="B31" s="65" t="s">
+        <v>494</v>
+      </c>
+      <c r="C31" s="26" t="s">
+        <v>495</v>
+      </c>
+      <c r="D31" s="26" t="s">
         <v>496</v>
       </c>
-      <c r="C31" s="26" t="s">
+      <c r="E31" s="26" t="s">
         <v>497</v>
-      </c>
-      <c r="D31" s="26" t="s">
-        <v>498</v>
-      </c>
-      <c r="E31" s="26" t="s">
-        <v>499</v>
       </c>
       <c r="F31" s="25" t="s">
         <v>67</v>
@@ -6971,58 +7172,64 @@
         <v>339</v>
       </c>
       <c r="Q31" s="61" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="R31" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="S31" s="53" t="str">
+        <v>467</v>
+      </c>
+      <c r="S31" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="T31" s="53" t="str">
         <f t="shared" si="21"/>
         <v>Temporais</v>
       </c>
-      <c r="T31" s="53" t="str">
+      <c r="U31" s="53" t="str">
         <f t="shared" si="21"/>
         <v>Eventos</v>
       </c>
-      <c r="U31" s="60" t="str">
+      <c r="V31" s="60" t="str">
         <f t="shared" si="21"/>
         <v>Etapas</v>
       </c>
-      <c r="V31" s="53" t="s">
+      <c r="W31" s="53" t="s">
         <v>179</v>
       </c>
-      <c r="W31" s="64" t="str">
+      <c r="X31" s="64" t="str">
         <f t="shared" si="3"/>
         <v>Key-CRONO-31</v>
       </c>
-      <c r="X31" s="53" t="s">
-        <v>510</v>
-      </c>
       <c r="Y31" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="Z31" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="AA31" s="53" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="32" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>520</v>
+      </c>
+      <c r="AB31" s="53" t="s">
+        <v>520</v>
+      </c>
+      <c r="AC31" s="53" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="32" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="69">
         <v>32</v>
       </c>
       <c r="B32" s="65" t="s">
+        <v>494</v>
+      </c>
+      <c r="C32" s="26" t="s">
+        <v>495</v>
+      </c>
+      <c r="D32" s="26" t="s">
         <v>496</v>
       </c>
-      <c r="C32" s="26" t="s">
+      <c r="E32" s="26" t="s">
         <v>497</v>
-      </c>
-      <c r="D32" s="26" t="s">
-        <v>498</v>
-      </c>
-      <c r="E32" s="26" t="s">
-        <v>499</v>
       </c>
       <c r="F32" s="26" t="s">
         <v>63</v>
@@ -7062,58 +7269,64 @@
         <v>340</v>
       </c>
       <c r="Q32" s="61" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="R32" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="S32" s="53" t="str">
+        <v>468</v>
+      </c>
+      <c r="S32" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="T32" s="53" t="str">
         <f t="shared" si="21"/>
         <v>Temporais</v>
       </c>
-      <c r="T32" s="53" t="str">
+      <c r="U32" s="53" t="str">
         <f t="shared" si="21"/>
         <v>Eventos</v>
       </c>
-      <c r="U32" s="60" t="str">
+      <c r="V32" s="60" t="str">
         <f t="shared" si="21"/>
         <v>Etapas</v>
       </c>
-      <c r="V32" s="53" t="s">
+      <c r="W32" s="53" t="s">
         <v>179</v>
       </c>
-      <c r="W32" s="64" t="str">
+      <c r="X32" s="64" t="str">
         <f t="shared" si="3"/>
         <v>Key-CRONO-32</v>
       </c>
-      <c r="X32" s="53" t="s">
-        <v>510</v>
-      </c>
       <c r="Y32" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="Z32" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="AA32" s="53" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="33" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>520</v>
+      </c>
+      <c r="AB32" s="53" t="s">
+        <v>520</v>
+      </c>
+      <c r="AC32" s="53" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="33" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="69">
         <v>33</v>
       </c>
       <c r="B33" s="65" t="s">
+        <v>494</v>
+      </c>
+      <c r="C33" s="26" t="s">
+        <v>495</v>
+      </c>
+      <c r="D33" s="26" t="s">
         <v>496</v>
       </c>
-      <c r="C33" s="26" t="s">
+      <c r="E33" s="26" t="s">
         <v>497</v>
-      </c>
-      <c r="D33" s="26" t="s">
-        <v>498</v>
-      </c>
-      <c r="E33" s="26" t="s">
-        <v>499</v>
       </c>
       <c r="F33" s="26" t="s">
         <v>64</v>
@@ -7153,58 +7366,64 @@
         <v>341</v>
       </c>
       <c r="Q33" s="61" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="R33" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="S33" s="53" t="str">
+        <v>469</v>
+      </c>
+      <c r="S33" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="T33" s="53" t="str">
         <f t="shared" si="21"/>
         <v>Temporais</v>
       </c>
-      <c r="T33" s="53" t="str">
+      <c r="U33" s="53" t="str">
         <f t="shared" si="21"/>
         <v>Eventos</v>
       </c>
-      <c r="U33" s="60" t="str">
+      <c r="V33" s="60" t="str">
         <f t="shared" si="21"/>
         <v>Etapas</v>
       </c>
-      <c r="V33" s="53" t="s">
+      <c r="W33" s="53" t="s">
         <v>179</v>
       </c>
-      <c r="W33" s="64" t="str">
+      <c r="X33" s="64" t="str">
         <f t="shared" si="3"/>
         <v>Key-CRONO-33</v>
       </c>
-      <c r="X33" s="53" t="s">
-        <v>510</v>
-      </c>
       <c r="Y33" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="Z33" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="AA33" s="53" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="34" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>520</v>
+      </c>
+      <c r="AB33" s="53" t="s">
+        <v>520</v>
+      </c>
+      <c r="AC33" s="53" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="34" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="69">
         <v>34</v>
       </c>
       <c r="B34" s="65" t="s">
+        <v>494</v>
+      </c>
+      <c r="C34" s="26" t="s">
+        <v>495</v>
+      </c>
+      <c r="D34" s="26" t="s">
         <v>496</v>
       </c>
-      <c r="C34" s="26" t="s">
+      <c r="E34" s="26" t="s">
         <v>497</v>
-      </c>
-      <c r="D34" s="26" t="s">
-        <v>498</v>
-      </c>
-      <c r="E34" s="26" t="s">
-        <v>499</v>
       </c>
       <c r="F34" s="26" t="s">
         <v>66</v>
@@ -7244,58 +7463,64 @@
         <v>342</v>
       </c>
       <c r="Q34" s="61" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="R34" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="S34" s="53" t="str">
+        <v>470</v>
+      </c>
+      <c r="S34" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="T34" s="53" t="str">
         <f t="shared" si="21"/>
         <v>Temporais</v>
       </c>
-      <c r="T34" s="53" t="str">
+      <c r="U34" s="53" t="str">
         <f t="shared" si="21"/>
         <v>Eventos</v>
       </c>
-      <c r="U34" s="60" t="str">
+      <c r="V34" s="60" t="str">
         <f t="shared" si="21"/>
         <v>Etapas</v>
       </c>
-      <c r="V34" s="53" t="s">
+      <c r="W34" s="53" t="s">
         <v>179</v>
       </c>
-      <c r="W34" s="64" t="str">
+      <c r="X34" s="64" t="str">
         <f t="shared" si="3"/>
         <v>Key-CRONO-34</v>
       </c>
-      <c r="X34" s="53" t="s">
-        <v>510</v>
-      </c>
       <c r="Y34" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="Z34" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="AA34" s="53" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="35" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>520</v>
+      </c>
+      <c r="AB34" s="53" t="s">
+        <v>520</v>
+      </c>
+      <c r="AC34" s="53" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="35" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="69">
         <v>35</v>
       </c>
       <c r="B35" s="65" t="s">
+        <v>494</v>
+      </c>
+      <c r="C35" s="26" t="s">
+        <v>495</v>
+      </c>
+      <c r="D35" s="26" t="s">
         <v>496</v>
       </c>
-      <c r="C35" s="26" t="s">
+      <c r="E35" s="26" t="s">
         <v>497</v>
-      </c>
-      <c r="D35" s="26" t="s">
-        <v>498</v>
-      </c>
-      <c r="E35" s="26" t="s">
-        <v>499</v>
       </c>
       <c r="F35" s="20" t="s">
         <v>65</v>
@@ -7335,58 +7560,64 @@
         <v>343</v>
       </c>
       <c r="Q35" s="61" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="R35" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="S35" s="53" t="str">
+        <v>441</v>
+      </c>
+      <c r="S35" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="T35" s="53" t="str">
         <f t="shared" si="21"/>
         <v>Temporais</v>
       </c>
-      <c r="T35" s="53" t="str">
+      <c r="U35" s="53" t="str">
         <f t="shared" si="21"/>
         <v>Eventos</v>
       </c>
-      <c r="U35" s="60" t="str">
+      <c r="V35" s="60" t="str">
         <f t="shared" si="21"/>
         <v>Etapas</v>
       </c>
-      <c r="V35" s="53" t="s">
+      <c r="W35" s="53" t="s">
         <v>179</v>
       </c>
-      <c r="W35" s="64" t="str">
+      <c r="X35" s="64" t="str">
         <f t="shared" si="3"/>
         <v>Key-CRONO-35</v>
       </c>
-      <c r="X35" s="53" t="s">
-        <v>510</v>
-      </c>
       <c r="Y35" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="Z35" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="AA35" s="53" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="36" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>520</v>
+      </c>
+      <c r="AB35" s="53" t="s">
+        <v>520</v>
+      </c>
+      <c r="AC35" s="53" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="36" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="69">
         <v>36</v>
       </c>
       <c r="B36" s="65" t="s">
+        <v>494</v>
+      </c>
+      <c r="C36" s="26" t="s">
+        <v>495</v>
+      </c>
+      <c r="D36" s="26" t="s">
         <v>496</v>
       </c>
-      <c r="C36" s="26" t="s">
-        <v>497</v>
-      </c>
-      <c r="D36" s="26" t="s">
-        <v>498</v>
-      </c>
       <c r="E36" s="21" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="F36" s="20" t="s">
         <v>253</v>
@@ -7426,58 +7657,64 @@
         <v>344</v>
       </c>
       <c r="Q36" s="61" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="R36" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="S36" s="53" t="str">
+        <v>471</v>
+      </c>
+      <c r="S36" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="T36" s="53" t="str">
         <f t="shared" si="21"/>
         <v>Temporais</v>
       </c>
-      <c r="T36" s="53" t="str">
+      <c r="U36" s="53" t="str">
         <f t="shared" si="21"/>
         <v>Eventos</v>
       </c>
-      <c r="U36" s="60" t="str">
+      <c r="V36" s="60" t="str">
         <f t="shared" si="21"/>
         <v>Históricos</v>
       </c>
-      <c r="V36" s="53" t="s">
+      <c r="W36" s="53" t="s">
         <v>179</v>
       </c>
-      <c r="W36" s="64" t="str">
+      <c r="X36" s="64" t="str">
         <f t="shared" si="3"/>
         <v>Key-CRONO-36</v>
       </c>
-      <c r="X36" s="53" t="s">
-        <v>510</v>
-      </c>
       <c r="Y36" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="Z36" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="AA36" s="53" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="37" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>520</v>
+      </c>
+      <c r="AB36" s="53" t="s">
+        <v>520</v>
+      </c>
+      <c r="AC36" s="53" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="37" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="69">
         <v>37</v>
       </c>
       <c r="B37" s="65" t="s">
+        <v>494</v>
+      </c>
+      <c r="C37" s="26" t="s">
+        <v>495</v>
+      </c>
+      <c r="D37" s="26" t="s">
         <v>496</v>
       </c>
-      <c r="C37" s="26" t="s">
-        <v>497</v>
-      </c>
-      <c r="D37" s="26" t="s">
-        <v>498</v>
-      </c>
       <c r="E37" s="21" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="F37" s="20" t="s">
         <v>258</v>
@@ -7517,58 +7754,64 @@
         <v>345</v>
       </c>
       <c r="Q37" s="61" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="R37" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="S37" s="53" t="str">
+        <v>472</v>
+      </c>
+      <c r="S37" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="T37" s="53" t="str">
         <f t="shared" si="21"/>
         <v>Temporais</v>
       </c>
-      <c r="T37" s="53" t="str">
+      <c r="U37" s="53" t="str">
         <f t="shared" si="21"/>
         <v>Eventos</v>
       </c>
-      <c r="U37" s="60" t="str">
+      <c r="V37" s="60" t="str">
         <f t="shared" si="21"/>
         <v>Históricos</v>
       </c>
-      <c r="V37" s="53" t="s">
+      <c r="W37" s="53" t="s">
         <v>179</v>
       </c>
-      <c r="W37" s="64" t="str">
+      <c r="X37" s="64" t="str">
         <f t="shared" si="3"/>
         <v>Key-CRONO-37</v>
       </c>
-      <c r="X37" s="53" t="s">
-        <v>510</v>
-      </c>
       <c r="Y37" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="Z37" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="AA37" s="53" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="38" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>520</v>
+      </c>
+      <c r="AB37" s="53" t="s">
+        <v>520</v>
+      </c>
+      <c r="AC37" s="53" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="38" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="69">
         <v>38</v>
       </c>
       <c r="B38" s="65" t="s">
+        <v>494</v>
+      </c>
+      <c r="C38" s="26" t="s">
+        <v>495</v>
+      </c>
+      <c r="D38" s="26" t="s">
         <v>496</v>
       </c>
-      <c r="C38" s="26" t="s">
-        <v>497</v>
-      </c>
-      <c r="D38" s="26" t="s">
-        <v>498</v>
-      </c>
       <c r="E38" s="21" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="F38" s="20" t="s">
         <v>257</v>
@@ -7608,58 +7851,64 @@
         <v>346</v>
       </c>
       <c r="Q38" s="61" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="R38" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="S38" s="53" t="str">
+        <v>473</v>
+      </c>
+      <c r="S38" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="T38" s="53" t="str">
         <f t="shared" si="21"/>
         <v>Temporais</v>
       </c>
-      <c r="T38" s="53" t="str">
+      <c r="U38" s="53" t="str">
         <f t="shared" si="21"/>
         <v>Eventos</v>
       </c>
-      <c r="U38" s="60" t="str">
+      <c r="V38" s="60" t="str">
         <f t="shared" si="21"/>
         <v>Históricos</v>
       </c>
-      <c r="V38" s="53" t="s">
+      <c r="W38" s="53" t="s">
         <v>179</v>
       </c>
-      <c r="W38" s="64" t="str">
+      <c r="X38" s="64" t="str">
         <f t="shared" si="3"/>
         <v>Key-CRONO-38</v>
       </c>
-      <c r="X38" s="53" t="s">
-        <v>510</v>
-      </c>
       <c r="Y38" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="Z38" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="AA38" s="53" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="39" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>520</v>
+      </c>
+      <c r="AB38" s="53" t="s">
+        <v>520</v>
+      </c>
+      <c r="AC38" s="53" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="39" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="69">
         <v>39</v>
       </c>
       <c r="B39" s="65" t="s">
+        <v>494</v>
+      </c>
+      <c r="C39" s="26" t="s">
+        <v>495</v>
+      </c>
+      <c r="D39" s="26" t="s">
         <v>496</v>
       </c>
-      <c r="C39" s="26" t="s">
-        <v>497</v>
-      </c>
-      <c r="D39" s="26" t="s">
-        <v>498</v>
-      </c>
       <c r="E39" s="21" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="F39" s="20" t="s">
         <v>103</v>
@@ -7699,58 +7948,64 @@
         <v>347</v>
       </c>
       <c r="Q39" s="61" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="R39" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="S39" s="53" t="str">
+        <v>474</v>
+      </c>
+      <c r="S39" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="T39" s="53" t="str">
         <f t="shared" si="21"/>
         <v>Temporais</v>
       </c>
-      <c r="T39" s="53" t="str">
+      <c r="U39" s="53" t="str">
         <f t="shared" si="21"/>
         <v>Eventos</v>
       </c>
-      <c r="U39" s="60" t="str">
+      <c r="V39" s="60" t="str">
         <f t="shared" si="21"/>
         <v>Históricos</v>
       </c>
-      <c r="V39" s="53" t="s">
+      <c r="W39" s="53" t="s">
         <v>179</v>
       </c>
-      <c r="W39" s="64" t="str">
+      <c r="X39" s="64" t="str">
         <f t="shared" si="3"/>
         <v>Key-CRONO-39</v>
       </c>
-      <c r="X39" s="53" t="s">
-        <v>510</v>
-      </c>
       <c r="Y39" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="Z39" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="AA39" s="53" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="40" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>520</v>
+      </c>
+      <c r="AB39" s="53" t="s">
+        <v>520</v>
+      </c>
+      <c r="AC39" s="53" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="40" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="69">
         <v>40</v>
       </c>
       <c r="B40" s="65" t="s">
+        <v>494</v>
+      </c>
+      <c r="C40" s="26" t="s">
+        <v>495</v>
+      </c>
+      <c r="D40" s="26" t="s">
         <v>496</v>
       </c>
-      <c r="C40" s="26" t="s">
-        <v>497</v>
-      </c>
-      <c r="D40" s="26" t="s">
-        <v>498</v>
-      </c>
       <c r="E40" s="21" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="F40" s="50" t="s">
         <v>256</v>
@@ -7790,58 +8045,64 @@
         <v>348</v>
       </c>
       <c r="Q40" s="61" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="R40" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="S40" s="53" t="str">
+        <v>475</v>
+      </c>
+      <c r="S40" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="T40" s="53" t="str">
         <f t="shared" si="21"/>
         <v>Temporais</v>
       </c>
-      <c r="T40" s="53" t="str">
+      <c r="U40" s="53" t="str">
         <f t="shared" si="21"/>
         <v>Eventos</v>
       </c>
-      <c r="U40" s="60" t="str">
+      <c r="V40" s="60" t="str">
         <f t="shared" si="21"/>
         <v>Históricos</v>
       </c>
-      <c r="V40" s="53" t="s">
+      <c r="W40" s="53" t="s">
         <v>179</v>
       </c>
-      <c r="W40" s="64" t="str">
+      <c r="X40" s="64" t="str">
         <f t="shared" si="3"/>
         <v>Key-CRONO-40</v>
       </c>
-      <c r="X40" s="53" t="s">
-        <v>510</v>
-      </c>
       <c r="Y40" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="Z40" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="AA40" s="53" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="41" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>520</v>
+      </c>
+      <c r="AB40" s="53" t="s">
+        <v>520</v>
+      </c>
+      <c r="AC40" s="53" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="41" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="69">
         <v>41</v>
       </c>
       <c r="B41" s="65" t="s">
+        <v>494</v>
+      </c>
+      <c r="C41" s="26" t="s">
+        <v>495</v>
+      </c>
+      <c r="D41" s="26" t="s">
         <v>496</v>
       </c>
-      <c r="C41" s="26" t="s">
-        <v>497</v>
-      </c>
-      <c r="D41" s="26" t="s">
-        <v>498</v>
-      </c>
       <c r="E41" s="21" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="F41" s="50" t="s">
         <v>252</v>
@@ -7881,58 +8142,64 @@
         <v>349</v>
       </c>
       <c r="Q41" s="61" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="R41" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="S41" s="53" t="str">
+        <v>476</v>
+      </c>
+      <c r="S41" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="T41" s="53" t="str">
         <f t="shared" si="21"/>
         <v>Temporais</v>
       </c>
-      <c r="T41" s="53" t="str">
+      <c r="U41" s="53" t="str">
         <f t="shared" si="21"/>
         <v>Eventos</v>
       </c>
-      <c r="U41" s="60" t="str">
+      <c r="V41" s="60" t="str">
         <f t="shared" si="21"/>
         <v>Históricos</v>
       </c>
-      <c r="V41" s="53" t="s">
+      <c r="W41" s="53" t="s">
         <v>179</v>
       </c>
-      <c r="W41" s="64" t="str">
+      <c r="X41" s="64" t="str">
         <f t="shared" si="3"/>
         <v>Key-CRONO-41</v>
       </c>
-      <c r="X41" s="53" t="s">
-        <v>510</v>
-      </c>
       <c r="Y41" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="Z41" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="AA41" s="53" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="42" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>520</v>
+      </c>
+      <c r="AB41" s="53" t="s">
+        <v>520</v>
+      </c>
+      <c r="AC41" s="53" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="42" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="69">
         <v>42</v>
       </c>
       <c r="B42" s="65" t="s">
+        <v>494</v>
+      </c>
+      <c r="C42" s="26" t="s">
+        <v>495</v>
+      </c>
+      <c r="D42" s="26" t="s">
         <v>496</v>
       </c>
-      <c r="C42" s="26" t="s">
-        <v>497</v>
-      </c>
-      <c r="D42" s="26" t="s">
+      <c r="E42" s="21" t="s">
         <v>498</v>
-      </c>
-      <c r="E42" s="21" t="s">
-        <v>500</v>
       </c>
       <c r="F42" s="50" t="s">
         <v>319</v>
@@ -7972,58 +8239,64 @@
         <v>350</v>
       </c>
       <c r="Q42" s="61" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="R42" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="S42" s="53" t="str">
+        <v>477</v>
+      </c>
+      <c r="S42" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="T42" s="53" t="str">
         <f t="shared" si="21"/>
         <v>Temporais</v>
       </c>
-      <c r="T42" s="53" t="str">
+      <c r="U42" s="53" t="str">
         <f t="shared" si="21"/>
         <v>Eventos</v>
       </c>
-      <c r="U42" s="60" t="str">
+      <c r="V42" s="60" t="str">
         <f t="shared" si="21"/>
         <v>Agendados</v>
       </c>
-      <c r="V42" s="53" t="s">
+      <c r="W42" s="53" t="s">
         <v>179</v>
       </c>
-      <c r="W42" s="64" t="str">
+      <c r="X42" s="64" t="str">
         <f t="shared" si="3"/>
         <v>Key-CRONO-42</v>
       </c>
-      <c r="X42" s="53" t="s">
-        <v>510</v>
-      </c>
       <c r="Y42" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="Z42" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="AA42" s="53" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="43" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>520</v>
+      </c>
+      <c r="AB42" s="53" t="s">
+        <v>520</v>
+      </c>
+      <c r="AC42" s="53" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="43" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="69">
         <v>43</v>
       </c>
       <c r="B43" s="65" t="s">
+        <v>494</v>
+      </c>
+      <c r="C43" s="26" t="s">
+        <v>495</v>
+      </c>
+      <c r="D43" s="26" t="s">
         <v>496</v>
       </c>
-      <c r="C43" s="26" t="s">
-        <v>497</v>
-      </c>
-      <c r="D43" s="26" t="s">
+      <c r="E43" s="21" t="s">
         <v>498</v>
-      </c>
-      <c r="E43" s="21" t="s">
-        <v>500</v>
       </c>
       <c r="F43" s="50" t="s">
         <v>318</v>
@@ -8063,58 +8336,64 @@
         <v>351</v>
       </c>
       <c r="Q43" s="61" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="R43" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="S43" s="53" t="str">
+        <v>478</v>
+      </c>
+      <c r="S43" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="T43" s="53" t="str">
         <f t="shared" si="21"/>
         <v>Temporais</v>
       </c>
-      <c r="T43" s="53" t="str">
+      <c r="U43" s="53" t="str">
         <f t="shared" si="21"/>
         <v>Eventos</v>
       </c>
-      <c r="U43" s="60" t="str">
+      <c r="V43" s="60" t="str">
         <f t="shared" si="21"/>
         <v>Agendados</v>
       </c>
-      <c r="V43" s="53" t="s">
+      <c r="W43" s="53" t="s">
         <v>179</v>
       </c>
-      <c r="W43" s="64" t="str">
+      <c r="X43" s="64" t="str">
         <f t="shared" si="3"/>
         <v>Key-CRONO-43</v>
       </c>
-      <c r="X43" s="53" t="s">
-        <v>510</v>
-      </c>
       <c r="Y43" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="Z43" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="AA43" s="53" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="44" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>520</v>
+      </c>
+      <c r="AB43" s="53" t="s">
+        <v>520</v>
+      </c>
+      <c r="AC43" s="53" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="44" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="69">
         <v>44</v>
       </c>
       <c r="B44" s="65" t="s">
+        <v>494</v>
+      </c>
+      <c r="C44" s="26" t="s">
+        <v>495</v>
+      </c>
+      <c r="D44" s="26" t="s">
         <v>496</v>
       </c>
-      <c r="C44" s="26" t="s">
-        <v>497</v>
-      </c>
-      <c r="D44" s="26" t="s">
+      <c r="E44" s="21" t="s">
         <v>498</v>
-      </c>
-      <c r="E44" s="21" t="s">
-        <v>500</v>
       </c>
       <c r="F44" s="50" t="s">
         <v>101</v>
@@ -8154,58 +8433,64 @@
         <v>352</v>
       </c>
       <c r="Q44" s="61" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="R44" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="S44" s="53" t="str">
+        <v>442</v>
+      </c>
+      <c r="S44" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="T44" s="53" t="str">
         <f t="shared" si="21"/>
         <v>Temporais</v>
       </c>
-      <c r="T44" s="53" t="str">
+      <c r="U44" s="53" t="str">
         <f t="shared" si="21"/>
         <v>Eventos</v>
       </c>
-      <c r="U44" s="60" t="str">
+      <c r="V44" s="60" t="str">
         <f t="shared" si="21"/>
         <v>Agendados</v>
       </c>
-      <c r="V44" s="53" t="s">
+      <c r="W44" s="53" t="s">
         <v>179</v>
       </c>
-      <c r="W44" s="64" t="str">
+      <c r="X44" s="64" t="str">
         <f t="shared" si="3"/>
         <v>Key-CRONO-44</v>
       </c>
-      <c r="X44" s="53" t="s">
-        <v>510</v>
-      </c>
       <c r="Y44" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="Z44" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="AA44" s="53" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="45" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>520</v>
+      </c>
+      <c r="AB44" s="53" t="s">
+        <v>520</v>
+      </c>
+      <c r="AC44" s="53" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="45" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="69">
         <v>45</v>
       </c>
       <c r="B45" s="65" t="s">
+        <v>494</v>
+      </c>
+      <c r="C45" s="21" t="s">
+        <v>495</v>
+      </c>
+      <c r="D45" s="21" t="s">
         <v>496</v>
       </c>
-      <c r="C45" s="21" t="s">
-        <v>497</v>
-      </c>
-      <c r="D45" s="21" t="s">
+      <c r="E45" s="21" t="s">
         <v>498</v>
-      </c>
-      <c r="E45" s="21" t="s">
-        <v>500</v>
       </c>
       <c r="F45" s="50" t="s">
         <v>320</v>
@@ -8245,61 +8530,67 @@
         <v>353</v>
       </c>
       <c r="Q45" s="61" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="R45" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="S45" s="53" t="str">
-        <f t="shared" ref="S45:U45" si="23">SUBSTITUTE(C45, "_", " ")</f>
+        <v>479</v>
+      </c>
+      <c r="S45" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="T45" s="53" t="str">
+        <f t="shared" ref="T45:V45" si="23">SUBSTITUTE(C45, "_", " ")</f>
         <v>Temporais</v>
       </c>
-      <c r="T45" s="53" t="str">
+      <c r="U45" s="53" t="str">
         <f t="shared" si="23"/>
         <v>Eventos</v>
       </c>
-      <c r="U45" s="60" t="str">
+      <c r="V45" s="60" t="str">
         <f t="shared" si="23"/>
         <v>Agendados</v>
       </c>
-      <c r="V45" s="53" t="s">
+      <c r="W45" s="53" t="s">
         <v>179</v>
       </c>
-      <c r="W45" s="64" t="str">
+      <c r="X45" s="64" t="str">
         <f t="shared" si="3"/>
         <v>Key-CRONO-45</v>
       </c>
-      <c r="X45" s="53" t="s">
-        <v>510</v>
-      </c>
       <c r="Y45" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="Z45" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="AA45" s="53" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="46" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>520</v>
+      </c>
+      <c r="AB45" s="53" t="s">
+        <v>520</v>
+      </c>
+      <c r="AC45" s="53" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="46" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="69">
         <v>46</v>
       </c>
       <c r="B46" s="65" t="s">
+        <v>508</v>
+      </c>
+      <c r="C46" s="21" t="s">
+        <v>512</v>
+      </c>
+      <c r="D46" s="21" t="s">
         <v>511</v>
       </c>
-      <c r="C46" s="21" t="s">
-        <v>515</v>
-      </c>
-      <c r="D46" s="21" t="s">
-        <v>514</v>
-      </c>
       <c r="E46" s="21" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="F46" s="50" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="G46" s="66" t="s">
         <v>1</v>
@@ -8333,76 +8624,89 @@
         <v>Evento.Projetual</v>
       </c>
       <c r="P46" s="62" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="Q46" s="61" t="str">
         <f>_xlfn.TRANSLATE(P46,"pt","es")</f>
         <v>Evento relacionado con el proyecto que ocurrió.</v>
       </c>
-      <c r="R46" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="S46" s="53" t="str">
-        <f t="shared" ref="S46" si="28">SUBSTITUTE(C46, "_", " ")</f>
+      <c r="R46" s="61" t="s">
+        <v>515</v>
+      </c>
+      <c r="S46" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="T46" s="53" t="str">
+        <f t="shared" ref="T46" si="28">SUBSTITUTE(C46, "_", " ")</f>
         <v>Cronológico</v>
       </c>
-      <c r="T46" s="53" t="str">
-        <f t="shared" ref="T46" si="29">SUBSTITUTE(D46, "_", " ")</f>
+      <c r="U46" s="53" t="str">
+        <f t="shared" ref="U46" si="29">SUBSTITUTE(D46, "_", " ")</f>
         <v>Cronologias</v>
       </c>
-      <c r="U46" s="60" t="str">
-        <f t="shared" ref="U46" si="30">SUBSTITUTE(E46, "_", " ")</f>
+      <c r="V46" s="60" t="str">
+        <f t="shared" ref="V46" si="30">SUBSTITUTE(E46, "_", " ")</f>
         <v>Cronologia</v>
       </c>
-      <c r="V46" s="53" t="s">
+      <c r="W46" s="53" t="s">
         <v>179</v>
       </c>
-      <c r="W46" s="64" t="str">
-        <f t="shared" ref="W46" si="31">CONCATENATE("Key-CRONO-",A46)</f>
+      <c r="X46" s="64" t="str">
+        <f t="shared" ref="X46" si="31">CONCATENATE("Key-CRONO-",A46)</f>
         <v>Key-CRONO-46</v>
       </c>
-      <c r="X46" s="53" t="s">
-        <v>510</v>
-      </c>
       <c r="Y46" s="53" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="Z46" s="53" t="s">
-        <v>510</v>
-      </c>
-      <c r="AA46" s="61" t="str">
-        <f>_xlfn.TRANSLATE(P46,"pt","en")</f>
-        <v>Event related to the project that happened.</v>
+        <v>520</v>
+      </c>
+      <c r="AA46" s="53" t="s">
+        <v>520</v>
+      </c>
+      <c r="AB46" s="53" t="s">
+        <v>520</v>
+      </c>
+      <c r="AC46" s="53" t="s">
+        <v>520</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="V2:V46 AA1:AA45 A2:B46">
-    <cfRule type="cellIs" dxfId="0" priority="6" operator="equal">
+  <conditionalFormatting sqref="F1:F39">
+    <cfRule type="duplicateValues" dxfId="16" priority="25"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F1:F46">
+    <cfRule type="duplicateValues" dxfId="15" priority="24"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:B46 W2:W46">
+    <cfRule type="cellIs" dxfId="14" priority="7" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F39">
-    <cfRule type="duplicateValues" dxfId="15" priority="24"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F46">
-    <cfRule type="duplicateValues" dxfId="14" priority="23"/>
+  <conditionalFormatting sqref="R1:R45">
+    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{402BD1C2-A59C-4020-8FC9-E5402FE7B33F}">
   <dimension ref="A1:U3"/>
-  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="10" width="5.85546875" style="2" customWidth="1"/>
-    <col min="11" max="21" width="5.85546875" style="5" customWidth="1"/>
-    <col min="22" max="16384" width="11.140625" style="5"/>
+    <col min="1" max="1" width="2.84375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="10" width="5.84375" style="2" customWidth="1"/>
+    <col min="11" max="21" width="5.84375" style="5" customWidth="1"/>
+    <col min="22" max="16384" width="11.15234375" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="3" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" s="3" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="44" t="s">
         <v>22</v>
       </c>
@@ -8467,7 +8771,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="44">
         <v>2</v>
       </c>
@@ -8532,7 +8836,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="44">
         <v>3</v>
       </c>
@@ -8600,7 +8904,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8612,14 +8916,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C7BFE13-E93E-488C-9C8F-4E4982DFBAE7}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.28515625" customWidth="1"/>
-    <col min="2" max="2" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.3046875" customWidth="1"/>
+    <col min="2" max="2" width="6.69140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="42">
         <v>1</v>
       </c>
@@ -8630,7 +8934,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="19">
         <v>2</v>
       </c>
@@ -8641,7 +8945,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="19">
         <v>3</v>
       </c>
@@ -8652,7 +8956,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" s="19">
         <v>4</v>
       </c>
@@ -8660,12 +8964,12 @@
         <v>315</v>
       </c>
       <c r="C4" s="48" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A4">
-    <cfRule type="cellIs" dxfId="12" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8676,36 +8980,36 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5087910E-DA31-4318-A539-726BE963325D}">
   <dimension ref="A1:Y84"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="7.35" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="7.4" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="3.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="3.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="3.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="3.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="49" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.42578125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="3.42578125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="4.28515625" style="59" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.85546875" style="59" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="5.28515625" style="59" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11.42578125" style="59" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.23046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.53515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.53515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="2.23046875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.53515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.53515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="2.3828125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="1.921875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="35.15234375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="2.61328125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.3046875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="2.3828125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="1.921875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="2.3828125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="1.921875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="2.3828125" style="59" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6.3046875" style="59" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="3.61328125" style="59" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="7.84375" style="59" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="40" t="s">
         <v>182</v>
       </c>
@@ -8782,7 +9086,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="31">
         <v>2</v>
       </c>
@@ -8847,24 +9151,24 @@
         <v>1</v>
       </c>
       <c r="V2" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W2" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X2" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W2" s="35" t="s">
-        <v>374</v>
-      </c>
-      <c r="X2" s="30" t="s">
-        <v>375</v>
-      </c>
       <c r="Y2" s="35" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="3" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="31">
         <v>3</v>
       </c>
       <c r="B3" s="49" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C3" s="25" t="s">
         <v>51</v>
@@ -8903,7 +9207,7 @@
         <v>72</v>
       </c>
       <c r="O3" s="35" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="P3" s="30" t="s">
         <v>1</v>
@@ -8924,19 +9228,19 @@
         <v>1</v>
       </c>
       <c r="V3" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W3" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X3" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W3" s="35" t="s">
-        <v>374</v>
-      </c>
-      <c r="X3" s="30" t="s">
-        <v>375</v>
-      </c>
       <c r="Y3" s="35" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="4" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="31">
         <v>4</v>
       </c>
@@ -9001,24 +9305,24 @@
         <v>1</v>
       </c>
       <c r="V4" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W4" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X4" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W4" s="35" t="s">
-        <v>374</v>
-      </c>
-      <c r="X4" s="30" t="s">
-        <v>375</v>
-      </c>
       <c r="Y4" s="35" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="5" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="31">
         <v>5</v>
       </c>
       <c r="B5" s="49" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C5" s="25" t="s">
         <v>51</v>
@@ -9027,7 +9331,7 @@
         <v>249</v>
       </c>
       <c r="E5" s="34" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="F5" s="29" t="s">
         <v>1</v>
@@ -9057,40 +9361,40 @@
         <v>72</v>
       </c>
       <c r="O5" s="35" t="s">
+        <v>369</v>
+      </c>
+      <c r="P5" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="R5" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="S5" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="T5" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="U5" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="V5" s="30" t="s">
         <v>371</v>
       </c>
-      <c r="P5" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="R5" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="S5" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="T5" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="U5" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="V5" s="30" t="s">
+      <c r="W5" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X5" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W5" s="35" t="s">
-        <v>374</v>
-      </c>
-      <c r="X5" s="30" t="s">
-        <v>375</v>
-      </c>
       <c r="Y5" s="35" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="6" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="31">
         <v>6</v>
       </c>
@@ -9098,7 +9402,7 @@
         <v>282</v>
       </c>
       <c r="C6" s="26" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="D6" s="29" t="s">
         <v>260</v>
@@ -9155,19 +9459,19 @@
         <v>1</v>
       </c>
       <c r="V6" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W6" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X6" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W6" s="35" t="s">
-        <v>374</v>
-      </c>
-      <c r="X6" s="30" t="s">
-        <v>375</v>
-      </c>
       <c r="Y6" s="35" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="31">
         <v>7</v>
       </c>
@@ -9175,7 +9479,7 @@
         <v>283</v>
       </c>
       <c r="C7" s="26" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="D7" s="29" t="s">
         <v>260</v>
@@ -9232,19 +9536,19 @@
         <v>1</v>
       </c>
       <c r="V7" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W7" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X7" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W7" s="35" t="s">
-        <v>374</v>
-      </c>
-      <c r="X7" s="30" t="s">
-        <v>375</v>
-      </c>
       <c r="Y7" s="35" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="31">
         <v>8</v>
       </c>
@@ -9252,7 +9556,7 @@
         <v>212</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="D8" s="29" t="s">
         <v>1</v>
@@ -9309,19 +9613,19 @@
         <v>1</v>
       </c>
       <c r="V8" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W8" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X8" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W8" s="35" t="s">
-        <v>374</v>
-      </c>
-      <c r="X8" s="30" t="s">
-        <v>375</v>
-      </c>
       <c r="Y8" s="35" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="31">
         <v>9</v>
       </c>
@@ -9329,7 +9633,7 @@
         <v>211</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="D9" s="29" t="s">
         <v>1</v>
@@ -9386,19 +9690,19 @@
         <v>1</v>
       </c>
       <c r="V9" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W9" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X9" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W9" s="35" t="s">
-        <v>374</v>
-      </c>
-      <c r="X9" s="30" t="s">
-        <v>375</v>
-      </c>
       <c r="Y9" s="35" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="31">
         <v>10</v>
       </c>
@@ -9442,7 +9746,7 @@
         <v>72</v>
       </c>
       <c r="O10" s="35" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="P10" s="30" t="s">
         <v>183</v>
@@ -9463,19 +9767,19 @@
         <v>1</v>
       </c>
       <c r="V10" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W10" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X10" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W10" s="35" t="s">
-        <v>374</v>
-      </c>
-      <c r="X10" s="30" t="s">
-        <v>375</v>
-      </c>
       <c r="Y10" s="35" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="31">
         <v>11</v>
       </c>
@@ -9519,7 +9823,7 @@
         <v>72</v>
       </c>
       <c r="O11" s="35" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="P11" s="30" t="s">
         <v>183</v>
@@ -9540,19 +9844,19 @@
         <v>1</v>
       </c>
       <c r="V11" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W11" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X11" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W11" s="35" t="s">
-        <v>374</v>
-      </c>
-      <c r="X11" s="30" t="s">
-        <v>375</v>
-      </c>
       <c r="Y11" s="35" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="12" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="31">
         <v>12</v>
       </c>
@@ -9617,19 +9921,19 @@
         <v>1</v>
       </c>
       <c r="V12" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W12" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X12" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W12" s="35" t="s">
-        <v>374</v>
-      </c>
-      <c r="X12" s="30" t="s">
-        <v>375</v>
-      </c>
       <c r="Y12" s="35" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="31">
         <v>13</v>
       </c>
@@ -9694,19 +9998,19 @@
         <v>1</v>
       </c>
       <c r="V13" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W13" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X13" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W13" s="35" t="s">
-        <v>374</v>
-      </c>
-      <c r="X13" s="30" t="s">
-        <v>375</v>
-      </c>
       <c r="Y13" s="35" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="14" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="31">
         <v>14</v>
       </c>
@@ -9771,19 +10075,19 @@
         <v>1</v>
       </c>
       <c r="V14" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W14" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X14" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W14" s="35" t="s">
-        <v>374</v>
-      </c>
-      <c r="X14" s="30" t="s">
+      <c r="Y14" s="35" t="s">
         <v>375</v>
       </c>
-      <c r="Y14" s="35" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="31">
         <v>15</v>
       </c>
@@ -9848,19 +10152,19 @@
         <v>1</v>
       </c>
       <c r="V15" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W15" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X15" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W15" s="35" t="s">
-        <v>374</v>
-      </c>
-      <c r="X15" s="30" t="s">
+      <c r="Y15" s="35" t="s">
         <v>375</v>
       </c>
-      <c r="Y15" s="35" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="31">
         <v>16</v>
       </c>
@@ -9925,19 +10229,19 @@
         <v>1</v>
       </c>
       <c r="V16" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W16" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X16" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W16" s="35" t="s">
-        <v>374</v>
-      </c>
-      <c r="X16" s="30" t="s">
+      <c r="Y16" s="35" t="s">
         <v>375</v>
       </c>
-      <c r="Y16" s="35" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="17" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="31">
         <v>17</v>
       </c>
@@ -10002,19 +10306,19 @@
         <v>1</v>
       </c>
       <c r="V17" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W17" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X17" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W17" s="35" t="s">
-        <v>374</v>
-      </c>
-      <c r="X17" s="30" t="s">
+      <c r="Y17" s="35" t="s">
         <v>375</v>
       </c>
-      <c r="Y17" s="35" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="18" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="31">
         <v>18</v>
       </c>
@@ -10079,19 +10383,19 @@
         <v>1</v>
       </c>
       <c r="V18" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W18" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X18" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W18" s="35" t="s">
-        <v>374</v>
-      </c>
-      <c r="X18" s="30" t="s">
+      <c r="Y18" s="35" t="s">
         <v>375</v>
       </c>
-      <c r="Y18" s="35" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="19" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="31">
         <v>19</v>
       </c>
@@ -10156,19 +10460,19 @@
         <v>1</v>
       </c>
       <c r="V19" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W19" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X19" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W19" s="35" t="s">
-        <v>374</v>
-      </c>
-      <c r="X19" s="30" t="s">
+      <c r="Y19" s="35" t="s">
         <v>375</v>
       </c>
-      <c r="Y19" s="35" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="20" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="31">
         <v>20</v>
       </c>
@@ -10233,19 +10537,19 @@
         <v>1</v>
       </c>
       <c r="V20" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W20" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X20" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W20" s="35" t="s">
-        <v>374</v>
-      </c>
-      <c r="X20" s="30" t="s">
+      <c r="Y20" s="35" t="s">
         <v>375</v>
       </c>
-      <c r="Y20" s="35" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="21" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="31">
         <v>21</v>
       </c>
@@ -10253,7 +10557,7 @@
         <v>71</v>
       </c>
       <c r="C21" s="26" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D21" s="29" t="s">
         <v>1</v>
@@ -10310,19 +10614,19 @@
         <v>1</v>
       </c>
       <c r="V21" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W21" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X21" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W21" s="35" t="s">
-        <v>374</v>
-      </c>
-      <c r="X21" s="30" t="s">
-        <v>375</v>
-      </c>
       <c r="Y21" s="35" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="22" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="31">
         <v>22</v>
       </c>
@@ -10330,7 +10634,7 @@
         <v>91</v>
       </c>
       <c r="C22" s="26" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D22" s="29" t="s">
         <v>1</v>
@@ -10387,19 +10691,19 @@
         <v>1</v>
       </c>
       <c r="V22" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W22" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X22" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W22" s="35" t="s">
-        <v>374</v>
-      </c>
-      <c r="X22" s="30" t="s">
-        <v>375</v>
-      </c>
       <c r="Y22" s="35" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="23" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="31">
         <v>23</v>
       </c>
@@ -10407,7 +10711,7 @@
         <v>93</v>
       </c>
       <c r="C23" s="26" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D23" s="29" t="s">
         <v>248</v>
@@ -10464,19 +10768,19 @@
         <v>1</v>
       </c>
       <c r="V23" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W23" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X23" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W23" s="35" t="s">
-        <v>374</v>
-      </c>
-      <c r="X23" s="30" t="s">
-        <v>375</v>
-      </c>
       <c r="Y23" s="35" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="24" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="31">
         <v>24</v>
       </c>
@@ -10484,7 +10788,7 @@
         <v>95</v>
       </c>
       <c r="C24" s="26" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D24" s="29" t="s">
         <v>248</v>
@@ -10541,19 +10845,19 @@
         <v>1</v>
       </c>
       <c r="V24" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W24" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X24" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W24" s="35" t="s">
-        <v>374</v>
-      </c>
-      <c r="X24" s="30" t="s">
-        <v>375</v>
-      </c>
       <c r="Y24" s="35" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="25" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="31">
         <v>25</v>
       </c>
@@ -10561,7 +10865,7 @@
         <v>97</v>
       </c>
       <c r="C25" s="26" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D25" s="29" t="s">
         <v>248</v>
@@ -10618,19 +10922,19 @@
         <v>1</v>
       </c>
       <c r="V25" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W25" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X25" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W25" s="35" t="s">
-        <v>374</v>
-      </c>
-      <c r="X25" s="30" t="s">
-        <v>375</v>
-      </c>
       <c r="Y25" s="35" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="26" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="31">
         <v>26</v>
       </c>
@@ -10638,7 +10942,7 @@
         <v>99</v>
       </c>
       <c r="C26" s="26" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D26" s="29" t="s">
         <v>248</v>
@@ -10695,19 +10999,19 @@
         <v>1</v>
       </c>
       <c r="V26" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W26" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X26" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W26" s="35" t="s">
-        <v>374</v>
-      </c>
-      <c r="X26" s="30" t="s">
-        <v>375</v>
-      </c>
       <c r="Y26" s="35" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="27" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="31">
         <v>27</v>
       </c>
@@ -10715,7 +11019,7 @@
         <v>101</v>
       </c>
       <c r="C27" s="26" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D27" s="29" t="s">
         <v>248</v>
@@ -10772,19 +11076,19 @@
         <v>1</v>
       </c>
       <c r="V27" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W27" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X27" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W27" s="35" t="s">
-        <v>374</v>
-      </c>
-      <c r="X27" s="30" t="s">
-        <v>375</v>
-      </c>
       <c r="Y27" s="35" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="28" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="31">
         <v>28</v>
       </c>
@@ -10792,7 +11096,7 @@
         <v>103</v>
       </c>
       <c r="C28" s="26" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D28" s="29" t="s">
         <v>248</v>
@@ -10849,19 +11153,19 @@
         <v>1</v>
       </c>
       <c r="V28" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W28" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X28" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W28" s="35" t="s">
-        <v>374</v>
-      </c>
-      <c r="X28" s="30" t="s">
-        <v>375</v>
-      </c>
       <c r="Y28" s="35" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="29" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="31">
         <v>29</v>
       </c>
@@ -10869,7 +11173,7 @@
         <v>121</v>
       </c>
       <c r="C29" s="26" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D29" s="29" t="s">
         <v>1</v>
@@ -10926,19 +11230,19 @@
         <v>1</v>
       </c>
       <c r="V29" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W29" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X29" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W29" s="35" t="s">
-        <v>374</v>
-      </c>
-      <c r="X29" s="30" t="s">
-        <v>375</v>
-      </c>
       <c r="Y29" s="35" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="30" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="31">
         <v>30</v>
       </c>
@@ -10946,7 +11250,7 @@
         <v>123</v>
       </c>
       <c r="C30" s="26" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D30" s="29" t="s">
         <v>1</v>
@@ -11003,19 +11307,19 @@
         <v>1</v>
       </c>
       <c r="V30" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W30" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X30" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W30" s="35" t="s">
-        <v>374</v>
-      </c>
-      <c r="X30" s="30" t="s">
-        <v>375</v>
-      </c>
       <c r="Y30" s="35" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="31" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="31">
         <v>31</v>
       </c>
@@ -11023,7 +11327,7 @@
         <v>125</v>
       </c>
       <c r="C31" s="26" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D31" s="29" t="s">
         <v>1</v>
@@ -11080,19 +11384,19 @@
         <v>1</v>
       </c>
       <c r="V31" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W31" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X31" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W31" s="35" t="s">
-        <v>374</v>
-      </c>
-      <c r="X31" s="30" t="s">
-        <v>375</v>
-      </c>
       <c r="Y31" s="35" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="32" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="31">
         <v>32</v>
       </c>
@@ -11100,7 +11404,7 @@
         <v>127</v>
       </c>
       <c r="C32" s="26" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D32" s="29" t="s">
         <v>1</v>
@@ -11157,19 +11461,19 @@
         <v>1</v>
       </c>
       <c r="V32" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W32" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X32" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W32" s="35" t="s">
-        <v>374</v>
-      </c>
-      <c r="X32" s="30" t="s">
-        <v>375</v>
-      </c>
       <c r="Y32" s="35" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="33" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="33" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="31">
         <v>33</v>
       </c>
@@ -11177,7 +11481,7 @@
         <v>129</v>
       </c>
       <c r="C33" s="26" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D33" s="29" t="s">
         <v>1</v>
@@ -11234,19 +11538,19 @@
         <v>1</v>
       </c>
       <c r="V33" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W33" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X33" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W33" s="35" t="s">
-        <v>374</v>
-      </c>
-      <c r="X33" s="30" t="s">
-        <v>375</v>
-      </c>
       <c r="Y33" s="35" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="34" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="34" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="31">
         <v>34</v>
       </c>
@@ -11254,7 +11558,7 @@
         <v>131</v>
       </c>
       <c r="C34" s="26" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D34" s="29" t="s">
         <v>1</v>
@@ -11311,19 +11615,19 @@
         <v>1</v>
       </c>
       <c r="V34" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W34" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X34" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W34" s="35" t="s">
-        <v>374</v>
-      </c>
-      <c r="X34" s="30" t="s">
-        <v>375</v>
-      </c>
       <c r="Y34" s="35" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="35" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="35" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="31">
         <v>35</v>
       </c>
@@ -11331,7 +11635,7 @@
         <v>133</v>
       </c>
       <c r="C35" s="26" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D35" s="29" t="s">
         <v>1</v>
@@ -11388,19 +11692,19 @@
         <v>1</v>
       </c>
       <c r="V35" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W35" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X35" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W35" s="35" t="s">
-        <v>374</v>
-      </c>
-      <c r="X35" s="30" t="s">
-        <v>375</v>
-      </c>
       <c r="Y35" s="35" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="36" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="31">
         <v>36</v>
       </c>
@@ -11408,7 +11712,7 @@
         <v>135</v>
       </c>
       <c r="C36" s="26" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D36" s="29" t="s">
         <v>1</v>
@@ -11465,19 +11769,19 @@
         <v>1</v>
       </c>
       <c r="V36" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W36" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X36" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W36" s="35" t="s">
-        <v>374</v>
-      </c>
-      <c r="X36" s="30" t="s">
-        <v>375</v>
-      </c>
       <c r="Y36" s="35" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="37" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="37" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="31">
         <v>37</v>
       </c>
@@ -11542,19 +11846,19 @@
         <v>1</v>
       </c>
       <c r="V37" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W37" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X37" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W37" s="35" t="s">
-        <v>374</v>
-      </c>
-      <c r="X37" s="30" t="s">
-        <v>375</v>
-      </c>
       <c r="Y37" s="35" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="38" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="38" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="31">
         <v>38</v>
       </c>
@@ -11619,19 +11923,19 @@
         <v>1</v>
       </c>
       <c r="V38" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W38" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X38" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W38" s="35" t="s">
-        <v>374</v>
-      </c>
-      <c r="X38" s="30" t="s">
-        <v>375</v>
-      </c>
       <c r="Y38" s="35" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="39" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="39" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="31">
         <v>39</v>
       </c>
@@ -11639,7 +11943,7 @@
         <v>76</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="D39" s="29" t="s">
         <v>1</v>
@@ -11696,19 +12000,19 @@
         <v>1</v>
       </c>
       <c r="V39" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W39" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X39" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W39" s="35" t="s">
-        <v>374</v>
-      </c>
-      <c r="X39" s="30" t="s">
-        <v>375</v>
-      </c>
       <c r="Y39" s="35" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="40" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="40" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="31">
         <v>40</v>
       </c>
@@ -11716,7 +12020,7 @@
         <v>79</v>
       </c>
       <c r="C40" s="21" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="D40" s="29" t="s">
         <v>1</v>
@@ -11773,19 +12077,19 @@
         <v>1</v>
       </c>
       <c r="V40" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W40" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X40" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W40" s="35" t="s">
-        <v>374</v>
-      </c>
-      <c r="X40" s="30" t="s">
-        <v>375</v>
-      </c>
       <c r="Y40" s="35" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="41" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="41" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="31">
         <v>41</v>
       </c>
@@ -11793,7 +12097,7 @@
         <v>82</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="D41" s="29" t="s">
         <v>1</v>
@@ -11850,19 +12154,19 @@
         <v>1</v>
       </c>
       <c r="V41" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W41" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X41" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W41" s="35" t="s">
-        <v>374</v>
-      </c>
-      <c r="X41" s="30" t="s">
-        <v>375</v>
-      </c>
       <c r="Y41" s="35" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="42" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="42" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="31">
         <v>42</v>
       </c>
@@ -11870,7 +12174,7 @@
         <v>84</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="D42" s="29" t="s">
         <v>1</v>
@@ -11927,19 +12231,19 @@
         <v>1</v>
       </c>
       <c r="V42" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W42" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X42" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W42" s="35" t="s">
-        <v>374</v>
-      </c>
-      <c r="X42" s="30" t="s">
-        <v>375</v>
-      </c>
       <c r="Y42" s="35" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="43" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="43" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="31">
         <v>43</v>
       </c>
@@ -12004,19 +12308,19 @@
         <v>1</v>
       </c>
       <c r="V43" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W43" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X43" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W43" s="35" t="s">
-        <v>374</v>
-      </c>
-      <c r="X43" s="30" t="s">
-        <v>375</v>
-      </c>
       <c r="Y43" s="35" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="44" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="44" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="31">
         <v>44</v>
       </c>
@@ -12081,19 +12385,19 @@
         <v>1</v>
       </c>
       <c r="V44" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W44" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X44" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W44" s="35" t="s">
-        <v>374</v>
-      </c>
-      <c r="X44" s="30" t="s">
-        <v>375</v>
-      </c>
       <c r="Y44" s="35" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="45" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="45" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="31">
         <v>45</v>
       </c>
@@ -12158,19 +12462,19 @@
         <v>1</v>
       </c>
       <c r="V45" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W45" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X45" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W45" s="35" t="s">
-        <v>374</v>
-      </c>
-      <c r="X45" s="30" t="s">
-        <v>375</v>
-      </c>
       <c r="Y45" s="35" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="46" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="46" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="31">
         <v>46</v>
       </c>
@@ -12235,19 +12539,19 @@
         <v>1</v>
       </c>
       <c r="V46" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W46" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X46" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W46" s="35" t="s">
-        <v>374</v>
-      </c>
-      <c r="X46" s="30" t="s">
-        <v>375</v>
-      </c>
       <c r="Y46" s="35" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="47" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="47" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="31">
         <v>47</v>
       </c>
@@ -12312,19 +12616,19 @@
         <v>1</v>
       </c>
       <c r="V47" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W47" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X47" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W47" s="35" t="s">
-        <v>374</v>
-      </c>
-      <c r="X47" s="30" t="s">
-        <v>375</v>
-      </c>
       <c r="Y47" s="35" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="48" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="48" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="31">
         <v>48</v>
       </c>
@@ -12389,19 +12693,19 @@
         <v>1</v>
       </c>
       <c r="V48" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W48" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X48" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W48" s="35" t="s">
-        <v>374</v>
-      </c>
-      <c r="X48" s="30" t="s">
-        <v>375</v>
-      </c>
       <c r="Y48" s="35" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="49" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="49" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="31">
         <v>49</v>
       </c>
@@ -12466,19 +12770,19 @@
         <v>1</v>
       </c>
       <c r="V49" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W49" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X49" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W49" s="35" t="s">
-        <v>374</v>
-      </c>
-      <c r="X49" s="30" t="s">
-        <v>375</v>
-      </c>
       <c r="Y49" s="35" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="50" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="50" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="31">
         <v>50</v>
       </c>
@@ -12492,7 +12796,7 @@
         <v>330</v>
       </c>
       <c r="E50" s="34" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F50" s="29" t="s">
         <v>310</v>
@@ -12543,19 +12847,19 @@
         <v>1</v>
       </c>
       <c r="V50" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W50" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X50" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W50" s="35" t="s">
+      <c r="Y50" s="35" t="s">
         <v>374</v>
       </c>
-      <c r="X50" s="30" t="s">
-        <v>375</v>
-      </c>
-      <c r="Y50" s="35" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="51" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="51" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="31">
         <v>51</v>
       </c>
@@ -12569,7 +12873,7 @@
         <v>308</v>
       </c>
       <c r="E51" s="34" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F51" s="29" t="s">
         <v>310</v>
@@ -12620,19 +12924,19 @@
         <v>1</v>
       </c>
       <c r="V51" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W51" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X51" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W51" s="35" t="s">
+      <c r="Y51" s="35" t="s">
         <v>374</v>
       </c>
-      <c r="X51" s="30" t="s">
-        <v>375</v>
-      </c>
-      <c r="Y51" s="35" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="52" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="52" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="31">
         <v>52</v>
       </c>
@@ -12646,7 +12950,7 @@
         <v>308</v>
       </c>
       <c r="E52" s="34" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F52" s="29" t="s">
         <v>310</v>
@@ -12697,19 +13001,19 @@
         <v>1</v>
       </c>
       <c r="V52" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W52" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X52" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W52" s="35" t="s">
+      <c r="Y52" s="35" t="s">
         <v>374</v>
       </c>
-      <c r="X52" s="30" t="s">
-        <v>375</v>
-      </c>
-      <c r="Y52" s="35" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="53" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="53" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" s="31">
         <v>53</v>
       </c>
@@ -12723,7 +13027,7 @@
         <v>308</v>
       </c>
       <c r="E53" s="34" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F53" s="29" t="s">
         <v>310</v>
@@ -12774,19 +13078,19 @@
         <v>1</v>
       </c>
       <c r="V53" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W53" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X53" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W53" s="35" t="s">
+      <c r="Y53" s="35" t="s">
         <v>374</v>
       </c>
-      <c r="X53" s="30" t="s">
-        <v>375</v>
-      </c>
-      <c r="Y53" s="35" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="54" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="54" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="31">
         <v>54</v>
       </c>
@@ -12800,7 +13104,7 @@
         <v>308</v>
       </c>
       <c r="E54" s="34" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F54" s="29" t="s">
         <v>310</v>
@@ -12851,19 +13155,19 @@
         <v>1</v>
       </c>
       <c r="V54" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W54" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X54" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W54" s="35" t="s">
+      <c r="Y54" s="35" t="s">
         <v>374</v>
       </c>
-      <c r="X54" s="30" t="s">
-        <v>375</v>
-      </c>
-      <c r="Y54" s="35" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="55" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="55" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" s="31">
         <v>55</v>
       </c>
@@ -12877,7 +13181,7 @@
         <v>308</v>
       </c>
       <c r="E55" s="34" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F55" s="29" t="s">
         <v>310</v>
@@ -12928,19 +13232,19 @@
         <v>1</v>
       </c>
       <c r="V55" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W55" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X55" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W55" s="35" t="s">
+      <c r="Y55" s="35" t="s">
         <v>374</v>
       </c>
-      <c r="X55" s="30" t="s">
-        <v>375</v>
-      </c>
-      <c r="Y55" s="35" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="56" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="56" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="31">
         <v>56</v>
       </c>
@@ -12954,7 +13258,7 @@
         <v>308</v>
       </c>
       <c r="E56" s="34" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F56" s="29" t="s">
         <v>310</v>
@@ -13005,19 +13309,19 @@
         <v>1</v>
       </c>
       <c r="V56" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W56" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X56" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W56" s="35" t="s">
+      <c r="Y56" s="35" t="s">
         <v>374</v>
       </c>
-      <c r="X56" s="30" t="s">
-        <v>375</v>
-      </c>
-      <c r="Y56" s="35" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="57" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="57" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" s="31">
         <v>57</v>
       </c>
@@ -13031,7 +13335,7 @@
         <v>308</v>
       </c>
       <c r="E57" s="34" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F57" s="29" t="s">
         <v>310</v>
@@ -13082,19 +13386,19 @@
         <v>1</v>
       </c>
       <c r="V57" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W57" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X57" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W57" s="35" t="s">
+      <c r="Y57" s="35" t="s">
         <v>374</v>
       </c>
-      <c r="X57" s="30" t="s">
-        <v>375</v>
-      </c>
-      <c r="Y57" s="35" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="58" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="58" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="31">
         <v>58</v>
       </c>
@@ -13108,7 +13412,7 @@
         <v>308</v>
       </c>
       <c r="E58" s="34" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F58" s="29" t="s">
         <v>310</v>
@@ -13159,19 +13463,19 @@
         <v>1</v>
       </c>
       <c r="V58" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W58" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X58" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W58" s="35" t="s">
+      <c r="Y58" s="35" t="s">
         <v>374</v>
       </c>
-      <c r="X58" s="30" t="s">
-        <v>375</v>
-      </c>
-      <c r="Y58" s="35" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="59" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="59" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="31">
         <v>59</v>
       </c>
@@ -13185,7 +13489,7 @@
         <v>308</v>
       </c>
       <c r="E59" s="34" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F59" s="29" t="s">
         <v>310</v>
@@ -13236,19 +13540,19 @@
         <v>1</v>
       </c>
       <c r="V59" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W59" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X59" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W59" s="35" t="s">
+      <c r="Y59" s="35" t="s">
         <v>374</v>
       </c>
-      <c r="X59" s="30" t="s">
-        <v>375</v>
-      </c>
-      <c r="Y59" s="35" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="60" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="60" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="31">
         <v>60</v>
       </c>
@@ -13262,7 +13566,7 @@
         <v>308</v>
       </c>
       <c r="E60" s="34" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F60" s="29" t="s">
         <v>310</v>
@@ -13313,19 +13617,19 @@
         <v>1</v>
       </c>
       <c r="V60" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W60" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X60" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W60" s="35" t="s">
+      <c r="Y60" s="35" t="s">
         <v>374</v>
       </c>
-      <c r="X60" s="30" t="s">
-        <v>375</v>
-      </c>
-      <c r="Y60" s="35" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="61" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="61" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="31">
         <v>61</v>
       </c>
@@ -13339,7 +13643,7 @@
         <v>322</v>
       </c>
       <c r="E61" s="34" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F61" s="29" t="s">
         <v>1</v>
@@ -13390,19 +13694,19 @@
         <v>1</v>
       </c>
       <c r="V61" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W61" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X61" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W61" s="35" t="s">
+      <c r="Y61" s="35" t="s">
         <v>374</v>
       </c>
-      <c r="X61" s="30" t="s">
-        <v>375</v>
-      </c>
-      <c r="Y61" s="35" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="62" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="62" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" s="31">
         <v>62</v>
       </c>
@@ -13467,19 +13771,19 @@
         <v>1</v>
       </c>
       <c r="V62" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W62" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X62" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W62" s="35" t="s">
-        <v>374</v>
-      </c>
-      <c r="X62" s="30" t="s">
-        <v>375</v>
-      </c>
       <c r="Y62" s="35" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="63" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="63" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A63" s="31">
         <v>63</v>
       </c>
@@ -13544,19 +13848,19 @@
         <v>1</v>
       </c>
       <c r="V63" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W63" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X63" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W63" s="35" t="s">
-        <v>374</v>
-      </c>
-      <c r="X63" s="30" t="s">
-        <v>375</v>
-      </c>
       <c r="Y63" s="35" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="64" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="64" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="31">
         <v>64</v>
       </c>
@@ -13621,19 +13925,19 @@
         <v>1</v>
       </c>
       <c r="V64" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W64" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X64" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W64" s="35" t="s">
-        <v>374</v>
-      </c>
-      <c r="X64" s="30" t="s">
-        <v>375</v>
-      </c>
       <c r="Y64" s="35" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="65" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="65" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="31">
         <v>65</v>
       </c>
@@ -13698,19 +14002,19 @@
         <v>1</v>
       </c>
       <c r="V65" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W65" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X65" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W65" s="35" t="s">
-        <v>374</v>
-      </c>
-      <c r="X65" s="30" t="s">
-        <v>375</v>
-      </c>
       <c r="Y65" s="35" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="66" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="66" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="31">
         <v>66</v>
       </c>
@@ -13775,19 +14079,19 @@
         <v>1</v>
       </c>
       <c r="V66" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W66" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X66" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W66" s="35" t="s">
-        <v>374</v>
-      </c>
-      <c r="X66" s="30" t="s">
-        <v>375</v>
-      </c>
       <c r="Y66" s="35" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="67" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="67" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="31">
         <v>67</v>
       </c>
@@ -13852,19 +14156,19 @@
         <v>1</v>
       </c>
       <c r="V67" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W67" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X67" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W67" s="35" t="s">
-        <v>374</v>
-      </c>
-      <c r="X67" s="30" t="s">
-        <v>375</v>
-      </c>
       <c r="Y67" s="35" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="68" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="68" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="31">
         <v>68</v>
       </c>
@@ -13929,19 +14233,19 @@
         <v>1</v>
       </c>
       <c r="V68" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W68" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X68" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W68" s="35" t="s">
-        <v>374</v>
-      </c>
-      <c r="X68" s="30" t="s">
-        <v>375</v>
-      </c>
       <c r="Y68" s="35" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="69" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="69" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="31">
         <v>69</v>
       </c>
@@ -14006,27 +14310,27 @@
         <v>1</v>
       </c>
       <c r="V69" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W69" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X69" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W69" s="35" t="s">
-        <v>374</v>
-      </c>
-      <c r="X69" s="30" t="s">
-        <v>375</v>
-      </c>
       <c r="Y69" s="35" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="70" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="70" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="31">
         <v>70</v>
       </c>
       <c r="B70" s="49" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C70" s="20" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D70" s="29" t="s">
         <v>323</v>
@@ -14062,7 +14366,7 @@
         <v>72</v>
       </c>
       <c r="O70" s="35" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="P70" s="30" t="s">
         <v>1</v>
@@ -14083,27 +14387,27 @@
         <v>1</v>
       </c>
       <c r="V70" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W70" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X70" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W70" s="35" t="s">
+      <c r="Y70" s="35" t="s">
         <v>374</v>
       </c>
-      <c r="X70" s="30" t="s">
-        <v>375</v>
-      </c>
-      <c r="Y70" s="35" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="71" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="71" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="31">
         <v>71</v>
       </c>
       <c r="B71" s="49" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="C71" s="20" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D71" s="29" t="s">
         <v>323</v>
@@ -14139,7 +14443,7 @@
         <v>72</v>
       </c>
       <c r="O71" s="35" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="P71" s="30" t="s">
         <v>1</v>
@@ -14160,27 +14464,27 @@
         <v>1</v>
       </c>
       <c r="V71" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W71" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X71" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W71" s="35" t="s">
+      <c r="Y71" s="35" t="s">
         <v>374</v>
       </c>
-      <c r="X71" s="30" t="s">
-        <v>375</v>
-      </c>
-      <c r="Y71" s="35" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="72" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="72" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="31">
         <v>72</v>
       </c>
       <c r="B72" s="49" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C72" s="20" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D72" s="29" t="s">
         <v>323</v>
@@ -14216,7 +14520,7 @@
         <v>72</v>
       </c>
       <c r="O72" s="35" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="P72" s="30" t="s">
         <v>1</v>
@@ -14237,24 +14541,24 @@
         <v>1</v>
       </c>
       <c r="V72" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W72" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X72" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W72" s="35" t="s">
+      <c r="Y72" s="35" t="s">
         <v>374</v>
       </c>
-      <c r="X72" s="30" t="s">
-        <v>375</v>
-      </c>
-      <c r="Y72" s="35" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="73" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="73" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="31">
         <v>73</v>
       </c>
       <c r="B73" s="49" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C73" s="20" t="s">
         <v>312</v>
@@ -14263,13 +14567,13 @@
         <v>323</v>
       </c>
       <c r="E73" s="34" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="F73" s="29" t="s">
         <v>323</v>
       </c>
       <c r="G73" s="34" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H73" s="29" t="s">
         <v>1</v>
@@ -14314,24 +14618,24 @@
         <v>1</v>
       </c>
       <c r="V73" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W73" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X73" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W73" s="35" t="s">
+      <c r="Y73" s="35" t="s">
         <v>374</v>
       </c>
-      <c r="X73" s="30" t="s">
-        <v>375</v>
-      </c>
-      <c r="Y73" s="35" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="74" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="74" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="31">
         <v>74</v>
       </c>
       <c r="B74" s="49" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C74" s="20" t="s">
         <v>312</v>
@@ -14340,13 +14644,13 @@
         <v>323</v>
       </c>
       <c r="E74" s="34" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="F74" s="29" t="s">
         <v>323</v>
       </c>
       <c r="G74" s="34" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="H74" s="29" t="s">
         <v>1</v>
@@ -14391,24 +14695,24 @@
         <v>1</v>
       </c>
       <c r="V74" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W74" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X74" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W74" s="35" t="s">
+      <c r="Y74" s="35" t="s">
         <v>374</v>
       </c>
-      <c r="X74" s="30" t="s">
-        <v>375</v>
-      </c>
-      <c r="Y74" s="35" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="75" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="75" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="31">
         <v>75</v>
       </c>
       <c r="B75" s="49" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="C75" s="20" t="s">
         <v>311</v>
@@ -14468,24 +14772,24 @@
         <v>1</v>
       </c>
       <c r="V75" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W75" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X75" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W75" s="35" t="s">
+      <c r="Y75" s="35" t="s">
         <v>374</v>
       </c>
-      <c r="X75" s="30" t="s">
-        <v>375</v>
-      </c>
-      <c r="Y75" s="35" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="76" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="76" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="31">
         <v>76</v>
       </c>
       <c r="B76" s="49" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C76" s="20" t="s">
         <v>311</v>
@@ -14545,24 +14849,24 @@
         <v>1</v>
       </c>
       <c r="V76" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W76" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X76" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W76" s="35" t="s">
+      <c r="Y76" s="35" t="s">
         <v>374</v>
       </c>
-      <c r="X76" s="30" t="s">
-        <v>375</v>
-      </c>
-      <c r="Y76" s="35" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="77" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="77" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="31">
         <v>77</v>
       </c>
       <c r="B77" s="49" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C77" s="20" t="s">
         <v>311</v>
@@ -14622,24 +14926,24 @@
         <v>1</v>
       </c>
       <c r="V77" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W77" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X77" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W77" s="35" t="s">
+      <c r="Y77" s="35" t="s">
         <v>374</v>
       </c>
-      <c r="X77" s="30" t="s">
-        <v>375</v>
-      </c>
-      <c r="Y77" s="35" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="78" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="78" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="31">
         <v>78</v>
       </c>
       <c r="B78" s="49" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C78" s="20" t="s">
         <v>311</v>
@@ -14699,19 +15003,19 @@
         <v>1</v>
       </c>
       <c r="V78" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W78" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X78" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W78" s="35" t="s">
+      <c r="Y78" s="35" t="s">
         <v>374</v>
       </c>
-      <c r="X78" s="30" t="s">
-        <v>375</v>
-      </c>
-      <c r="Y78" s="35" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="79" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="79" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="31">
         <v>79</v>
       </c>
@@ -14755,7 +15059,7 @@
         <v>72</v>
       </c>
       <c r="O79" s="35" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="P79" s="30" t="s">
         <v>1</v>
@@ -14776,19 +15080,19 @@
         <v>1</v>
       </c>
       <c r="V79" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W79" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X79" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W79" s="35" t="s">
-        <v>374</v>
-      </c>
-      <c r="X79" s="30" t="s">
-        <v>375</v>
-      </c>
       <c r="Y79" s="35" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="80" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="80" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="31">
         <v>80</v>
       </c>
@@ -14853,19 +15157,19 @@
         <v>1</v>
       </c>
       <c r="V80" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W80" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X80" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W80" s="35" t="s">
-        <v>374</v>
-      </c>
-      <c r="X80" s="30" t="s">
-        <v>375</v>
-      </c>
       <c r="Y80" s="35" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="81" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="81" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="31">
         <v>81</v>
       </c>
@@ -14930,19 +15234,19 @@
         <v>1</v>
       </c>
       <c r="V81" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W81" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X81" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W81" s="35" t="s">
-        <v>374</v>
-      </c>
-      <c r="X81" s="30" t="s">
-        <v>375</v>
-      </c>
       <c r="Y81" s="35" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="82" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="82" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="31">
         <v>82</v>
       </c>
@@ -15007,19 +15311,19 @@
         <v>1</v>
       </c>
       <c r="V82" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W82" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X82" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W82" s="35" t="s">
-        <v>374</v>
-      </c>
-      <c r="X82" s="30" t="s">
-        <v>375</v>
-      </c>
       <c r="Y82" s="35" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="83" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="83" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="31">
         <v>83</v>
       </c>
@@ -15084,19 +15388,19 @@
         <v>1</v>
       </c>
       <c r="V83" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W83" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X83" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W83" s="35" t="s">
-        <v>374</v>
-      </c>
-      <c r="X83" s="30" t="s">
-        <v>375</v>
-      </c>
       <c r="Y83" s="35" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="84" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="84" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="31">
         <v>84</v>
       </c>
@@ -15161,16 +15465,16 @@
         <v>1</v>
       </c>
       <c r="V84" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="W84" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="X84" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="W84" s="35" t="s">
-        <v>374</v>
-      </c>
-      <c r="X84" s="30" t="s">
-        <v>375</v>
-      </c>
       <c r="Y84" s="35" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
   </sheetData>
@@ -15179,31 +15483,31 @@
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="B1 B34:B35 B38:B78">
-    <cfRule type="duplicateValues" dxfId="11" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="10" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B76">
-    <cfRule type="duplicateValues" dxfId="7" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B79">
-    <cfRule type="duplicateValues" dxfId="6" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B80:B81">
-    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B82:B84">
-    <cfRule type="duplicateValues" dxfId="4" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C43">
-    <cfRule type="duplicateValues" dxfId="3" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G6:G7">
-    <cfRule type="duplicateValues" dxfId="1" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -15212,14 +15516,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FB56A46-58D1-419D-AFD2-969B66B932B3}">
   <dimension ref="A1:B15"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.3828125" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.42578125" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="61.5703125" style="6" customWidth="1"/>
-    <col min="3" max="16384" width="11.42578125" style="6"/>
+    <col min="1" max="1" width="2.3828125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="61.53515625" style="6" customWidth="1"/>
+    <col min="3" max="16384" width="11.3828125" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="8">
         <v>1</v>
       </c>
@@ -15227,7 +15531,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="33" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:2" ht="30.9" x14ac:dyDescent="0.2">
       <c r="A2" s="8">
         <v>2</v>
       </c>
@@ -15235,7 +15539,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="33" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:2" ht="30.9" x14ac:dyDescent="0.2">
       <c r="A3" s="8">
         <v>3</v>
       </c>
@@ -15243,7 +15547,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="41.25" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:2" ht="38.6" x14ac:dyDescent="0.2">
       <c r="A4" s="8">
         <v>4</v>
       </c>
@@ -15251,7 +15555,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="86.45" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:2" ht="86.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="8">
         <v>5</v>
       </c>
@@ -15259,7 +15563,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="8">
         <v>6</v>
       </c>
@@ -15267,7 +15571,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="8">
         <v>7</v>
       </c>
@@ -15275,7 +15579,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="8">
         <v>8</v>
       </c>
@@ -15283,7 +15587,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="8">
         <v>9</v>
       </c>
@@ -15291,7 +15595,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="8">
         <v>10</v>
       </c>
@@ -15299,7 +15603,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="8">
         <v>11</v>
       </c>
@@ -15307,7 +15611,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="8">
         <v>12</v>
       </c>
@@ -15315,7 +15619,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="8">
         <v>13</v>
       </c>
@@ -15323,7 +15627,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="8">
         <v>14</v>
       </c>
@@ -15331,7 +15635,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="8">
         <v>15</v>
       </c>

--- a/Versão5/PRO/Ontologia_Crono.xlsx
+++ b/Versão5/PRO/Ontologia_Crono.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\PRO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D6E85D1-16AE-497D-8A34-031302F8A7A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28A7E196-C76D-4CA9-A0DE-E2988EFF2E1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="4" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="26" r:id="rId1"/>
@@ -3556,39 +3556,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="26">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
+  <dxfs count="22">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -4114,15 +4082,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{612B613C-8B96-43A0-BB50-A45AC26373E3}">
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultColWidth="3.28515625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="3.3046875" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" style="12" customWidth="1"/>
-    <col min="2" max="2" width="39.85546875" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" style="55" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="3.28515625" style="12"/>
+    <col min="1" max="1" width="9.69140625" style="12" customWidth="1"/>
+    <col min="2" max="2" width="39.84375" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.3828125" style="55" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="3.3046875" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="49.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="13" t="s">
         <v>137</v>
       </c>
@@ -4133,7 +4101,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="14" t="s">
         <v>146</v>
       </c>
@@ -4144,7 +4112,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="14" t="s">
         <v>147</v>
       </c>
@@ -4155,7 +4123,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="14" t="s">
         <v>138</v>
       </c>
@@ -4166,7 +4134,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="14" t="s">
         <v>139</v>
       </c>
@@ -4178,7 +4146,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="14" t="s">
         <v>140</v>
       </c>
@@ -4190,7 +4158,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="14" t="s">
         <v>141</v>
       </c>
@@ -4201,7 +4169,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="8" spans="1:3" customFormat="1" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" customFormat="1" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="16" t="s">
         <v>142</v>
       </c>
@@ -4212,7 +4180,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="14" t="s">
         <v>150</v>
       </c>
@@ -4223,7 +4191,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="14" t="s">
         <v>152</v>
       </c>
@@ -4234,7 +4202,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="14" t="s">
         <v>143</v>
       </c>
@@ -4245,7 +4213,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="14" t="s">
         <v>144</v>
       </c>
@@ -4256,7 +4224,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="14" t="s">
         <v>153</v>
       </c>
@@ -4267,7 +4235,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="14" t="s">
         <v>154</v>
       </c>
@@ -4278,7 +4246,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="14" t="s">
         <v>155</v>
       </c>
@@ -4289,7 +4257,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="14" t="s">
         <v>156</v>
       </c>
@@ -4300,7 +4268,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="14" t="s">
         <v>145</v>
       </c>
@@ -4311,19 +4279,19 @@
         <v>359</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="14" t="s">
         <v>157</v>
       </c>
       <c r="B18" s="17">
         <f ca="1">NOW()</f>
-        <v>46259.693160416668</v>
+        <v>46264.568321412036</v>
       </c>
       <c r="C18" s="54" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="19" spans="1:3" s="57" customFormat="1" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" s="57" customFormat="1" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="16" t="s">
         <v>362</v>
       </c>
@@ -4334,7 +4302,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="20" spans="1:3" s="57" customFormat="1" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" s="57" customFormat="1" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="16" t="s">
         <v>364</v>
       </c>
@@ -4346,7 +4314,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="21" spans="1:3" s="57" customFormat="1" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" s="57" customFormat="1" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="16" t="s">
         <v>365</v>
       </c>
@@ -4358,7 +4326,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="14" t="s">
         <v>158</v>
       </c>
@@ -4369,7 +4337,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="14" t="s">
         <v>159</v>
       </c>
@@ -4380,7 +4348,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="16" t="s">
         <v>160</v>
       </c>
@@ -4391,7 +4359,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="16" t="s">
         <v>161</v>
       </c>
@@ -4402,7 +4370,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="26" spans="1:3" customFormat="1" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" customFormat="1" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="16" t="s">
         <v>356</v>
       </c>
@@ -4422,36 +4390,36 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A7B04F8-6372-42A9-A10C-B0C4EF342E07}">
   <dimension ref="A1:AC47"/>
-  <sheetFormatPr defaultColWidth="6.5703125" defaultRowHeight="6.95" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="6.53515625" defaultRowHeight="7" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.42578125" style="69" customWidth="1"/>
-    <col min="2" max="2" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="7.28515625" customWidth="1"/>
-    <col min="12" max="12" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.3828125" style="69" customWidth="1"/>
+    <col min="2" max="2" width="6.3046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.53515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.3828125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.15234375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.3828125" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="7.3046875" customWidth="1"/>
+    <col min="12" max="12" width="5.15234375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="40.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="37.5703125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="44.7109375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.7109375" style="58" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="7.5703125" style="58" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="7.42578125" style="58" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.3046875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.53515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="40.69140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="37.53515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="44.69140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.69140625" style="58" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="7.53515625" style="58" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="7.3828125" style="58" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="7" style="58" customWidth="1"/>
-    <col min="23" max="23" width="6.85546875" style="58" customWidth="1"/>
+    <col min="23" max="23" width="6.84375" style="58" customWidth="1"/>
     <col min="24" max="24" width="9" style="58" customWidth="1"/>
-    <col min="25" max="25" width="6.5703125" style="58" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.42578125" style="58" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="5.42578125" style="58" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="6.53515625" style="58" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6.3828125" style="58" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="5.3828125" style="58" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="6" style="58" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="3" style="58" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" ht="32.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="67" t="s">
         <v>166</v>
       </c>
@@ -4540,7 +4508,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="2" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="68">
         <v>2</v>
       </c>
@@ -4637,7 +4605,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="68">
         <v>3</v>
       </c>
@@ -4734,7 +4702,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="68">
         <v>4</v>
       </c>
@@ -4831,7 +4799,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="68">
         <v>5</v>
       </c>
@@ -4928,7 +4896,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="68">
         <v>6</v>
       </c>
@@ -5025,7 +4993,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="68">
         <v>7</v>
       </c>
@@ -5122,7 +5090,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="68">
         <v>8</v>
       </c>
@@ -5219,7 +5187,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="68">
         <v>9</v>
       </c>
@@ -5316,7 +5284,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="68">
         <v>10</v>
       </c>
@@ -5413,7 +5381,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="68">
         <v>11</v>
       </c>
@@ -5510,7 +5478,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="68">
         <v>12</v>
       </c>
@@ -5607,7 +5575,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="68">
         <v>13</v>
       </c>
@@ -5704,7 +5672,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="68">
         <v>14</v>
       </c>
@@ -5801,7 +5769,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="68">
         <v>15</v>
       </c>
@@ -5898,7 +5866,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="68">
         <v>16</v>
       </c>
@@ -5995,7 +5963,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="68">
         <v>17</v>
       </c>
@@ -6092,7 +6060,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="68">
         <v>18</v>
       </c>
@@ -6189,7 +6157,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="68">
         <v>19</v>
       </c>
@@ -6286,7 +6254,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="68">
         <v>20</v>
       </c>
@@ -6383,7 +6351,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="68">
         <v>21</v>
       </c>
@@ -6480,7 +6448,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="68">
         <v>22</v>
       </c>
@@ -6577,7 +6545,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="68">
         <v>23</v>
       </c>
@@ -6674,7 +6642,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="68">
         <v>24</v>
       </c>
@@ -6771,7 +6739,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="68">
         <v>25</v>
       </c>
@@ -6868,7 +6836,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="68">
         <v>26</v>
       </c>
@@ -6965,7 +6933,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="68">
         <v>27</v>
       </c>
@@ -7062,7 +7030,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="68">
         <v>28</v>
       </c>
@@ -7159,7 +7127,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="68">
         <v>29</v>
       </c>
@@ -7256,7 +7224,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="68">
         <v>30</v>
       </c>
@@ -7353,7 +7321,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="68">
         <v>31</v>
       </c>
@@ -7450,7 +7418,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="68">
         <v>32</v>
       </c>
@@ -7547,7 +7515,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="68">
         <v>33</v>
       </c>
@@ -7644,7 +7612,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="68">
         <v>34</v>
       </c>
@@ -7741,7 +7709,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="68">
         <v>35</v>
       </c>
@@ -7838,7 +7806,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="68">
         <v>36</v>
       </c>
@@ -7935,7 +7903,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="68">
         <v>37</v>
       </c>
@@ -8032,7 +8000,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="68">
         <v>38</v>
       </c>
@@ -8129,7 +8097,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="68">
         <v>39</v>
       </c>
@@ -8226,7 +8194,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="68">
         <v>40</v>
       </c>
@@ -8323,7 +8291,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="68">
         <v>41</v>
       </c>
@@ -8420,7 +8388,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="68">
         <v>42</v>
       </c>
@@ -8517,7 +8485,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="68">
         <v>43</v>
       </c>
@@ -8614,7 +8582,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="68">
         <v>44</v>
       </c>
@@ -8711,7 +8679,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="68">
         <v>45</v>
       </c>
@@ -8808,7 +8776,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="68">
         <v>46</v>
       </c>
@@ -8906,7 +8874,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:29" s="75" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:29" s="75" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="68">
         <v>47</v>
       </c>
@@ -8917,10 +8885,10 @@
         <v>520</v>
       </c>
       <c r="D47" s="71" t="s">
+        <v>522</v>
+      </c>
+      <c r="E47" s="71" t="s">
         <v>521</v>
-      </c>
-      <c r="E47" s="71" t="s">
-        <v>522</v>
       </c>
       <c r="F47" s="71" t="s">
         <v>523</v>
@@ -8946,11 +8914,11 @@
       </c>
       <c r="M47" s="59" t="str">
         <f t="shared" si="31"/>
-        <v>Métodos</v>
+        <v>Macros</v>
       </c>
       <c r="N47" s="59" t="str">
         <f t="shared" si="31"/>
-        <v>Macros</v>
+        <v>Métodos</v>
       </c>
       <c r="O47" s="59" t="str">
         <f t="shared" si="31"/>
@@ -8974,11 +8942,11 @@
       </c>
       <c r="U47" s="52" t="str">
         <f t="shared" si="32"/>
-        <v>Métodos</v>
+        <v>Macros</v>
       </c>
       <c r="V47" s="73" t="str">
         <f t="shared" si="32"/>
-        <v>Macros</v>
+        <v>Métodos</v>
       </c>
       <c r="W47" s="52" t="s">
         <v>179</v>
@@ -9005,31 +8973,31 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:B47">
-    <cfRule type="cellIs" dxfId="25" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F39">
-    <cfRule type="duplicateValues" dxfId="24" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F46">
-    <cfRule type="duplicateValues" dxfId="23" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F47">
-    <cfRule type="duplicateValues" dxfId="22" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1:R45">
-    <cfRule type="cellIs" dxfId="21" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R47">
-    <cfRule type="cellIs" dxfId="20" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W46">
-    <cfRule type="cellIs" dxfId="19" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="11" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9043,15 +9011,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{402BD1C2-A59C-4020-8FC9-E5402FE7B33F}">
   <dimension ref="A1:U3"/>
-  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="10" width="5.85546875" style="2" customWidth="1"/>
-    <col min="11" max="21" width="5.85546875" style="5" customWidth="1"/>
-    <col min="22" max="16384" width="11.140625" style="5"/>
+    <col min="1" max="1" width="2.84375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="10" width="5.84375" style="2" customWidth="1"/>
+    <col min="11" max="21" width="5.84375" style="5" customWidth="1"/>
+    <col min="22" max="16384" width="11.15234375" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="3" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" s="3" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="43" t="s">
         <v>22</v>
       </c>
@@ -9116,7 +9084,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="43">
         <v>2</v>
       </c>
@@ -9181,7 +9149,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="43">
         <v>3</v>
       </c>
@@ -9249,7 +9217,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="18" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9261,14 +9229,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C7BFE13-E93E-488C-9C8F-4E4982DFBAE7}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.28515625" customWidth="1"/>
-    <col min="2" max="2" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.3046875" customWidth="1"/>
+    <col min="2" max="2" width="6.69140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="41">
         <v>1</v>
       </c>
@@ -9279,7 +9247,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="19">
         <v>2</v>
       </c>
@@ -9290,7 +9258,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="19">
         <v>3</v>
       </c>
@@ -9301,7 +9269,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" s="19">
         <v>4</v>
       </c>
@@ -9314,7 +9282,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A4">
-    <cfRule type="cellIs" dxfId="17" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9325,46 +9293,46 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5087910E-DA31-4318-A539-726BE963325D}">
   <dimension ref="A1:AI89"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="7.35" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="7.4" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="3.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="3.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="3.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="3.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.53515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.69140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.84375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.53515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.15234375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.3046875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.3828125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.3046875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="3.3828125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.3046875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="3.3828125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.3046875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="3.3828125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="6" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="49" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="3.42578125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="4.28515625" style="58" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.85546875" style="58" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="5.28515625" style="58" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.28515625" style="58" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="3.42578125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="3.42578125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="3.42578125" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="3.42578125" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="3.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4.3046875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.69140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.53515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.3828125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="4.3046875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="3.3828125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.3046875" style="58" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.84375" style="58" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.3046875" style="58" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.3046875" style="58" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="4.3046875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="3.3828125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="4.3046875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="3.3828125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="4.3046875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="3.3828125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="4.3046875" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="3.3828125" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="4.3046875" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="3.3828125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:35" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="39" t="s">
         <v>182</v>
       </c>
@@ -9471,7 +9439,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="2" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="83">
         <v>2</v>
       </c>
@@ -9578,7 +9546,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="83">
         <v>3</v>
       </c>
@@ -9685,7 +9653,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="83">
         <v>4</v>
       </c>
@@ -9792,7 +9760,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="83">
         <v>5</v>
       </c>
@@ -9899,7 +9867,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="83">
         <v>6</v>
       </c>
@@ -10006,7 +9974,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="83">
         <v>7</v>
       </c>
@@ -10113,7 +10081,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="83">
         <v>8</v>
       </c>
@@ -10220,7 +10188,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="83">
         <v>9</v>
       </c>
@@ -10327,7 +10295,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="83">
         <v>10</v>
       </c>
@@ -10434,7 +10402,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="83">
         <v>11</v>
       </c>
@@ -10541,7 +10509,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="83">
         <v>12</v>
       </c>
@@ -10648,7 +10616,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="83">
         <v>13</v>
       </c>
@@ -10755,7 +10723,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="83">
         <v>14</v>
       </c>
@@ -10862,7 +10830,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="83">
         <v>15</v>
       </c>
@@ -10969,7 +10937,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="83">
         <v>16</v>
       </c>
@@ -11076,7 +11044,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="83">
         <v>17</v>
       </c>
@@ -11183,7 +11151,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="83">
         <v>18</v>
       </c>
@@ -11290,7 +11258,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="83">
         <v>19</v>
       </c>
@@ -11397,7 +11365,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="83">
         <v>20</v>
       </c>
@@ -11504,7 +11472,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="83">
         <v>21</v>
       </c>
@@ -11611,7 +11579,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="83">
         <v>22</v>
       </c>
@@ -11718,7 +11686,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="83">
         <v>23</v>
       </c>
@@ -11825,7 +11793,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="83">
         <v>24</v>
       </c>
@@ -11932,7 +11900,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="83">
         <v>25</v>
       </c>
@@ -12039,7 +12007,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="83">
         <v>26</v>
       </c>
@@ -12146,7 +12114,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="83">
         <v>27</v>
       </c>
@@ -12253,7 +12221,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="83">
         <v>28</v>
       </c>
@@ -12360,7 +12328,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="83">
         <v>29</v>
       </c>
@@ -12467,7 +12435,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="83">
         <v>30</v>
       </c>
@@ -12574,7 +12542,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="83">
         <v>31</v>
       </c>
@@ -12681,7 +12649,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="83">
         <v>32</v>
       </c>
@@ -12788,7 +12756,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="83">
         <v>33</v>
       </c>
@@ -12895,7 +12863,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="83">
         <v>34</v>
       </c>
@@ -13002,7 +12970,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="83">
         <v>35</v>
       </c>
@@ -13109,7 +13077,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="83">
         <v>36</v>
       </c>
@@ -13216,7 +13184,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="83">
         <v>37</v>
       </c>
@@ -13323,7 +13291,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="83">
         <v>38</v>
       </c>
@@ -13430,7 +13398,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="83">
         <v>39</v>
       </c>
@@ -13537,7 +13505,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="83">
         <v>40</v>
       </c>
@@ -13644,7 +13612,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="83">
         <v>41</v>
       </c>
@@ -13751,7 +13719,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="83">
         <v>42</v>
       </c>
@@ -13858,7 +13826,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="83">
         <v>43</v>
       </c>
@@ -13965,7 +13933,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="83">
         <v>44</v>
       </c>
@@ -14072,7 +14040,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="83">
         <v>45</v>
       </c>
@@ -14179,7 +14147,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="83">
         <v>46</v>
       </c>
@@ -14286,7 +14254,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="83">
         <v>47</v>
       </c>
@@ -14393,7 +14361,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="83">
         <v>48</v>
       </c>
@@ -14500,7 +14468,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="83">
         <v>49</v>
       </c>
@@ -14607,7 +14575,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="83">
         <v>50</v>
       </c>
@@ -14714,7 +14682,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="83">
         <v>51</v>
       </c>
@@ -14821,7 +14789,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="83">
         <v>52</v>
       </c>
@@ -14928,7 +14896,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" s="83">
         <v>53</v>
       </c>
@@ -15035,7 +15003,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="83">
         <v>54</v>
       </c>
@@ -15142,7 +15110,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" s="83">
         <v>55</v>
       </c>
@@ -15249,7 +15217,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="83">
         <v>56</v>
       </c>
@@ -15356,7 +15324,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" s="83">
         <v>57</v>
       </c>
@@ -15463,7 +15431,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="83">
         <v>58</v>
       </c>
@@ -15570,7 +15538,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="83">
         <v>59</v>
       </c>
@@ -15677,7 +15645,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="83">
         <v>60</v>
       </c>
@@ -15784,7 +15752,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="83">
         <v>61</v>
       </c>
@@ -15891,7 +15859,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" s="83">
         <v>62</v>
       </c>
@@ -15998,7 +15966,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A63" s="83">
         <v>63</v>
       </c>
@@ -16105,7 +16073,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="83">
         <v>64</v>
       </c>
@@ -16212,7 +16180,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="83">
         <v>65</v>
       </c>
@@ -16319,7 +16287,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="83">
         <v>66</v>
       </c>
@@ -16426,7 +16394,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="83">
         <v>67</v>
       </c>
@@ -16533,7 +16501,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="83">
         <v>68</v>
       </c>
@@ -16640,7 +16608,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="83">
         <v>69</v>
       </c>
@@ -16747,7 +16715,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="83">
         <v>70</v>
       </c>
@@ -16854,7 +16822,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="83">
         <v>71</v>
       </c>
@@ -16961,7 +16929,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="83">
         <v>72</v>
       </c>
@@ -17068,7 +17036,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="83">
         <v>73</v>
       </c>
@@ -17175,7 +17143,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="83">
         <v>74</v>
       </c>
@@ -17282,7 +17250,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="83">
         <v>75</v>
       </c>
@@ -17389,7 +17357,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="83">
         <v>76</v>
       </c>
@@ -17496,7 +17464,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="83">
         <v>77</v>
       </c>
@@ -17603,7 +17571,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="83">
         <v>78</v>
       </c>
@@ -17710,7 +17678,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="83">
         <v>79</v>
       </c>
@@ -17817,7 +17785,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="83">
         <v>80</v>
       </c>
@@ -17924,7 +17892,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="83">
         <v>81</v>
       </c>
@@ -18031,7 +17999,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="83">
         <v>82</v>
       </c>
@@ -18138,7 +18106,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="83">
         <v>83</v>
       </c>
@@ -18245,7 +18213,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="83">
         <v>84</v>
       </c>
@@ -18352,7 +18320,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:35" s="82" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:35" s="82" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="83">
         <v>85</v>
       </c>
@@ -18460,7 +18428,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:35" s="82" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:35" s="82" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="83">
         <v>86</v>
       </c>
@@ -18568,7 +18536,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:35" s="82" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:35" s="82" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="83">
         <v>87</v>
       </c>
@@ -18676,7 +18644,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:35" s="82" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:35" s="82" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="83">
         <v>88</v>
       </c>
@@ -18784,7 +18752,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:35" s="82" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:35" s="82" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="83">
         <v>89</v>
       </c>
@@ -18898,35 +18866,35 @@
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="B1 B34:B35 B38:B78">
-    <cfRule type="duplicateValues" dxfId="16" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B84 B90:B1048576">
-    <cfRule type="duplicateValues" dxfId="15" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B76">
-    <cfRule type="duplicateValues" dxfId="12" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B79">
-    <cfRule type="duplicateValues" dxfId="11" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B80:B81">
-    <cfRule type="duplicateValues" dxfId="10" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B82:B84">
-    <cfRule type="duplicateValues" dxfId="9" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B85:B89">
+    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C43">
-    <cfRule type="duplicateValues" dxfId="8" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G6:G7">
-    <cfRule type="duplicateValues" dxfId="6" priority="13"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B85:B89">
-    <cfRule type="duplicateValues" dxfId="5" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -18935,14 +18903,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FB56A46-58D1-419D-AFD2-969B66B932B3}">
   <dimension ref="A1:B15"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.3828125" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.42578125" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="61.5703125" style="6" customWidth="1"/>
-    <col min="3" max="16384" width="11.42578125" style="6"/>
+    <col min="1" max="1" width="2.3828125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="61.53515625" style="6" customWidth="1"/>
+    <col min="3" max="16384" width="11.3828125" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="8">
         <v>1</v>
       </c>
@@ -18950,7 +18918,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="33" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:2" ht="30.9" x14ac:dyDescent="0.2">
       <c r="A2" s="8">
         <v>2</v>
       </c>
@@ -18958,7 +18926,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="33" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:2" ht="30.9" x14ac:dyDescent="0.2">
       <c r="A3" s="8">
         <v>3</v>
       </c>
@@ -18966,7 +18934,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="41.25" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:2" ht="38.6" x14ac:dyDescent="0.2">
       <c r="A4" s="8">
         <v>4</v>
       </c>
@@ -18974,7 +18942,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="86.45" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:2" ht="86.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="8">
         <v>5</v>
       </c>
@@ -18982,7 +18950,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="8">
         <v>6</v>
       </c>
@@ -18990,7 +18958,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="8">
         <v>7</v>
       </c>
@@ -18998,7 +18966,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="8">
         <v>8</v>
       </c>
@@ -19006,7 +18974,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="8">
         <v>9</v>
       </c>
@@ -19014,7 +18982,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="8">
         <v>10</v>
       </c>
@@ -19022,7 +18990,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="8">
         <v>11</v>
       </c>
@@ -19030,7 +18998,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="8">
         <v>12</v>
       </c>
@@ -19038,7 +19006,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="8">
         <v>13</v>
       </c>
@@ -19046,7 +19014,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="8">
         <v>14</v>
       </c>
@@ -19054,7 +19022,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="8">
         <v>15</v>
       </c>

--- a/Versão5/PRO/Ontologia_Crono.xlsx
+++ b/Versão5/PRO/Ontologia_Crono.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\PRO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28A7E196-C76D-4CA9-A0DE-E2988EFF2E1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{123853B0-BE5B-4D3B-BDCD-3AF45A9763D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="26" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4126" uniqueCount="548">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4257" uniqueCount="566">
   <si>
     <t>Key</t>
   </si>
@@ -2833,18 +2833,6 @@
     <t>Macros</t>
   </si>
   <si>
-    <t>API.Revit</t>
-  </si>
-  <si>
-    <t>Aplicação Revit</t>
-  </si>
-  <si>
-    <t>Aplicativo Revit</t>
-  </si>
-  <si>
-    <t>Revit Aplication</t>
-  </si>
-  <si>
     <t>API_Ambiente</t>
   </si>
   <si>
@@ -2906,6 +2894,72 @@
   </si>
   <si>
     <t>"[ Materiais ]"</t>
+  </si>
+  <si>
+    <t>Função.Auxiliar</t>
+  </si>
+  <si>
+    <t>Define uma Função Auxiliar (helper) numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol de ayudante en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Helper Role in an application</t>
+  </si>
+  <si>
+    <t>Função.Global</t>
+  </si>
+  <si>
+    <t>Define uma Função Global numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol global en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Global Role in an application</t>
+  </si>
+  <si>
+    <t>Função.Local</t>
+  </si>
+  <si>
+    <t>Define uma Função Local numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol local en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Local Role in an application</t>
+  </si>
+  <si>
+    <t>Função.Filtro</t>
+  </si>
+  <si>
+    <t>Define uma Função para filtrar objetos numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina una función para filtrar objetos en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Function to filter objects in an application</t>
+  </si>
+  <si>
+    <t>Códigos.Visuais</t>
+  </si>
+  <si>
+    <t>Bloco.de.Código</t>
+  </si>
+  <si>
+    <t>Define um Código escrito em sistemas de programação visual</t>
+  </si>
+  <si>
+    <t>Define un código escrito en sistemas de programación visual</t>
+  </si>
+  <si>
+    <t>Defines a Code written in visual programming systems</t>
+  </si>
+  <si>
+    <t>KML</t>
   </si>
 </sst>
 </file>
@@ -3218,12 +3272,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFBE79D"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor rgb="FFFEF2CB"/>
       </patternFill>
@@ -3250,6 +3298,12 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE89F"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -3304,7 +3358,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3509,25 +3563,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="23" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3536,20 +3584,23 @@
     <xf numFmtId="0" fontId="23" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3721,11 +3772,13 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
+        <color rgb="FF9C0006"/>
       </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -4082,15 +4135,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{612B613C-8B96-43A0-BB50-A45AC26373E3}">
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultColWidth="3.3046875" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="3.28515625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.69140625" style="12" customWidth="1"/>
-    <col min="2" max="2" width="39.84375" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.3828125" style="55" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="3.3046875" style="12"/>
+    <col min="1" max="1" width="9.7109375" style="12" customWidth="1"/>
+    <col min="2" max="2" width="39.85546875" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.42578125" style="55" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="3.28515625" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="49.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
         <v>137</v>
       </c>
@@ -4101,7 +4154,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
         <v>146</v>
       </c>
@@ -4112,7 +4165,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
         <v>147</v>
       </c>
@@ -4123,7 +4176,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
         <v>138</v>
       </c>
@@ -4134,7 +4187,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
         <v>139</v>
       </c>
@@ -4146,7 +4199,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
         <v>140</v>
       </c>
@@ -4158,7 +4211,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
         <v>141</v>
       </c>
@@ -4169,7 +4222,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="8" spans="1:3" customFormat="1" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" customFormat="1" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
         <v>142</v>
       </c>
@@ -4180,7 +4233,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
         <v>150</v>
       </c>
@@ -4191,7 +4244,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
         <v>152</v>
       </c>
@@ -4202,7 +4255,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
         <v>143</v>
       </c>
@@ -4213,7 +4266,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
         <v>144</v>
       </c>
@@ -4224,7 +4277,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
         <v>153</v>
       </c>
@@ -4235,7 +4288,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>154</v>
       </c>
@@ -4246,7 +4299,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
         <v>155</v>
       </c>
@@ -4257,7 +4310,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
         <v>156</v>
       </c>
@@ -4268,7 +4321,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
         <v>145</v>
       </c>
@@ -4279,19 +4332,19 @@
         <v>359</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
         <v>157</v>
       </c>
       <c r="B18" s="17">
         <f ca="1">NOW()</f>
-        <v>46264.568321412036</v>
+        <v>46268.698619097224</v>
       </c>
       <c r="C18" s="54" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="19" spans="1:3" s="57" customFormat="1" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3" s="57" customFormat="1" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
         <v>362</v>
       </c>
@@ -4302,7 +4355,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="20" spans="1:3" s="57" customFormat="1" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" s="57" customFormat="1" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
         <v>364</v>
       </c>
@@ -4314,7 +4367,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="21" spans="1:3" s="57" customFormat="1" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" s="57" customFormat="1" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
         <v>365</v>
       </c>
@@ -4326,7 +4379,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
         <v>158</v>
       </c>
@@ -4337,7 +4390,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
         <v>159</v>
       </c>
@@ -4348,7 +4401,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
         <v>160</v>
       </c>
@@ -4359,7 +4412,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="16" t="s">
         <v>161</v>
       </c>
@@ -4370,7 +4423,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="26" spans="1:3" customFormat="1" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:3" customFormat="1" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="16" t="s">
         <v>356</v>
       </c>
@@ -4389,37 +4442,36 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A7B04F8-6372-42A9-A10C-B0C4EF342E07}">
-  <dimension ref="A1:AC47"/>
-  <sheetFormatPr defaultColWidth="6.53515625" defaultRowHeight="7" customHeight="1" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:AD51"/>
+  <sheetFormatPr defaultColWidth="6.5703125" defaultRowHeight="6.95" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.3828125" style="69" customWidth="1"/>
-    <col min="2" max="2" width="6.3046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.53515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.3828125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.15234375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.3828125" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="7.3046875" customWidth="1"/>
-    <col min="12" max="12" width="5.15234375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.3046875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6.53515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="40.69140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="37.53515625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="44.69140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.69140625" style="58" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="7.53515625" style="58" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="7.3828125" style="58" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="7" style="58" customWidth="1"/>
-    <col min="23" max="23" width="6.84375" style="58" customWidth="1"/>
-    <col min="24" max="24" width="9" style="58" customWidth="1"/>
-    <col min="25" max="25" width="6.53515625" style="58" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.3828125" style="58" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="5.3828125" style="58" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.42578125" style="69" customWidth="1"/>
+    <col min="2" max="2" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="8" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="55.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="50.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="44.7109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.7109375" style="58" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="7.5703125" style="58" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="7.42578125" style="58" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.5703125" style="58" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="10.42578125" style="58" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.140625" style="58" customWidth="1"/>
+    <col min="25" max="25" width="6.5703125" style="58" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6.28515625" style="58" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="5.5703125" style="58" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="6" style="58" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="3" style="58" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="4" style="58" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="32.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:30" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="67" t="s">
         <v>166</v>
       </c>
@@ -4507,8 +4559,11 @@
       <c r="AC1" s="23" t="s">
         <v>354</v>
       </c>
+      <c r="AD1" s="23" t="s">
+        <v>565</v>
+      </c>
     </row>
-    <row r="2" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="68">
         <v>2</v>
       </c>
@@ -4586,26 +4641,29 @@
         <v>179</v>
       </c>
       <c r="X2" s="63" t="str">
-        <f t="shared" ref="X2:X47" si="3">CONCATENATE("Key-CRONO-",A2)</f>
+        <f t="shared" ref="X2:X46" si="3">CONCATENATE("Key-CRONO-",A2)</f>
         <v>Key-CRONO-2</v>
       </c>
-      <c r="Y2" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z2" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA2" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB2" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC2" s="74" t="s">
+      <c r="Y2" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z2" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA2" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB2" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC2" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD2" s="72" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="68">
         <v>3</v>
       </c>
@@ -4686,23 +4744,26 @@
         <f t="shared" si="3"/>
         <v>Key-CRONO-3</v>
       </c>
-      <c r="Y3" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z3" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA3" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB3" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC3" s="74" t="s">
+      <c r="Y3" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z3" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA3" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB3" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC3" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD3" s="72" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="68">
         <v>4</v>
       </c>
@@ -4783,23 +4844,26 @@
         <f t="shared" si="3"/>
         <v>Key-CRONO-4</v>
       </c>
-      <c r="Y4" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA4" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB4" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC4" s="74" t="s">
+      <c r="Y4" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z4" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA4" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB4" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC4" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD4" s="72" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="68">
         <v>5</v>
       </c>
@@ -4880,23 +4944,26 @@
         <f t="shared" si="3"/>
         <v>Key-CRONO-5</v>
       </c>
-      <c r="Y5" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z5" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA5" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB5" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC5" s="74" t="s">
+      <c r="Y5" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z5" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA5" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB5" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC5" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD5" s="72" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="68">
         <v>6</v>
       </c>
@@ -4977,23 +5044,26 @@
         <f t="shared" si="3"/>
         <v>Key-CRONO-6</v>
       </c>
-      <c r="Y6" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z6" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA6" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB6" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC6" s="74" t="s">
+      <c r="Y6" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z6" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA6" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB6" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC6" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD6" s="72" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="68">
         <v>7</v>
       </c>
@@ -5074,23 +5144,26 @@
         <f t="shared" si="3"/>
         <v>Key-CRONO-7</v>
       </c>
-      <c r="Y7" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z7" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA7" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB7" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC7" s="74" t="s">
+      <c r="Y7" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z7" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA7" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB7" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC7" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD7" s="72" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="68">
         <v>8</v>
       </c>
@@ -5171,23 +5244,26 @@
         <f t="shared" si="3"/>
         <v>Key-CRONO-8</v>
       </c>
-      <c r="Y8" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z8" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA8" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB8" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC8" s="74" t="s">
+      <c r="Y8" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z8" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA8" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB8" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC8" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD8" s="72" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="68">
         <v>9</v>
       </c>
@@ -5268,23 +5344,26 @@
         <f t="shared" si="3"/>
         <v>Key-CRONO-9</v>
       </c>
-      <c r="Y9" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z9" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA9" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB9" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC9" s="74" t="s">
+      <c r="Y9" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z9" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA9" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB9" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC9" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD9" s="72" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="68">
         <v>10</v>
       </c>
@@ -5365,23 +5444,26 @@
         <f t="shared" si="3"/>
         <v>Key-CRONO-10</v>
       </c>
-      <c r="Y10" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z10" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA10" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB10" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC10" s="74" t="s">
+      <c r="Y10" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z10" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA10" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB10" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC10" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD10" s="72" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="68">
         <v>11</v>
       </c>
@@ -5462,23 +5544,26 @@
         <f t="shared" si="3"/>
         <v>Key-CRONO-11</v>
       </c>
-      <c r="Y11" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z11" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA11" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB11" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC11" s="74" t="s">
+      <c r="Y11" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z11" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA11" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB11" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC11" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD11" s="72" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="68">
         <v>12</v>
       </c>
@@ -5559,23 +5644,26 @@
         <f t="shared" si="3"/>
         <v>Key-CRONO-12</v>
       </c>
-      <c r="Y12" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z12" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA12" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB12" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC12" s="74" t="s">
+      <c r="Y12" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z12" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA12" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB12" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC12" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD12" s="72" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="68">
         <v>13</v>
       </c>
@@ -5656,23 +5744,26 @@
         <f t="shared" si="3"/>
         <v>Key-CRONO-13</v>
       </c>
-      <c r="Y13" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z13" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA13" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB13" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC13" s="74" t="s">
+      <c r="Y13" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z13" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA13" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB13" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC13" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD13" s="72" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="68">
         <v>14</v>
       </c>
@@ -5753,23 +5844,26 @@
         <f t="shared" si="3"/>
         <v>Key-CRONO-14</v>
       </c>
-      <c r="Y14" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z14" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA14" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB14" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC14" s="74" t="s">
+      <c r="Y14" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z14" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA14" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB14" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC14" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD14" s="72" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="68">
         <v>15</v>
       </c>
@@ -5850,23 +5944,26 @@
         <f t="shared" si="3"/>
         <v>Key-CRONO-15</v>
       </c>
-      <c r="Y15" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z15" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA15" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB15" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC15" s="74" t="s">
+      <c r="Y15" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z15" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA15" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB15" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC15" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD15" s="72" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="68">
         <v>16</v>
       </c>
@@ -5947,23 +6044,26 @@
         <f t="shared" si="3"/>
         <v>Key-CRONO-16</v>
       </c>
-      <c r="Y16" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z16" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA16" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB16" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC16" s="74" t="s">
+      <c r="Y16" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z16" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA16" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB16" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC16" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD16" s="72" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="68">
         <v>17</v>
       </c>
@@ -6044,23 +6144,26 @@
         <f t="shared" ref="X17" si="19">CONCATENATE("Key-CRONO-",A17)</f>
         <v>Key-CRONO-17</v>
       </c>
-      <c r="Y17" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z17" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA17" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB17" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC17" s="74" t="s">
+      <c r="Y17" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z17" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA17" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB17" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC17" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD17" s="72" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="68">
         <v>18</v>
       </c>
@@ -6141,23 +6244,26 @@
         <f t="shared" si="3"/>
         <v>Key-CRONO-18</v>
       </c>
-      <c r="Y18" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z18" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA18" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB18" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC18" s="74" t="s">
+      <c r="Y18" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z18" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA18" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB18" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC18" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD18" s="72" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="68">
         <v>19</v>
       </c>
@@ -6238,23 +6344,26 @@
         <f t="shared" si="3"/>
         <v>Key-CRONO-19</v>
       </c>
-      <c r="Y19" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z19" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA19" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB19" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC19" s="74" t="s">
+      <c r="Y19" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z19" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA19" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB19" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC19" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD19" s="72" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="68">
         <v>20</v>
       </c>
@@ -6335,23 +6444,26 @@
         <f t="shared" si="3"/>
         <v>Key-CRONO-20</v>
       </c>
-      <c r="Y20" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z20" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA20" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB20" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC20" s="74" t="s">
+      <c r="Y20" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z20" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA20" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB20" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC20" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD20" s="72" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="68">
         <v>21</v>
       </c>
@@ -6432,23 +6544,26 @@
         <f t="shared" si="3"/>
         <v>Key-CRONO-21</v>
       </c>
-      <c r="Y21" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z21" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA21" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB21" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC21" s="74" t="s">
+      <c r="Y21" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z21" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA21" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB21" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC21" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD21" s="72" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="68">
         <v>22</v>
       </c>
@@ -6529,23 +6644,26 @@
         <f t="shared" si="3"/>
         <v>Key-CRONO-22</v>
       </c>
-      <c r="Y22" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z22" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA22" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB22" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC22" s="74" t="s">
+      <c r="Y22" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z22" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA22" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB22" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC22" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD22" s="72" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="68">
         <v>23</v>
       </c>
@@ -6626,23 +6744,26 @@
         <f t="shared" si="3"/>
         <v>Key-CRONO-23</v>
       </c>
-      <c r="Y23" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z23" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA23" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB23" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC23" s="74" t="s">
+      <c r="Y23" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z23" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA23" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB23" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC23" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD23" s="72" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="68">
         <v>24</v>
       </c>
@@ -6723,23 +6844,26 @@
         <f t="shared" si="3"/>
         <v>Key-CRONO-24</v>
       </c>
-      <c r="Y24" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z24" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA24" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB24" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC24" s="74" t="s">
+      <c r="Y24" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z24" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA24" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB24" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC24" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD24" s="72" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="68">
         <v>25</v>
       </c>
@@ -6820,23 +6944,26 @@
         <f t="shared" si="3"/>
         <v>Key-CRONO-25</v>
       </c>
-      <c r="Y25" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z25" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA25" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB25" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC25" s="74" t="s">
+      <c r="Y25" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z25" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA25" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB25" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC25" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD25" s="72" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="68">
         <v>26</v>
       </c>
@@ -6917,23 +7044,26 @@
         <f t="shared" si="3"/>
         <v>Key-CRONO-26</v>
       </c>
-      <c r="Y26" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z26" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA26" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB26" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC26" s="74" t="s">
+      <c r="Y26" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z26" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA26" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB26" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC26" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD26" s="72" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="68">
         <v>27</v>
       </c>
@@ -7014,23 +7144,26 @@
         <f t="shared" si="3"/>
         <v>Key-CRONO-27</v>
       </c>
-      <c r="Y27" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z27" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA27" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB27" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC27" s="74" t="s">
+      <c r="Y27" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z27" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA27" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB27" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC27" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD27" s="72" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="68">
         <v>28</v>
       </c>
@@ -7111,23 +7244,26 @@
         <f t="shared" si="3"/>
         <v>Key-CRONO-28</v>
       </c>
-      <c r="Y28" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z28" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA28" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB28" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC28" s="74" t="s">
+      <c r="Y28" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z28" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA28" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB28" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC28" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD28" s="72" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="68">
         <v>29</v>
       </c>
@@ -7208,23 +7344,26 @@
         <f t="shared" si="3"/>
         <v>Key-CRONO-29</v>
       </c>
-      <c r="Y29" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z29" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA29" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB29" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC29" s="74" t="s">
+      <c r="Y29" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z29" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA29" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB29" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC29" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD29" s="72" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="68">
         <v>30</v>
       </c>
@@ -7305,23 +7444,26 @@
         <f t="shared" si="3"/>
         <v>Key-CRONO-30</v>
       </c>
-      <c r="Y30" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z30" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA30" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB30" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC30" s="74" t="s">
+      <c r="Y30" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z30" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA30" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB30" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC30" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD30" s="72" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="68">
         <v>31</v>
       </c>
@@ -7402,23 +7544,26 @@
         <f t="shared" si="3"/>
         <v>Key-CRONO-31</v>
       </c>
-      <c r="Y31" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z31" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA31" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB31" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC31" s="74" t="s">
+      <c r="Y31" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z31" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA31" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB31" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC31" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD31" s="72" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="68">
         <v>32</v>
       </c>
@@ -7499,23 +7644,26 @@
         <f t="shared" si="3"/>
         <v>Key-CRONO-32</v>
       </c>
-      <c r="Y32" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z32" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA32" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB32" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC32" s="74" t="s">
+      <c r="Y32" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z32" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA32" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB32" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC32" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD32" s="72" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="68">
         <v>33</v>
       </c>
@@ -7596,23 +7744,26 @@
         <f t="shared" si="3"/>
         <v>Key-CRONO-33</v>
       </c>
-      <c r="Y33" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z33" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA33" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB33" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC33" s="74" t="s">
+      <c r="Y33" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z33" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA33" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB33" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC33" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD33" s="72" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="68">
         <v>34</v>
       </c>
@@ -7693,23 +7844,26 @@
         <f t="shared" si="3"/>
         <v>Key-CRONO-34</v>
       </c>
-      <c r="Y34" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z34" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA34" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB34" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC34" s="74" t="s">
+      <c r="Y34" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z34" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA34" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB34" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC34" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD34" s="72" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="68">
         <v>35</v>
       </c>
@@ -7790,23 +7944,26 @@
         <f t="shared" si="3"/>
         <v>Key-CRONO-35</v>
       </c>
-      <c r="Y35" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z35" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA35" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB35" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC35" s="74" t="s">
+      <c r="Y35" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z35" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA35" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB35" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC35" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD35" s="72" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="68">
         <v>36</v>
       </c>
@@ -7887,23 +8044,26 @@
         <f t="shared" si="3"/>
         <v>Key-CRONO-36</v>
       </c>
-      <c r="Y36" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z36" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA36" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB36" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC36" s="74" t="s">
+      <c r="Y36" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z36" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA36" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB36" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC36" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD36" s="72" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="68">
         <v>37</v>
       </c>
@@ -7984,23 +8144,26 @@
         <f t="shared" si="3"/>
         <v>Key-CRONO-37</v>
       </c>
-      <c r="Y37" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z37" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA37" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB37" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC37" s="74" t="s">
+      <c r="Y37" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z37" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA37" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB37" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC37" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD37" s="72" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="68">
         <v>38</v>
       </c>
@@ -8081,23 +8244,26 @@
         <f t="shared" si="3"/>
         <v>Key-CRONO-38</v>
       </c>
-      <c r="Y38" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z38" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA38" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB38" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC38" s="74" t="s">
+      <c r="Y38" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z38" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA38" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB38" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC38" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD38" s="72" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="68">
         <v>39</v>
       </c>
@@ -8178,23 +8344,26 @@
         <f t="shared" si="3"/>
         <v>Key-CRONO-39</v>
       </c>
-      <c r="Y39" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z39" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA39" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB39" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC39" s="74" t="s">
+      <c r="Y39" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z39" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA39" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB39" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC39" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD39" s="72" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="68">
         <v>40</v>
       </c>
@@ -8275,23 +8444,26 @@
         <f t="shared" si="3"/>
         <v>Key-CRONO-40</v>
       </c>
-      <c r="Y40" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z40" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA40" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB40" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC40" s="74" t="s">
+      <c r="Y40" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z40" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA40" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB40" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC40" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD40" s="72" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="68">
         <v>41</v>
       </c>
@@ -8372,23 +8544,26 @@
         <f t="shared" si="3"/>
         <v>Key-CRONO-41</v>
       </c>
-      <c r="Y41" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z41" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA41" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB41" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC41" s="74" t="s">
+      <c r="Y41" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z41" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA41" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB41" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC41" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD41" s="72" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="68">
         <v>42</v>
       </c>
@@ -8469,23 +8644,26 @@
         <f t="shared" si="3"/>
         <v>Key-CRONO-42</v>
       </c>
-      <c r="Y42" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z42" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA42" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB42" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC42" s="74" t="s">
+      <c r="Y42" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z42" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA42" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB42" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC42" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD42" s="72" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="68">
         <v>43</v>
       </c>
@@ -8566,23 +8744,26 @@
         <f t="shared" si="3"/>
         <v>Key-CRONO-43</v>
       </c>
-      <c r="Y43" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z43" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA43" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB43" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC43" s="74" t="s">
+      <c r="Y43" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z43" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA43" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB43" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC43" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD43" s="72" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="68">
         <v>44</v>
       </c>
@@ -8663,23 +8844,26 @@
         <f t="shared" si="3"/>
         <v>Key-CRONO-44</v>
       </c>
-      <c r="Y44" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z44" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA44" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB44" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC44" s="74" t="s">
+      <c r="Y44" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z44" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA44" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB44" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC44" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD44" s="72" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="68">
         <v>45</v>
       </c>
@@ -8760,23 +8944,26 @@
         <f t="shared" si="3"/>
         <v>Key-CRONO-45</v>
       </c>
-      <c r="Y45" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z45" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA45" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB45" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC45" s="74" t="s">
+      <c r="Y45" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z45" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA45" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB45" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC45" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD45" s="72" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="68">
         <v>46</v>
       </c>
@@ -8858,58 +9045,61 @@
         <f t="shared" si="3"/>
         <v>Key-CRONO-46</v>
       </c>
-      <c r="Y46" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z46" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA46" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB46" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC46" s="74" t="s">
+      <c r="Y46" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z46" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA46" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB46" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC46" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD46" s="72" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:29" s="75" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:30" s="73" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="68">
         <v>47</v>
       </c>
-      <c r="B47" s="70" t="s">
+      <c r="B47" s="82" t="s">
         <v>508</v>
       </c>
-      <c r="C47" s="71" t="s">
+      <c r="C47" s="83" t="s">
         <v>520</v>
       </c>
-      <c r="D47" s="71" t="s">
+      <c r="D47" s="83" t="s">
         <v>522</v>
       </c>
-      <c r="E47" s="71" t="s">
+      <c r="E47" s="83" t="s">
         <v>521</v>
       </c>
-      <c r="F47" s="71" t="s">
-        <v>523</v>
-      </c>
-      <c r="G47" s="72" t="s">
-        <v>1</v>
-      </c>
-      <c r="H47" s="72" t="s">
-        <v>1</v>
-      </c>
-      <c r="I47" s="72" t="s">
-        <v>1</v>
-      </c>
-      <c r="J47" s="72" t="s">
-        <v>1</v>
-      </c>
-      <c r="K47" s="72" t="s">
+      <c r="F47" s="83" t="s">
+        <v>544</v>
+      </c>
+      <c r="G47" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="H47" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="I47" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="J47" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="K47" s="70" t="s">
         <v>1</v>
       </c>
       <c r="L47" s="59" t="str">
-        <f t="shared" ref="L47:O47" si="31">SUBSTITUTE(CONCATENATE("", C47), ".", " ")</f>
+        <f t="shared" ref="L47:O51" si="31">SUBSTITUTE(CONCATENATE("", C47), ".", " ")</f>
         <v>De API</v>
       </c>
       <c r="M47" s="59" t="str">
@@ -8922,29 +9112,29 @@
       </c>
       <c r="O47" s="59" t="str">
         <f t="shared" si="31"/>
-        <v>API Revit</v>
+        <v>Função Auxiliar</v>
       </c>
       <c r="P47" s="52" t="s">
-        <v>524</v>
+        <v>545</v>
       </c>
       <c r="Q47" s="52" t="s">
-        <v>525</v>
+        <v>546</v>
       </c>
       <c r="R47" s="52" t="s">
-        <v>526</v>
+        <v>547</v>
       </c>
       <c r="S47" s="52" t="s">
         <v>1</v>
       </c>
       <c r="T47" s="52" t="str">
-        <f t="shared" ref="T47:V47" si="32">SUBSTITUTE(C47, ".", " ")</f>
+        <f t="shared" ref="T47:V51" si="32">SUBSTITUTE(C47, ".", " ")</f>
         <v>De API</v>
       </c>
       <c r="U47" s="52" t="str">
         <f t="shared" si="32"/>
         <v>Macros</v>
       </c>
-      <c r="V47" s="73" t="str">
+      <c r="V47" s="71" t="str">
         <f t="shared" si="32"/>
         <v>Métodos</v>
       </c>
@@ -8952,52 +9142,453 @@
         <v>179</v>
       </c>
       <c r="X47" s="63" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="X47:X51" si="33">CONCATENATE("Key-CRONO-",A47)</f>
         <v>Key-CRONO-47</v>
       </c>
-      <c r="Y47" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z47" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA47" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB47" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC47" s="74" t="s">
+      <c r="Y47" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z47" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA47" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB47" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC47" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD47" s="72" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:30" s="73" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="68">
+        <v>48</v>
+      </c>
+      <c r="B48" s="82" t="s">
+        <v>508</v>
+      </c>
+      <c r="C48" s="83" t="s">
+        <v>520</v>
+      </c>
+      <c r="D48" s="83" t="s">
+        <v>522</v>
+      </c>
+      <c r="E48" s="83" t="s">
+        <v>521</v>
+      </c>
+      <c r="F48" s="83" t="s">
+        <v>548</v>
+      </c>
+      <c r="G48" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="H48" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="I48" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="J48" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="K48" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="L48" s="59" t="str">
+        <f t="shared" si="31"/>
+        <v>De API</v>
+      </c>
+      <c r="M48" s="59" t="str">
+        <f t="shared" si="31"/>
+        <v>Macros</v>
+      </c>
+      <c r="N48" s="59" t="str">
+        <f t="shared" si="31"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O48" s="59" t="str">
+        <f t="shared" si="31"/>
+        <v>Função Global</v>
+      </c>
+      <c r="P48" s="52" t="s">
+        <v>549</v>
+      </c>
+      <c r="Q48" s="52" t="s">
+        <v>550</v>
+      </c>
+      <c r="R48" s="52" t="s">
+        <v>551</v>
+      </c>
+      <c r="S48" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="T48" s="52" t="str">
+        <f t="shared" si="32"/>
+        <v>De API</v>
+      </c>
+      <c r="U48" s="52" t="str">
+        <f t="shared" si="32"/>
+        <v>Macros</v>
+      </c>
+      <c r="V48" s="71" t="str">
+        <f t="shared" si="32"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W48" s="52" t="s">
+        <v>179</v>
+      </c>
+      <c r="X48" s="63" t="str">
+        <f t="shared" si="33"/>
+        <v>Key-CRONO-48</v>
+      </c>
+      <c r="Y48" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z48" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA48" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB48" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC48" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD48" s="72" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:30" s="73" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="68">
+        <v>49</v>
+      </c>
+      <c r="B49" s="82" t="s">
+        <v>508</v>
+      </c>
+      <c r="C49" s="83" t="s">
+        <v>520</v>
+      </c>
+      <c r="D49" s="83" t="s">
+        <v>522</v>
+      </c>
+      <c r="E49" s="83" t="s">
+        <v>521</v>
+      </c>
+      <c r="F49" s="83" t="s">
+        <v>552</v>
+      </c>
+      <c r="G49" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="H49" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="I49" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="J49" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="K49" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="L49" s="59" t="str">
+        <f t="shared" si="31"/>
+        <v>De API</v>
+      </c>
+      <c r="M49" s="59" t="str">
+        <f t="shared" si="31"/>
+        <v>Macros</v>
+      </c>
+      <c r="N49" s="59" t="str">
+        <f t="shared" si="31"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O49" s="59" t="str">
+        <f t="shared" si="31"/>
+        <v>Função Local</v>
+      </c>
+      <c r="P49" s="52" t="s">
+        <v>553</v>
+      </c>
+      <c r="Q49" s="52" t="s">
+        <v>554</v>
+      </c>
+      <c r="R49" s="52" t="s">
+        <v>555</v>
+      </c>
+      <c r="S49" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="T49" s="52" t="str">
+        <f t="shared" si="32"/>
+        <v>De API</v>
+      </c>
+      <c r="U49" s="52" t="str">
+        <f t="shared" si="32"/>
+        <v>Macros</v>
+      </c>
+      <c r="V49" s="71" t="str">
+        <f t="shared" si="32"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W49" s="52" t="s">
+        <v>179</v>
+      </c>
+      <c r="X49" s="63" t="str">
+        <f t="shared" si="33"/>
+        <v>Key-CRONO-49</v>
+      </c>
+      <c r="Y49" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z49" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA49" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB49" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC49" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD49" s="72" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:30" s="73" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="68">
+        <v>50</v>
+      </c>
+      <c r="B50" s="82" t="s">
+        <v>508</v>
+      </c>
+      <c r="C50" s="83" t="s">
+        <v>520</v>
+      </c>
+      <c r="D50" s="83" t="s">
+        <v>522</v>
+      </c>
+      <c r="E50" s="83" t="s">
+        <v>521</v>
+      </c>
+      <c r="F50" s="83" t="s">
+        <v>556</v>
+      </c>
+      <c r="G50" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="H50" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="I50" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="J50" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="K50" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="L50" s="59" t="str">
+        <f t="shared" si="31"/>
+        <v>De API</v>
+      </c>
+      <c r="M50" s="59" t="str">
+        <f t="shared" si="31"/>
+        <v>Macros</v>
+      </c>
+      <c r="N50" s="59" t="str">
+        <f t="shared" si="31"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O50" s="59" t="str">
+        <f t="shared" si="31"/>
+        <v>Função Filtro</v>
+      </c>
+      <c r="P50" s="52" t="s">
+        <v>557</v>
+      </c>
+      <c r="Q50" s="52" t="s">
+        <v>558</v>
+      </c>
+      <c r="R50" s="52" t="s">
+        <v>559</v>
+      </c>
+      <c r="S50" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="T50" s="52" t="str">
+        <f t="shared" si="32"/>
+        <v>De API</v>
+      </c>
+      <c r="U50" s="52" t="str">
+        <f t="shared" si="32"/>
+        <v>Macros</v>
+      </c>
+      <c r="V50" s="71" t="str">
+        <f t="shared" si="32"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W50" s="52" t="s">
+        <v>179</v>
+      </c>
+      <c r="X50" s="63" t="str">
+        <f t="shared" si="33"/>
+        <v>Key-CRONO-50</v>
+      </c>
+      <c r="Y50" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z50" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA50" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB50" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC50" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD50" s="72" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:30" s="73" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="68">
+        <v>51</v>
+      </c>
+      <c r="B51" s="82" t="s">
+        <v>508</v>
+      </c>
+      <c r="C51" s="83" t="s">
+        <v>520</v>
+      </c>
+      <c r="D51" s="83" t="s">
+        <v>522</v>
+      </c>
+      <c r="E51" s="83" t="s">
+        <v>560</v>
+      </c>
+      <c r="F51" s="83" t="s">
+        <v>561</v>
+      </c>
+      <c r="G51" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="H51" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="I51" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="J51" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="K51" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="L51" s="59" t="str">
+        <f t="shared" si="31"/>
+        <v>De API</v>
+      </c>
+      <c r="M51" s="59" t="str">
+        <f t="shared" si="31"/>
+        <v>Macros</v>
+      </c>
+      <c r="N51" s="59" t="str">
+        <f t="shared" si="31"/>
+        <v>Códigos Visuais</v>
+      </c>
+      <c r="O51" s="59" t="str">
+        <f t="shared" si="31"/>
+        <v>Bloco de Código</v>
+      </c>
+      <c r="P51" s="52" t="s">
+        <v>562</v>
+      </c>
+      <c r="Q51" s="52" t="s">
+        <v>563</v>
+      </c>
+      <c r="R51" s="52" t="s">
+        <v>564</v>
+      </c>
+      <c r="S51" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="T51" s="52" t="str">
+        <f t="shared" si="32"/>
+        <v>De API</v>
+      </c>
+      <c r="U51" s="52" t="str">
+        <f t="shared" si="32"/>
+        <v>Macros</v>
+      </c>
+      <c r="V51" s="71" t="str">
+        <f t="shared" si="32"/>
+        <v>Códigos Visuais</v>
+      </c>
+      <c r="W51" s="52" t="s">
+        <v>179</v>
+      </c>
+      <c r="X51" s="63" t="str">
+        <f t="shared" si="33"/>
+        <v>Key-CRONO-51</v>
+      </c>
+      <c r="Y51" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z51" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA51" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB51" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC51" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD51" s="72" t="s">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:B47">
-    <cfRule type="cellIs" dxfId="21" priority="2" operator="equal">
+  <conditionalFormatting sqref="A2:B51">
+    <cfRule type="cellIs" dxfId="21" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="E51:F51">
+    <cfRule type="duplicateValues" dxfId="20" priority="2"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F1:F39">
-    <cfRule type="duplicateValues" dxfId="20" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F46">
-    <cfRule type="duplicateValues" dxfId="19" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="31"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F47">
-    <cfRule type="duplicateValues" dxfId="18" priority="3"/>
+  <conditionalFormatting sqref="F47:F50">
+    <cfRule type="duplicateValues" dxfId="17" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1:R45">
-    <cfRule type="cellIs" dxfId="17" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R47">
-    <cfRule type="cellIs" dxfId="16" priority="1" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="W2:W46">
-    <cfRule type="cellIs" dxfId="15" priority="11" operator="equal">
+  <conditionalFormatting sqref="W2:W51">
+    <cfRule type="cellIs" dxfId="15" priority="14" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9011,15 +9602,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{402BD1C2-A59C-4020-8FC9-E5402FE7B33F}">
   <dimension ref="A1:U3"/>
-  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.84375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="10" width="5.84375" style="2" customWidth="1"/>
-    <col min="11" max="21" width="5.84375" style="5" customWidth="1"/>
-    <col min="22" max="16384" width="11.15234375" style="5"/>
+    <col min="1" max="1" width="2.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="10" width="5.85546875" style="2" customWidth="1"/>
+    <col min="11" max="21" width="5.85546875" style="5" customWidth="1"/>
+    <col min="22" max="16384" width="11.140625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="3" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" s="3" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="43" t="s">
         <v>22</v>
       </c>
@@ -9084,7 +9675,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="43">
         <v>2</v>
       </c>
@@ -9149,7 +9740,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="43">
         <v>3</v>
       </c>
@@ -9229,14 +9820,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C7BFE13-E93E-488C-9C8F-4E4982DFBAE7}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.3046875" customWidth="1"/>
-    <col min="2" max="2" width="6.69140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.28515625" customWidth="1"/>
+    <col min="2" max="2" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="41">
         <v>1</v>
       </c>
@@ -9247,7 +9838,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="19">
         <v>2</v>
       </c>
@@ -9258,7 +9849,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="19">
         <v>3</v>
       </c>
@@ -9269,7 +9860,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="19">
         <v>4</v>
       </c>
@@ -9293,46 +9884,46 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5087910E-DA31-4318-A539-726BE963325D}">
   <dimension ref="A1:AI89"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="7.4" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="7.35" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.53515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.69140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.84375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.53515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.15234375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.3046875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="3.3828125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.3046875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="3.3828125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.3046875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="3.3828125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.3046875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="3.3828125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="3.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="3.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="3.42578125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="6" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="49" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="4.3046875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.69140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="7.53515625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="9.3828125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="4.3046875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="3.3828125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="4.3046875" style="58" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.84375" style="58" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="5.3046875" style="58" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.3046875" style="58" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="4.3046875" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="3.3828125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="4.3046875" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="3.3828125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="4.3046875" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="3.3828125" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="4.3046875" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="3.3828125" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="4.3046875" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="3.3828125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="3.42578125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.28515625" style="58" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.85546875" style="58" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.28515625" style="58" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.28515625" style="58" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="3.42578125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="3.42578125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="3.42578125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="3.42578125" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="3.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:35" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="39" t="s">
         <v>182</v>
       </c>
@@ -9439,8 +10030,8 @@
         <v>184</v>
       </c>
     </row>
-    <row r="2" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="83">
+    <row r="2" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="81">
         <v>2</v>
       </c>
       <c r="B2" s="48" t="s">
@@ -9546,8 +10137,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="83">
+    <row r="3" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="81">
         <v>3</v>
       </c>
       <c r="B3" s="48" t="s">
@@ -9653,8 +10244,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="83">
+    <row r="4" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="81">
         <v>4</v>
       </c>
       <c r="B4" s="48" t="s">
@@ -9760,8 +10351,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="83">
+    <row r="5" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="81">
         <v>5</v>
       </c>
       <c r="B5" s="48" t="s">
@@ -9867,8 +10458,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="83">
+    <row r="6" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="81">
         <v>6</v>
       </c>
       <c r="B6" s="35" t="s">
@@ -9974,8 +10565,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="83">
+    <row r="7" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="81">
         <v>7</v>
       </c>
       <c r="B7" s="35" t="s">
@@ -10081,8 +10672,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="83">
+    <row r="8" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="81">
         <v>8</v>
       </c>
       <c r="B8" s="32" t="s">
@@ -10188,8 +10779,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="83">
+    <row r="9" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="81">
         <v>9</v>
       </c>
       <c r="B9" s="32" t="s">
@@ -10295,8 +10886,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="83">
+    <row r="10" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="81">
         <v>10</v>
       </c>
       <c r="B10" s="37" t="s">
@@ -10402,8 +10993,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="83">
+    <row r="11" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="81">
         <v>11</v>
       </c>
       <c r="B11" s="37" t="s">
@@ -10509,8 +11100,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="83">
+    <row r="12" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="81">
         <v>12</v>
       </c>
       <c r="B12" s="32" t="s">
@@ -10616,8 +11207,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="83">
+    <row r="13" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="81">
         <v>13</v>
       </c>
       <c r="B13" s="32" t="s">
@@ -10723,8 +11314,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="83">
+    <row r="14" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="81">
         <v>14</v>
       </c>
       <c r="B14" s="48" t="s">
@@ -10830,8 +11421,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="83">
+    <row r="15" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="81">
         <v>15</v>
       </c>
       <c r="B15" s="48" t="s">
@@ -10937,8 +11528,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="83">
+    <row r="16" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="81">
         <v>16</v>
       </c>
       <c r="B16" s="48" t="s">
@@ -11044,8 +11635,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="83">
+    <row r="17" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="81">
         <v>17</v>
       </c>
       <c r="B17" s="48" t="s">
@@ -11151,8 +11742,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="83">
+    <row r="18" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="81">
         <v>18</v>
       </c>
       <c r="B18" s="48" t="s">
@@ -11258,8 +11849,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="83">
+    <row r="19" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="81">
         <v>19</v>
       </c>
       <c r="B19" s="48" t="s">
@@ -11365,8 +11956,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="83">
+    <row r="20" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="81">
         <v>20</v>
       </c>
       <c r="B20" s="48" t="s">
@@ -11472,8 +12063,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="83">
+    <row r="21" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="81">
         <v>21</v>
       </c>
       <c r="B21" s="37" t="s">
@@ -11579,8 +12170,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="83">
+    <row r="22" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="81">
         <v>22</v>
       </c>
       <c r="B22" s="37" t="s">
@@ -11686,8 +12277,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="83">
+    <row r="23" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="81">
         <v>23</v>
       </c>
       <c r="B23" s="38" t="s">
@@ -11793,8 +12384,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="83">
+    <row r="24" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="81">
         <v>24</v>
       </c>
       <c r="B24" s="38" t="s">
@@ -11900,8 +12491,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="83">
+    <row r="25" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="81">
         <v>25</v>
       </c>
       <c r="B25" s="38" t="s">
@@ -12007,8 +12598,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="83">
+    <row r="26" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="81">
         <v>26</v>
       </c>
       <c r="B26" s="37" t="s">
@@ -12114,8 +12705,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="83">
+    <row r="27" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="81">
         <v>27</v>
       </c>
       <c r="B27" s="37" t="s">
@@ -12221,8 +12812,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="83">
+    <row r="28" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="81">
         <v>28</v>
       </c>
       <c r="B28" s="37" t="s">
@@ -12328,8 +12919,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="83">
+    <row r="29" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="81">
         <v>29</v>
       </c>
       <c r="B29" s="37" t="s">
@@ -12435,8 +13026,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="83">
+    <row r="30" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="81">
         <v>30</v>
       </c>
       <c r="B30" s="37" t="s">
@@ -12542,8 +13133,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="83">
+    <row r="31" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="81">
         <v>31</v>
       </c>
       <c r="B31" s="37" t="s">
@@ -12649,8 +13240,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="83">
+    <row r="32" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="81">
         <v>32</v>
       </c>
       <c r="B32" s="37" t="s">
@@ -12756,8 +13347,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="83">
+    <row r="33" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="81">
         <v>33</v>
       </c>
       <c r="B33" s="37" t="s">
@@ -12863,8 +13454,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="83">
+    <row r="34" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="81">
         <v>34</v>
       </c>
       <c r="B34" s="37" t="s">
@@ -12970,8 +13561,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="83">
+    <row r="35" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="81">
         <v>35</v>
       </c>
       <c r="B35" s="37" t="s">
@@ -13077,8 +13668,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="83">
+    <row r="36" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="81">
         <v>36</v>
       </c>
       <c r="B36" s="37" t="s">
@@ -13184,8 +13775,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="83">
+    <row r="37" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="81">
         <v>37</v>
       </c>
       <c r="B37" s="37" t="s">
@@ -13291,8 +13882,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="83">
+    <row r="38" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="81">
         <v>38</v>
       </c>
       <c r="B38" s="37" t="s">
@@ -13398,8 +13989,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="83">
+    <row r="39" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="81">
         <v>39</v>
       </c>
       <c r="B39" s="36" t="s">
@@ -13505,8 +14096,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="83">
+    <row r="40" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="81">
         <v>40</v>
       </c>
       <c r="B40" s="32" t="s">
@@ -13612,8 +14203,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="83">
+    <row r="41" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="81">
         <v>41</v>
       </c>
       <c r="B41" s="32" t="s">
@@ -13719,8 +14310,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="83">
+    <row r="42" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="81">
         <v>42</v>
       </c>
       <c r="B42" s="32" t="s">
@@ -13826,8 +14417,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="83">
+    <row r="43" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="81">
         <v>43</v>
       </c>
       <c r="B43" s="37" t="s">
@@ -13933,8 +14524,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="83">
+    <row r="44" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="81">
         <v>44</v>
       </c>
       <c r="B44" s="37" t="s">
@@ -14040,8 +14631,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A45" s="83">
+    <row r="45" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="81">
         <v>45</v>
       </c>
       <c r="B45" s="37" t="s">
@@ -14147,8 +14738,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A46" s="83">
+    <row r="46" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="81">
         <v>46</v>
       </c>
       <c r="B46" s="37" t="s">
@@ -14254,8 +14845,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A47" s="83">
+    <row r="47" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="81">
         <v>47</v>
       </c>
       <c r="B47" s="37" t="s">
@@ -14361,8 +14952,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A48" s="83">
+    <row r="48" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="81">
         <v>48</v>
       </c>
       <c r="B48" s="37" t="s">
@@ -14468,8 +15059,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="83">
+    <row r="49" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="81">
         <v>49</v>
       </c>
       <c r="B49" s="37" t="s">
@@ -14575,8 +15166,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="83">
+    <row r="50" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="81">
         <v>50</v>
       </c>
       <c r="B50" s="48" t="s">
@@ -14682,8 +15273,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A51" s="83">
+    <row r="51" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="81">
         <v>51</v>
       </c>
       <c r="B51" s="48" t="s">
@@ -14789,8 +15380,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A52" s="83">
+    <row r="52" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="81">
         <v>52</v>
       </c>
       <c r="B52" s="48" t="s">
@@ -14896,8 +15487,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="83">
+    <row r="53" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="81">
         <v>53</v>
       </c>
       <c r="B53" s="48" t="s">
@@ -15003,8 +15594,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A54" s="83">
+    <row r="54" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="81">
         <v>54</v>
       </c>
       <c r="B54" s="48" t="s">
@@ -15110,8 +15701,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A55" s="83">
+    <row r="55" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="81">
         <v>55</v>
       </c>
       <c r="B55" s="48" t="s">
@@ -15217,8 +15808,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A56" s="83">
+    <row r="56" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="81">
         <v>56</v>
       </c>
       <c r="B56" s="48" t="s">
@@ -15324,8 +15915,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A57" s="83">
+    <row r="57" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="81">
         <v>57</v>
       </c>
       <c r="B57" s="48" t="s">
@@ -15431,8 +16022,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A58" s="83">
+    <row r="58" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="81">
         <v>58</v>
       </c>
       <c r="B58" s="48" t="s">
@@ -15538,8 +16129,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A59" s="83">
+    <row r="59" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="81">
         <v>59</v>
       </c>
       <c r="B59" s="48" t="s">
@@ -15645,8 +16236,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A60" s="83">
+    <row r="60" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="81">
         <v>60</v>
       </c>
       <c r="B60" s="48" t="s">
@@ -15752,8 +16343,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A61" s="83">
+    <row r="61" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="81">
         <v>61</v>
       </c>
       <c r="B61" s="48" t="s">
@@ -15859,8 +16450,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A62" s="83">
+    <row r="62" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="81">
         <v>62</v>
       </c>
       <c r="B62" s="37" t="s">
@@ -15966,8 +16557,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A63" s="83">
+    <row r="63" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="81">
         <v>63</v>
       </c>
       <c r="B63" s="37" t="s">
@@ -16073,8 +16664,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A64" s="83">
+    <row r="64" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="81">
         <v>64</v>
       </c>
       <c r="B64" s="37" t="s">
@@ -16180,8 +16771,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A65" s="83">
+    <row r="65" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="81">
         <v>65</v>
       </c>
       <c r="B65" s="37" t="s">
@@ -16287,8 +16878,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A66" s="83">
+    <row r="66" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="81">
         <v>66</v>
       </c>
       <c r="B66" s="38" t="s">
@@ -16394,8 +16985,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A67" s="83">
+    <row r="67" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="81">
         <v>67</v>
       </c>
       <c r="B67" s="38" t="s">
@@ -16501,8 +17092,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A68" s="83">
+    <row r="68" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="81">
         <v>68</v>
       </c>
       <c r="B68" s="37" t="s">
@@ -16608,8 +17199,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A69" s="83">
+    <row r="69" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="81">
         <v>69</v>
       </c>
       <c r="B69" s="37" t="s">
@@ -16715,8 +17306,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A70" s="83">
+    <row r="70" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="81">
         <v>70</v>
       </c>
       <c r="B70" s="48" t="s">
@@ -16822,8 +17413,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A71" s="83">
+    <row r="71" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="81">
         <v>71</v>
       </c>
       <c r="B71" s="48" t="s">
@@ -16929,8 +17520,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A72" s="83">
+    <row r="72" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="81">
         <v>72</v>
       </c>
       <c r="B72" s="48" t="s">
@@ -17036,8 +17627,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A73" s="83">
+    <row r="73" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="81">
         <v>73</v>
       </c>
       <c r="B73" s="48" t="s">
@@ -17143,8 +17734,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A74" s="83">
+    <row r="74" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="81">
         <v>74</v>
       </c>
       <c r="B74" s="48" t="s">
@@ -17250,8 +17841,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A75" s="83">
+    <row r="75" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="81">
         <v>75</v>
       </c>
       <c r="B75" s="48" t="s">
@@ -17357,8 +17948,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A76" s="83">
+    <row r="76" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="81">
         <v>76</v>
       </c>
       <c r="B76" s="48" t="s">
@@ -17464,8 +18055,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A77" s="83">
+    <row r="77" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="81">
         <v>77</v>
       </c>
       <c r="B77" s="48" t="s">
@@ -17571,8 +18162,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A78" s="83">
+    <row r="78" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="81">
         <v>78</v>
       </c>
       <c r="B78" s="48" t="s">
@@ -17678,8 +18269,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A79" s="83">
+    <row r="79" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="81">
         <v>79</v>
       </c>
       <c r="B79" s="48" t="s">
@@ -17785,8 +18376,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A80" s="83">
+    <row r="80" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="81">
         <v>80</v>
       </c>
       <c r="B80" s="37" t="s">
@@ -17892,8 +18483,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A81" s="83">
+    <row r="81" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="81">
         <v>81</v>
       </c>
       <c r="B81" s="37" t="s">
@@ -17999,8 +18590,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A82" s="83">
+    <row r="82" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="81">
         <v>82</v>
       </c>
       <c r="B82" s="48" t="s">
@@ -18106,8 +18697,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A83" s="83">
+    <row r="83" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="81">
         <v>83</v>
       </c>
       <c r="B83" s="37" t="s">
@@ -18213,8 +18804,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:35" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A84" s="83">
+    <row r="84" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="81">
         <v>84</v>
       </c>
       <c r="B84" s="37" t="s">
@@ -18320,16 +18911,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:35" s="82" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="83">
+    <row r="85" spans="1:35" s="80" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A85" s="81">
         <v>85</v>
       </c>
-      <c r="B85" s="76" t="s">
-        <v>527</v>
-      </c>
-      <c r="C85" s="84" t="s">
+      <c r="B85" s="74" t="s">
         <v>523</v>
       </c>
+      <c r="C85" s="83" t="s">
+        <v>556</v>
+      </c>
       <c r="D85" s="29" t="s">
         <v>1</v>
       </c>
@@ -18360,11 +18951,11 @@
       <c r="M85" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="N85" s="79" t="s">
+      <c r="N85" s="77" t="s">
         <v>72</v>
       </c>
-      <c r="O85" s="78" t="s">
-        <v>530</v>
+      <c r="O85" s="76" t="s">
+        <v>526</v>
       </c>
       <c r="P85" s="30" t="s">
         <v>1</v>
@@ -18372,12 +18963,12 @@
       <c r="Q85" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="R85" s="80" t="str">
+      <c r="R85" s="78" t="str">
         <f t="shared" ref="R85:R89" si="0">IF(S85="null", "null", "método.revit")</f>
         <v>método.revit</v>
       </c>
-      <c r="S85" s="81" t="s">
-        <v>531</v>
+      <c r="S85" s="79" t="s">
+        <v>527</v>
       </c>
       <c r="T85" s="30" t="s">
         <v>1</v>
@@ -18385,58 +18976,58 @@
       <c r="U85" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="V85" s="77" t="s">
+      <c r="V85" s="75" t="s">
         <v>371</v>
       </c>
-      <c r="W85" s="78" t="s">
+      <c r="W85" s="76" t="s">
+        <v>524</v>
+      </c>
+      <c r="X85" s="75" t="s">
+        <v>373</v>
+      </c>
+      <c r="Y85" s="76" t="s">
+        <v>525</v>
+      </c>
+      <c r="Z85" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA85" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB85" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC85" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD85" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE85" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF85" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG85" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH85" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI85" s="33" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:35" s="80" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A86" s="81">
+        <v>86</v>
+      </c>
+      <c r="B86" s="74" t="s">
         <v>528</v>
       </c>
-      <c r="X85" s="77" t="s">
-        <v>373</v>
-      </c>
-      <c r="Y85" s="78" t="s">
-        <v>529</v>
-      </c>
-      <c r="Z85" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA85" s="33" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB85" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC85" s="33" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD85" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE85" s="33" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF85" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG85" s="33" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH85" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI85" s="33" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86" spans="1:35" s="82" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="83">
-        <v>86</v>
-      </c>
-      <c r="B86" s="76" t="s">
-        <v>532</v>
-      </c>
-      <c r="C86" s="84" t="s">
-        <v>523</v>
+      <c r="C86" s="83" t="s">
+        <v>556</v>
       </c>
       <c r="D86" s="29" t="s">
         <v>1</v>
@@ -18468,11 +19059,11 @@
       <c r="M86" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="N86" s="79" t="s">
+      <c r="N86" s="77" t="s">
         <v>72</v>
       </c>
-      <c r="O86" s="78" t="s">
-        <v>534</v>
+      <c r="O86" s="76" t="s">
+        <v>530</v>
       </c>
       <c r="P86" s="30" t="s">
         <v>1</v>
@@ -18480,12 +19071,12 @@
       <c r="Q86" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="R86" s="80" t="str">
+      <c r="R86" s="78" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
-      <c r="S86" s="81" t="s">
-        <v>535</v>
+      <c r="S86" s="79" t="s">
+        <v>531</v>
       </c>
       <c r="T86" s="30" t="s">
         <v>1</v>
@@ -18493,17 +19084,17 @@
       <c r="U86" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="V86" s="77" t="s">
+      <c r="V86" s="75" t="s">
         <v>371</v>
       </c>
-      <c r="W86" s="78" t="s">
-        <v>528</v>
-      </c>
-      <c r="X86" s="77" t="s">
+      <c r="W86" s="76" t="s">
+        <v>524</v>
+      </c>
+      <c r="X86" s="75" t="s">
         <v>373</v>
       </c>
-      <c r="Y86" s="78" t="s">
-        <v>533</v>
+      <c r="Y86" s="76" t="s">
+        <v>529</v>
       </c>
       <c r="Z86" s="29" t="s">
         <v>1</v>
@@ -18536,15 +19127,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:35" s="82" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="83">
+    <row r="87" spans="1:35" s="80" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A87" s="81">
         <v>87</v>
       </c>
-      <c r="B87" s="76" t="s">
-        <v>536</v>
-      </c>
-      <c r="C87" s="84" t="s">
-        <v>523</v>
+      <c r="B87" s="74" t="s">
+        <v>532</v>
+      </c>
+      <c r="C87" s="83" t="s">
+        <v>556</v>
       </c>
       <c r="D87" s="29" t="s">
         <v>1</v>
@@ -18576,11 +19167,11 @@
       <c r="M87" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="N87" s="79" t="s">
+      <c r="N87" s="77" t="s">
         <v>72</v>
       </c>
-      <c r="O87" s="78" t="s">
-        <v>538</v>
+      <c r="O87" s="76" t="s">
+        <v>534</v>
       </c>
       <c r="P87" s="30" t="s">
         <v>1</v>
@@ -18588,12 +19179,12 @@
       <c r="Q87" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="R87" s="80" t="str">
+      <c r="R87" s="78" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
-      <c r="S87" s="81" t="s">
-        <v>539</v>
+      <c r="S87" s="79" t="s">
+        <v>535</v>
       </c>
       <c r="T87" s="30" t="s">
         <v>1</v>
@@ -18601,17 +19192,17 @@
       <c r="U87" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="V87" s="77" t="s">
+      <c r="V87" s="75" t="s">
         <v>371</v>
       </c>
-      <c r="W87" s="78" t="s">
-        <v>528</v>
-      </c>
-      <c r="X87" s="77" t="s">
+      <c r="W87" s="76" t="s">
+        <v>524</v>
+      </c>
+      <c r="X87" s="75" t="s">
         <v>373</v>
       </c>
-      <c r="Y87" s="78" t="s">
-        <v>537</v>
+      <c r="Y87" s="76" t="s">
+        <v>533</v>
       </c>
       <c r="Z87" s="29" t="s">
         <v>1</v>
@@ -18644,15 +19235,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:35" s="82" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="83">
+    <row r="88" spans="1:35" s="80" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A88" s="81">
         <v>88</v>
       </c>
-      <c r="B88" s="76" t="s">
-        <v>540</v>
-      </c>
-      <c r="C88" s="84" t="s">
-        <v>523</v>
+      <c r="B88" s="74" t="s">
+        <v>536</v>
+      </c>
+      <c r="C88" s="83" t="s">
+        <v>556</v>
       </c>
       <c r="D88" s="29" t="s">
         <v>1</v>
@@ -18684,11 +19275,11 @@
       <c r="M88" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="N88" s="79" t="s">
+      <c r="N88" s="77" t="s">
         <v>72</v>
       </c>
-      <c r="O88" s="78" t="s">
-        <v>542</v>
+      <c r="O88" s="76" t="s">
+        <v>538</v>
       </c>
       <c r="P88" s="30" t="s">
         <v>1</v>
@@ -18696,12 +19287,12 @@
       <c r="Q88" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="R88" s="80" t="str">
+      <c r="R88" s="78" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
-      <c r="S88" s="81" t="s">
-        <v>543</v>
+      <c r="S88" s="79" t="s">
+        <v>539</v>
       </c>
       <c r="T88" s="30" t="s">
         <v>1</v>
@@ -18709,17 +19300,17 @@
       <c r="U88" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="V88" s="77" t="s">
+      <c r="V88" s="75" t="s">
         <v>371</v>
       </c>
-      <c r="W88" s="78" t="s">
-        <v>528</v>
-      </c>
-      <c r="X88" s="77" t="s">
+      <c r="W88" s="76" t="s">
+        <v>524</v>
+      </c>
+      <c r="X88" s="75" t="s">
         <v>373</v>
       </c>
-      <c r="Y88" s="78" t="s">
-        <v>541</v>
+      <c r="Y88" s="76" t="s">
+        <v>537</v>
       </c>
       <c r="Z88" s="29" t="s">
         <v>1</v>
@@ -18752,15 +19343,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:35" s="82" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="83">
+    <row r="89" spans="1:35" s="80" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A89" s="81">
         <v>89</v>
       </c>
-      <c r="B89" s="76" t="s">
-        <v>544</v>
-      </c>
-      <c r="C89" s="84" t="s">
-        <v>523</v>
+      <c r="B89" s="74" t="s">
+        <v>540</v>
+      </c>
+      <c r="C89" s="83" t="s">
+        <v>556</v>
       </c>
       <c r="D89" s="29" t="s">
         <v>1</v>
@@ -18792,11 +19383,11 @@
       <c r="M89" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="N89" s="79" t="s">
+      <c r="N89" s="77" t="s">
         <v>72</v>
       </c>
-      <c r="O89" s="78" t="s">
-        <v>546</v>
+      <c r="O89" s="76" t="s">
+        <v>542</v>
       </c>
       <c r="P89" s="30" t="s">
         <v>1</v>
@@ -18804,12 +19395,12 @@
       <c r="Q89" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="R89" s="80" t="str">
+      <c r="R89" s="78" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
-      <c r="S89" s="81" t="s">
-        <v>547</v>
+      <c r="S89" s="79" t="s">
+        <v>543</v>
       </c>
       <c r="T89" s="30" t="s">
         <v>1</v>
@@ -18817,17 +19408,17 @@
       <c r="U89" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="V89" s="77" t="s">
+      <c r="V89" s="75" t="s">
         <v>371</v>
       </c>
-      <c r="W89" s="78" t="s">
-        <v>528</v>
-      </c>
-      <c r="X89" s="77" t="s">
+      <c r="W89" s="76" t="s">
+        <v>524</v>
+      </c>
+      <c r="X89" s="75" t="s">
         <v>373</v>
       </c>
-      <c r="Y89" s="78" t="s">
-        <v>545</v>
+      <c r="Y89" s="76" t="s">
+        <v>541</v>
       </c>
       <c r="Z89" s="29" t="s">
         <v>1</v>
@@ -18866,35 +19457,35 @@
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="B1 B34:B35 B38:B78">
-    <cfRule type="duplicateValues" dxfId="12" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B84 B90:B1048576">
-    <cfRule type="duplicateValues" dxfId="11" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B76">
-    <cfRule type="duplicateValues" dxfId="8" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B79">
-    <cfRule type="duplicateValues" dxfId="7" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B80:B81">
-    <cfRule type="duplicateValues" dxfId="6" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B82:B84">
-    <cfRule type="duplicateValues" dxfId="5" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B85:B89">
-    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C43">
-    <cfRule type="duplicateValues" dxfId="2" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G6:G7">
-    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -18903,14 +19494,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FB56A46-58D1-419D-AFD2-969B66B932B3}">
   <dimension ref="A1:B15"/>
-  <sheetFormatPr defaultColWidth="11.3828125" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.3828125" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="61.53515625" style="6" customWidth="1"/>
-    <col min="3" max="16384" width="11.3828125" style="6"/>
+    <col min="1" max="1" width="2.42578125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="61.5703125" style="6" customWidth="1"/>
+    <col min="3" max="16384" width="11.42578125" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="8">
         <v>1</v>
       </c>
@@ -18918,7 +19509,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="30.9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" ht="33" x14ac:dyDescent="0.15">
       <c r="A2" s="8">
         <v>2</v>
       </c>
@@ -18926,7 +19517,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="30.9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" ht="33" x14ac:dyDescent="0.15">
       <c r="A3" s="8">
         <v>3</v>
       </c>
@@ -18934,7 +19525,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="38.6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" ht="41.25" x14ac:dyDescent="0.15">
       <c r="A4" s="8">
         <v>4</v>
       </c>
@@ -18942,7 +19533,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="86.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" ht="86.45" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="8">
         <v>5</v>
       </c>
@@ -18950,7 +19541,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="8">
         <v>6</v>
       </c>
@@ -18958,7 +19549,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="8">
         <v>7</v>
       </c>
@@ -18966,7 +19557,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="8">
         <v>8</v>
       </c>
@@ -18974,7 +19565,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="8">
         <v>9</v>
       </c>
@@ -18982,7 +19573,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="8">
         <v>10</v>
       </c>
@@ -18990,7 +19581,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="8">
         <v>11</v>
       </c>
@@ -18998,7 +19589,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="8">
         <v>12</v>
       </c>
@@ -19006,7 +19597,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="8">
         <v>13</v>
       </c>
@@ -19014,7 +19605,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="8">
         <v>14</v>
       </c>
@@ -19022,7 +19613,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="8">
         <v>15</v>
       </c>

--- a/Versão5/PRO/Ontologia_Crono.xlsx
+++ b/Versão5/PRO/Ontologia_Crono.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\PRO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C55A05A4-38C0-4A75-B4CE-EE557FB35245}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B518F383-801C-48B6-97DF-DB0AEF578060}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="4" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="26" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4257" uniqueCount="568">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4326" uniqueCount="614">
   <si>
     <t>Key</t>
   </si>
@@ -1685,12 +1685,6 @@
     <t>Autor</t>
   </si>
   <si>
-    <t>Edição</t>
-  </si>
-  <si>
-    <t>ISBN</t>
-  </si>
-  <si>
     <t>Observações</t>
   </si>
   <si>
@@ -1710,21 +1704,6 @@
   </si>
   <si>
     <t>Escola Politécnica da UFRJ</t>
-  </si>
-  <si>
-    <t>NormaNúmero</t>
-  </si>
-  <si>
-    <t>NormaEscopo</t>
-  </si>
-  <si>
-    <t>NormaReferência1</t>
-  </si>
-  <si>
-    <t>NormaReferência2</t>
-  </si>
-  <si>
-    <t>NormaReferência3</t>
   </si>
   <si>
     <t>DataHora</t>
@@ -2966,6 +2945,165 @@
   </si>
   <si>
     <t>API.Método.Visual</t>
+  </si>
+  <si>
+    <t>Norma-Número</t>
+  </si>
+  <si>
+    <t>Norma-Edição</t>
+  </si>
+  <si>
+    <t>Norma-ISBN</t>
+  </si>
+  <si>
+    <t>Norma-Escopo</t>
+  </si>
+  <si>
+    <t>Norma-Referência-01</t>
+  </si>
+  <si>
+    <t>Norma-Referência-02</t>
+  </si>
+  <si>
+    <t>Norma-Referência-03</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-01</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-02</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-03</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-04</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-01</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-02</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-03</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-04</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-05</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-06</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-07</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-08</t>
+  </si>
+  <si>
+    <t>Fonte-SINAPI</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-Saúde-01</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-Saúde-02</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-Saúde-03</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-Saúde-04</t>
+  </si>
+  <si>
+    <t>Fonte-NBR-01</t>
+  </si>
+  <si>
+    <t>Fonte-NBR-02</t>
+  </si>
+  <si>
+    <t>Fonte-NBR-03</t>
+  </si>
+  <si>
+    <t>Fonte-NBR-04</t>
+  </si>
+  <si>
+    <t>Fonte-NBR-05</t>
+  </si>
+  <si>
+    <t>Fonte-Bombeiros-01</t>
+  </si>
+  <si>
+    <t>https://brasil.un.org/pt-br/sdgs</t>
+  </si>
+  <si>
+    <t>https://eaesp.fgv.br/centros/centro-estudos-sustentabilidade/projetos/programa-brasileiro-ghg-protocol</t>
+  </si>
+  <si>
+    <t>https://www.gov.br/fazenda/pt-br/acesso-a-informacao/acoes-e-programas/transformacao-ecologica/transformacao-ecologica</t>
+  </si>
+  <si>
+    <t>https://www.gov.br/fazenda/pt-br/orgaos/spe/taxonomia-sustentavel-brasileira/cadernos</t>
+  </si>
+  <si>
+    <t>https://museunacional.ufrj.br/hortobotanico</t>
+  </si>
+  <si>
+    <t>https://www.embrapa.br/florestas/publicacoes</t>
+  </si>
+  <si>
+    <t>https://www.arvoresgigantes.org</t>
+  </si>
+  <si>
+    <t>https://www.scielo.br/j/abb</t>
+  </si>
+  <si>
+    <t>https://www.gov.br/inpa/pt-br/Pesquisa/colecoes/botanica</t>
+  </si>
+  <si>
+    <t>https://botanicasaopaulo.org</t>
+  </si>
+  <si>
+    <t>https://pesquisa.in.gov.br/imprensa</t>
+  </si>
+  <si>
+    <t>https://mapas.florestal.gov.br</t>
+  </si>
+  <si>
+    <t>https://www.caixa.gov.br/site/Paginas/downloads.aspx#categoria_888</t>
+  </si>
+  <si>
+    <t>https://somasus.saude.gov.br/sistema/home</t>
+  </si>
+  <si>
+    <t>https://anvisalegis.datalegis.net</t>
+  </si>
+  <si>
+    <t>RDC 611/2022. Radiologia diagnóstica. Blindagem, proteção radiológica.</t>
+  </si>
+  <si>
+    <t>RDC 222/2018. Gerenciamento de resíduos. Plano de gerenciamento obrigatório.</t>
+  </si>
+  <si>
+    <t>NBR 9050. Acessibilidade. Todos os ambientes de uso público.</t>
+  </si>
+  <si>
+    <t>NBR 7256. Climatização em EAS. Obrigatória para CC, CTI, CME, hemodinâmica.</t>
+  </si>
+  <si>
+    <t>NBR 15575. Desempenho de edificações. Conforto térmico, acústico, lumínico.</t>
+  </si>
+  <si>
+    <t>NBR 13534. Instalações elétricas em EAS. Circuitos, aterramento, emergência.</t>
+  </si>
+  <si>
+    <t>NBR 12188. Gases medicinais. Centrais, redes, pontos de uso.</t>
+  </si>
+  <si>
+    <t>Segurança contra incêndio. Varia por estado, consultar regulamento local.</t>
   </si>
 </sst>
 </file>
@@ -2975,7 +3113,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="27" x14ac:knownFonts="1">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3148,8 +3286,16 @@
       <name val="Arial Nova Cond Light"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="29">
+  <fills count="31">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3318,6 +3464,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAEAAAA"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="4">
     <border>
@@ -3367,10 +3525,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3639,55 +3798,39 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="23" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="26">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
+  <dxfs count="22">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3889,6 +4032,14 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -4206,61 +4357,61 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{612B613C-8B96-43A0-BB50-A45AC26373E3}">
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultColWidth="3.28515625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" style="12" customWidth="1"/>
-    <col min="2" max="2" width="39.85546875" style="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="50.28515625" style="12" customWidth="1"/>
     <col min="3" max="3" width="3.42578125" style="54" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="3.28515625" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="92" t="s">
         <v>137</v>
       </c>
       <c r="B1" s="13" t="s">
         <v>69</v>
       </c>
       <c r="C1" s="52" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="14" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="C2" s="53" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="C3" s="53" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="B4" s="14" t="s">
         <v>146</v>
       </c>
-      <c r="B2" s="14" t="s">
-        <v>165</v>
-      </c>
-      <c r="C2" s="53" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
-        <v>147</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>244</v>
-      </c>
-      <c r="C3" s="53" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>148</v>
-      </c>
       <c r="C4" s="53" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="14" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="16" t="s">
         <v>139</v>
       </c>
       <c r="B5" s="14" t="str">
@@ -4268,11 +4419,11 @@
         <v>BIMProp</v>
       </c>
       <c r="C5" s="53" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="14" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="16" t="s">
         <v>140</v>
       </c>
       <c r="B6" s="14" t="str">
@@ -4280,234 +4431,496 @@
         <v>BIMData</v>
       </c>
       <c r="C6" s="53" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="14" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="16" t="s">
         <v>141</v>
       </c>
       <c r="B7" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="C7" s="53" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>350</v>
+      </c>
+      <c r="C8" s="53" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="B9" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="C7" s="53" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" customFormat="1" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="16" t="s">
-        <v>142</v>
-      </c>
-      <c r="B8" s="16" t="s">
-        <v>357</v>
-      </c>
-      <c r="C8" s="53" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>151</v>
-      </c>
       <c r="C9" s="53" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="14" t="s">
-        <v>152</v>
+        <v>352</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="16" t="s">
+        <v>561</v>
       </c>
       <c r="B10" s="14" t="s">
         <v>38</v>
       </c>
       <c r="C10" s="53" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="14" t="s">
-        <v>143</v>
+        <v>352</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="16" t="s">
+        <v>562</v>
       </c>
       <c r="B11" s="14" t="s">
         <v>38</v>
       </c>
       <c r="C11" s="53" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="14" t="s">
-        <v>144</v>
+        <v>352</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="16" t="s">
+        <v>563</v>
       </c>
       <c r="B12" s="14" t="s">
         <v>38</v>
       </c>
       <c r="C12" s="53" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="14" t="s">
-        <v>153</v>
+        <v>352</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="16" t="s">
+        <v>564</v>
       </c>
       <c r="B13" s="14" t="s">
         <v>38</v>
       </c>
       <c r="C13" s="53" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="14" t="s">
-        <v>154</v>
+        <v>352</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="16" t="s">
+        <v>565</v>
       </c>
       <c r="B14" s="14" t="s">
         <v>38</v>
       </c>
       <c r="C14" s="53" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="14" t="s">
-        <v>155</v>
+        <v>352</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="16" t="s">
+        <v>566</v>
       </c>
       <c r="B15" s="14" t="s">
         <v>38</v>
       </c>
       <c r="C15" s="53" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="14" t="s">
-        <v>156</v>
+        <v>352</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="16" t="s">
+        <v>567</v>
       </c>
       <c r="B16" s="14" t="s">
         <v>38</v>
       </c>
       <c r="C16" s="53" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="14" t="s">
-        <v>145</v>
+        <v>352</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="16" t="s">
+        <v>143</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="C17" s="53" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="14" t="s">
-        <v>157</v>
+        <v>352</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="16" t="s">
+        <v>150</v>
       </c>
       <c r="B18" s="17">
         <f ca="1">NOW()</f>
-        <v>46274.375636458331</v>
+        <v>46276.436386805559</v>
       </c>
       <c r="C18" s="53" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" s="56" customFormat="1" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" s="56" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="B19" s="55" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="C19" s="53" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" s="56" customFormat="1" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="16" t="s">
-        <v>364</v>
+        <v>352</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" s="56" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="14" t="s">
+        <v>357</v>
       </c>
       <c r="B20" s="55" t="str">
         <f>_xlfn.TRANSLATE(B19,"pt","es")</f>
         <v>Traducciones integradas al español e inglés - Las traducciones deben revisarse constantemente</v>
       </c>
       <c r="C20" s="53" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" s="56" customFormat="1" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="16" t="s">
-        <v>365</v>
+        <v>353</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" s="56" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="14" t="s">
+        <v>358</v>
       </c>
       <c r="B21" s="55" t="str">
         <f>_xlfn.TRANSLATE(B19,"pt","en")</f>
         <v>Built-in Spanish and English Translations - Translations must be constantly reviewed</v>
       </c>
       <c r="C21" s="53" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="14" t="s">
-        <v>158</v>
+        <v>354</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="16" t="s">
+        <v>151</v>
       </c>
       <c r="B22" s="14" t="s">
         <v>38</v>
       </c>
       <c r="C22" s="53" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="14" t="s">
-        <v>159</v>
+        <v>352</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="16" t="s">
+        <v>152</v>
       </c>
       <c r="B23" s="14" t="s">
         <v>38</v>
       </c>
       <c r="C23" s="53" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="B24" s="18" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="C24" s="53" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="16" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="C25" s="53" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" customFormat="1" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="16" t="s">
-        <v>356</v>
+        <v>353</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="14" t="s">
+        <v>349</v>
       </c>
       <c r="B26" s="18" t="str">
         <f>_xlfn.TRANSLATE(B24,"pt","en")</f>
         <v>Formalize Concepts of Time Elements</v>
       </c>
       <c r="C26" s="53" t="s">
-        <v>361</v>
+        <v>354</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="14" t="s">
+        <v>568</v>
+      </c>
+      <c r="B27" s="93" t="s">
+        <v>591</v>
+      </c>
+      <c r="C27" s="53" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="14" t="s">
+        <v>569</v>
+      </c>
+      <c r="B28" s="94" t="s">
+        <v>592</v>
+      </c>
+      <c r="C28" s="53" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="14" t="s">
+        <v>570</v>
+      </c>
+      <c r="B29" s="94" t="s">
+        <v>593</v>
+      </c>
+      <c r="C29" s="53" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="14" t="s">
+        <v>571</v>
+      </c>
+      <c r="B30" s="95" t="s">
+        <v>594</v>
+      </c>
+      <c r="C30" s="53" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="14" t="s">
+        <v>572</v>
+      </c>
+      <c r="B31" s="96" t="s">
+        <v>595</v>
+      </c>
+      <c r="C31" s="53" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="14" t="s">
+        <v>573</v>
+      </c>
+      <c r="B32" s="96" t="s">
+        <v>596</v>
+      </c>
+      <c r="C32" s="53" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="14" t="s">
+        <v>574</v>
+      </c>
+      <c r="B33" s="96" t="s">
+        <v>597</v>
+      </c>
+      <c r="C33" s="53" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="14" t="s">
+        <v>575</v>
+      </c>
+      <c r="B34" s="97" t="s">
+        <v>598</v>
+      </c>
+      <c r="C34" s="53" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="14" t="s">
+        <v>576</v>
+      </c>
+      <c r="B35" s="97" t="s">
+        <v>599</v>
+      </c>
+      <c r="C35" s="53" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="14" t="s">
+        <v>577</v>
+      </c>
+      <c r="B36" s="96" t="s">
+        <v>600</v>
+      </c>
+      <c r="C36" s="53" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="14" t="s">
+        <v>578</v>
+      </c>
+      <c r="B37" s="97" t="s">
+        <v>601</v>
+      </c>
+      <c r="C37" s="53" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="14" t="s">
+        <v>579</v>
+      </c>
+      <c r="B38" s="96" t="s">
+        <v>602</v>
+      </c>
+      <c r="C38" s="53" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="14" t="s">
+        <v>580</v>
+      </c>
+      <c r="B39" s="98" t="s">
+        <v>603</v>
+      </c>
+      <c r="C39" s="53" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="14" t="s">
+        <v>581</v>
+      </c>
+      <c r="B40" s="98" t="s">
+        <v>604</v>
+      </c>
+      <c r="C40" s="53" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="14" t="s">
+        <v>582</v>
+      </c>
+      <c r="B41" s="99" t="s">
+        <v>605</v>
+      </c>
+      <c r="C41" s="53" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="14" t="s">
+        <v>583</v>
+      </c>
+      <c r="B42" s="100" t="s">
+        <v>606</v>
+      </c>
+      <c r="C42" s="53" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="14" t="s">
+        <v>584</v>
+      </c>
+      <c r="B43" s="100" t="s">
+        <v>607</v>
+      </c>
+      <c r="C43" s="53" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="14" t="s">
+        <v>585</v>
+      </c>
+      <c r="B44" s="100" t="s">
+        <v>608</v>
+      </c>
+      <c r="C44" s="53" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="14" t="s">
+        <v>586</v>
+      </c>
+      <c r="B45" s="100" t="s">
+        <v>609</v>
+      </c>
+      <c r="C45" s="53" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="14" t="s">
+        <v>587</v>
+      </c>
+      <c r="B46" s="100" t="s">
+        <v>610</v>
+      </c>
+      <c r="C46" s="53" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="14" t="s">
+        <v>588</v>
+      </c>
+      <c r="B47" s="100" t="s">
+        <v>611</v>
+      </c>
+      <c r="C47" s="53" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="14" t="s">
+        <v>589</v>
+      </c>
+      <c r="B48" s="100" t="s">
+        <v>612</v>
+      </c>
+      <c r="C48" s="53" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="14" t="s">
+        <v>590</v>
+      </c>
+      <c r="B49" s="100" t="s">
+        <v>613</v>
+      </c>
+      <c r="C49" s="53" t="s">
+        <v>352</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B27" r:id="rId1" xr:uid="{D0E30792-008C-41BC-8A7C-A13A5C7D4B85}"/>
+    <hyperlink ref="B29" r:id="rId2" xr:uid="{873F5974-BE60-4E64-ABE7-FFC0DAC5182F}"/>
+    <hyperlink ref="B28" r:id="rId3" xr:uid="{95A2F904-CC8C-49DE-8B10-B263A7543165}"/>
+    <hyperlink ref="B39" r:id="rId4" location="categoria_888" xr:uid="{C9D6AF56-ADDC-413C-9D69-ED0D96D0606E}"/>
+    <hyperlink ref="B40" r:id="rId5" xr:uid="{92D399BD-2356-4F38-94F1-82BC8E39B1AA}"/>
+    <hyperlink ref="B41" r:id="rId6" xr:uid="{666BF13D-CAC5-497B-8618-E8EAC2FD9909}"/>
+    <hyperlink ref="B30" r:id="rId7" xr:uid="{8D2CDE98-1D40-414A-84E2-F02F941322F1}"/>
+  </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
@@ -4545,22 +4958,22 @@
   <sheetData>
     <row r="1" spans="1:30" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="65" t="s">
+        <v>159</v>
+      </c>
+      <c r="B1" s="22" t="s">
+        <v>163</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>164</v>
+      </c>
+      <c r="D1" s="22" t="s">
+        <v>165</v>
+      </c>
+      <c r="E1" s="22" t="s">
         <v>166</v>
       </c>
-      <c r="B1" s="22" t="s">
-        <v>170</v>
-      </c>
-      <c r="C1" s="22" t="s">
-        <v>171</v>
-      </c>
-      <c r="D1" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="E1" s="22" t="s">
-        <v>173</v>
-      </c>
       <c r="F1" s="22" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="G1" s="64" t="s">
         <v>39</v>
@@ -4590,49 +5003,49 @@
         <v>44</v>
       </c>
       <c r="P1" s="23" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="Q1" s="23" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="R1" s="50" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="S1" s="90" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="T1" s="23" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="U1" s="23" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="V1" s="24" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="W1" s="23" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="X1" s="61" t="s">
         <v>0</v>
       </c>
       <c r="Y1" s="23" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="Z1" s="23" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="AA1" s="23" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="AB1" s="23" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="AC1" s="23" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="AD1" s="23" t="s">
-        <v>561</v>
+        <v>554</v>
       </c>
     </row>
     <row r="2" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
@@ -4640,16 +5053,16 @@
         <v>2</v>
       </c>
       <c r="B2" s="82" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="C2" s="83" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="D2" s="83" t="s">
+        <v>489</v>
+      </c>
+      <c r="E2" s="84" t="s">
         <v>496</v>
-      </c>
-      <c r="E2" s="84" t="s">
-        <v>503</v>
       </c>
       <c r="F2" s="85" t="s">
         <v>49</v>
@@ -4686,13 +5099,13 @@
         <v>Era</v>
       </c>
       <c r="P2" s="59" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="Q2" s="59" t="s">
+        <v>429</v>
+      </c>
+      <c r="R2" s="51" t="s">
         <v>436</v>
-      </c>
-      <c r="R2" s="51" t="s">
-        <v>443</v>
       </c>
       <c r="S2" s="80" t="s">
         <v>1</v>
@@ -4710,7 +5123,7 @@
         <v>Macroeventos</v>
       </c>
       <c r="W2" s="51" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="X2" s="62" t="str">
         <f t="shared" ref="X2:X46" si="3">CONCATENATE("Key-CRONO-",A2)</f>
@@ -4740,16 +5153,16 @@
         <v>3</v>
       </c>
       <c r="B3" s="82" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="C3" s="83" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="D3" s="83" t="s">
+        <v>489</v>
+      </c>
+      <c r="E3" s="84" t="s">
         <v>496</v>
-      </c>
-      <c r="E3" s="84" t="s">
-        <v>503</v>
       </c>
       <c r="F3" s="85" t="s">
         <v>50</v>
@@ -4786,13 +5199,13 @@
         <v>Época</v>
       </c>
       <c r="P3" s="59" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="Q3" s="59" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="R3" s="51" t="s">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="S3" s="80" t="s">
         <v>1</v>
@@ -4810,7 +5223,7 @@
         <v>Macroeventos</v>
       </c>
       <c r="W3" s="51" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="X3" s="62" t="str">
         <f t="shared" si="3"/>
@@ -4840,19 +5253,19 @@
         <v>4</v>
       </c>
       <c r="B4" s="82" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="C4" s="83" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="D4" s="83" t="s">
+        <v>489</v>
+      </c>
+      <c r="E4" s="84" t="s">
         <v>496</v>
       </c>
-      <c r="E4" s="84" t="s">
-        <v>503</v>
-      </c>
       <c r="F4" s="85" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="G4" s="63" t="s">
         <v>1</v>
@@ -4886,13 +5299,13 @@
         <v>Século</v>
       </c>
       <c r="P4" s="59" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="Q4" s="59" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="R4" s="51" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="S4" s="80" t="s">
         <v>1</v>
@@ -4910,7 +5323,7 @@
         <v>Macroeventos</v>
       </c>
       <c r="W4" s="51" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="X4" s="62" t="str">
         <f t="shared" si="3"/>
@@ -4940,19 +5353,19 @@
         <v>5</v>
       </c>
       <c r="B5" s="82" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="C5" s="83" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="D5" s="83" t="s">
+        <v>489</v>
+      </c>
+      <c r="E5" s="84" t="s">
         <v>496</v>
       </c>
-      <c r="E5" s="84" t="s">
-        <v>503</v>
-      </c>
       <c r="F5" s="85" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="G5" s="63" t="s">
         <v>1</v>
@@ -4986,13 +5399,13 @@
         <v>Quinquagenário</v>
       </c>
       <c r="P5" s="59" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="Q5" s="59" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="R5" s="51" t="s">
-        <v>445</v>
+        <v>438</v>
       </c>
       <c r="S5" s="80" t="s">
         <v>1</v>
@@ -5010,7 +5423,7 @@
         <v>Macroeventos</v>
       </c>
       <c r="W5" s="51" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="X5" s="62" t="str">
         <f t="shared" si="3"/>
@@ -5040,19 +5453,19 @@
         <v>6</v>
       </c>
       <c r="B6" s="82" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="C6" s="83" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="D6" s="83" t="s">
+        <v>489</v>
+      </c>
+      <c r="E6" s="84" t="s">
         <v>496</v>
       </c>
-      <c r="E6" s="84" t="s">
-        <v>503</v>
-      </c>
       <c r="F6" s="85" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="G6" s="63" t="s">
         <v>1</v>
@@ -5086,13 +5499,13 @@
         <v>Década</v>
       </c>
       <c r="P6" s="59" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="Q6" s="59" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="R6" s="51" t="s">
-        <v>446</v>
+        <v>439</v>
       </c>
       <c r="S6" s="80" t="s">
         <v>1</v>
@@ -5110,7 +5523,7 @@
         <v>Macroeventos</v>
       </c>
       <c r="W6" s="51" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="X6" s="62" t="str">
         <f t="shared" si="3"/>
@@ -5140,19 +5553,19 @@
         <v>7</v>
       </c>
       <c r="B7" s="82" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="C7" s="83" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="D7" s="83" t="s">
+        <v>489</v>
+      </c>
+      <c r="E7" s="84" t="s">
         <v>496</v>
       </c>
-      <c r="E7" s="84" t="s">
-        <v>503</v>
-      </c>
       <c r="F7" s="85" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="G7" s="63" t="s">
         <v>1</v>
@@ -5186,13 +5599,13 @@
         <v>Quinquênio</v>
       </c>
       <c r="P7" s="59" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="Q7" s="59" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="R7" s="51" t="s">
-        <v>447</v>
+        <v>440</v>
       </c>
       <c r="S7" s="80" t="s">
         <v>1</v>
@@ -5210,7 +5623,7 @@
         <v>Macroeventos</v>
       </c>
       <c r="W7" s="51" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="X7" s="62" t="str">
         <f t="shared" si="3"/>
@@ -5240,19 +5653,19 @@
         <v>8</v>
       </c>
       <c r="B8" s="82" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="C8" s="83" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="D8" s="83" t="s">
+        <v>489</v>
+      </c>
+      <c r="E8" s="84" t="s">
         <v>496</v>
       </c>
-      <c r="E8" s="84" t="s">
-        <v>503</v>
-      </c>
       <c r="F8" s="85" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="G8" s="63" t="s">
         <v>1</v>
@@ -5286,13 +5699,13 @@
         <v>Lustro</v>
       </c>
       <c r="P8" s="59" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="Q8" s="59" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="R8" s="51" t="s">
-        <v>447</v>
+        <v>440</v>
       </c>
       <c r="S8" s="80" t="s">
         <v>1</v>
@@ -5310,7 +5723,7 @@
         <v>Macroeventos</v>
       </c>
       <c r="W8" s="51" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="X8" s="62" t="str">
         <f t="shared" si="3"/>
@@ -5340,19 +5753,19 @@
         <v>9</v>
       </c>
       <c r="B9" s="82" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="C9" s="83" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="D9" s="83" t="s">
+        <v>489</v>
+      </c>
+      <c r="E9" s="84" t="s">
         <v>496</v>
       </c>
-      <c r="E9" s="84" t="s">
-        <v>503</v>
-      </c>
       <c r="F9" s="85" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="G9" s="63" t="s">
         <v>1</v>
@@ -5386,13 +5799,13 @@
         <v>Biênio</v>
       </c>
       <c r="P9" s="59" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="Q9" s="59" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="R9" s="51" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="S9" s="80" t="s">
         <v>1</v>
@@ -5410,7 +5823,7 @@
         <v>Macroeventos</v>
       </c>
       <c r="W9" s="51" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="X9" s="62" t="str">
         <f t="shared" si="3"/>
@@ -5440,19 +5853,19 @@
         <v>10</v>
       </c>
       <c r="B10" s="82" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="C10" s="83" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="D10" s="83" t="s">
+        <v>489</v>
+      </c>
+      <c r="E10" s="84" t="s">
         <v>496</v>
       </c>
-      <c r="E10" s="84" t="s">
-        <v>503</v>
-      </c>
       <c r="F10" s="85" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="G10" s="63" t="s">
         <v>1</v>
@@ -5486,13 +5899,13 @@
         <v>Bienal</v>
       </c>
       <c r="P10" s="59" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="Q10" s="59" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="R10" s="51" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="S10" s="80" t="s">
         <v>1</v>
@@ -5510,7 +5923,7 @@
         <v>Macroeventos</v>
       </c>
       <c r="W10" s="51" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="X10" s="62" t="str">
         <f t="shared" si="3"/>
@@ -5540,16 +5953,16 @@
         <v>11</v>
       </c>
       <c r="B11" s="82" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="C11" s="83" t="s">
+        <v>488</v>
+      </c>
+      <c r="D11" s="83" t="s">
+        <v>489</v>
+      </c>
+      <c r="E11" s="84" t="s">
         <v>495</v>
-      </c>
-      <c r="D11" s="83" t="s">
-        <v>496</v>
-      </c>
-      <c r="E11" s="84" t="s">
-        <v>502</v>
       </c>
       <c r="F11" s="85" t="s">
         <v>51</v>
@@ -5586,13 +5999,13 @@
         <v>Ano</v>
       </c>
       <c r="P11" s="59" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="Q11" s="59" t="s">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="R11" s="51" t="s">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="S11" s="80" t="s">
         <v>1</v>
@@ -5610,7 +6023,7 @@
         <v>Calendários</v>
       </c>
       <c r="W11" s="51" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="X11" s="62" t="str">
         <f t="shared" si="3"/>
@@ -5640,19 +6053,19 @@
         <v>12</v>
       </c>
       <c r="B12" s="82" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="C12" s="83" t="s">
+        <v>488</v>
+      </c>
+      <c r="D12" s="83" t="s">
+        <v>489</v>
+      </c>
+      <c r="E12" s="84" t="s">
         <v>495</v>
       </c>
-      <c r="D12" s="83" t="s">
-        <v>496</v>
-      </c>
-      <c r="E12" s="84" t="s">
-        <v>502</v>
-      </c>
       <c r="F12" s="85" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="G12" s="63" t="s">
         <v>1</v>
@@ -5686,13 +6099,13 @@
         <v>Semestre</v>
       </c>
       <c r="P12" s="59" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="Q12" s="59" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="R12" s="51" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="S12" s="80" t="s">
         <v>1</v>
@@ -5710,7 +6123,7 @@
         <v>Calendários</v>
       </c>
       <c r="W12" s="51" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="X12" s="62" t="str">
         <f t="shared" si="3"/>
@@ -5740,19 +6153,19 @@
         <v>13</v>
       </c>
       <c r="B13" s="82" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="C13" s="83" t="s">
+        <v>488</v>
+      </c>
+      <c r="D13" s="83" t="s">
+        <v>489</v>
+      </c>
+      <c r="E13" s="84" t="s">
         <v>495</v>
       </c>
-      <c r="D13" s="83" t="s">
-        <v>496</v>
-      </c>
-      <c r="E13" s="84" t="s">
-        <v>502</v>
-      </c>
       <c r="F13" s="85" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="G13" s="63" t="s">
         <v>1</v>
@@ -5786,13 +6199,13 @@
         <v>Quadrimestre</v>
       </c>
       <c r="P13" s="59" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="Q13" s="59" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="R13" s="51" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="S13" s="80" t="s">
         <v>1</v>
@@ -5810,7 +6223,7 @@
         <v>Calendários</v>
       </c>
       <c r="W13" s="51" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="X13" s="62" t="str">
         <f t="shared" si="3"/>
@@ -5840,19 +6253,19 @@
         <v>14</v>
       </c>
       <c r="B14" s="82" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="C14" s="83" t="s">
+        <v>488</v>
+      </c>
+      <c r="D14" s="83" t="s">
+        <v>489</v>
+      </c>
+      <c r="E14" s="84" t="s">
         <v>495</v>
       </c>
-      <c r="D14" s="83" t="s">
-        <v>496</v>
-      </c>
-      <c r="E14" s="84" t="s">
-        <v>502</v>
-      </c>
       <c r="F14" s="85" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="G14" s="63" t="s">
         <v>1</v>
@@ -5886,13 +6299,13 @@
         <v>Trimestre</v>
       </c>
       <c r="P14" s="59" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="Q14" s="59" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="R14" s="51" t="s">
-        <v>452</v>
+        <v>445</v>
       </c>
       <c r="S14" s="80" t="s">
         <v>1</v>
@@ -5910,7 +6323,7 @@
         <v>Calendários</v>
       </c>
       <c r="W14" s="51" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="X14" s="62" t="str">
         <f t="shared" si="3"/>
@@ -5940,16 +6353,16 @@
         <v>15</v>
       </c>
       <c r="B15" s="82" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="C15" s="83" t="s">
+        <v>488</v>
+      </c>
+      <c r="D15" s="83" t="s">
+        <v>489</v>
+      </c>
+      <c r="E15" s="84" t="s">
         <v>495</v>
-      </c>
-      <c r="D15" s="83" t="s">
-        <v>496</v>
-      </c>
-      <c r="E15" s="84" t="s">
-        <v>502</v>
       </c>
       <c r="F15" s="85" t="s">
         <v>52</v>
@@ -5986,13 +6399,13 @@
         <v>Mês</v>
       </c>
       <c r="P15" s="59" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="Q15" s="59" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="R15" s="51" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="S15" s="80" t="s">
         <v>1</v>
@@ -6010,7 +6423,7 @@
         <v>Calendários</v>
       </c>
       <c r="W15" s="51" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="X15" s="62" t="str">
         <f t="shared" si="3"/>
@@ -6040,16 +6453,16 @@
         <v>16</v>
       </c>
       <c r="B16" s="82" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="C16" s="83" t="s">
+        <v>488</v>
+      </c>
+      <c r="D16" s="83" t="s">
+        <v>489</v>
+      </c>
+      <c r="E16" s="84" t="s">
         <v>495</v>
-      </c>
-      <c r="D16" s="83" t="s">
-        <v>496</v>
-      </c>
-      <c r="E16" s="84" t="s">
-        <v>502</v>
       </c>
       <c r="F16" s="85" t="s">
         <v>53</v>
@@ -6086,13 +6499,13 @@
         <v>Semana</v>
       </c>
       <c r="P16" s="59" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="Q16" s="59" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="R16" s="51" t="s">
-        <v>454</v>
+        <v>447</v>
       </c>
       <c r="S16" s="80" t="s">
         <v>1</v>
@@ -6110,7 +6523,7 @@
         <v>Calendários</v>
       </c>
       <c r="W16" s="51" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="X16" s="62" t="str">
         <f t="shared" si="3"/>
@@ -6140,16 +6553,16 @@
         <v>17</v>
       </c>
       <c r="B17" s="82" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="C17" s="83" t="s">
+        <v>488</v>
+      </c>
+      <c r="D17" s="83" t="s">
+        <v>489</v>
+      </c>
+      <c r="E17" s="84" t="s">
         <v>495</v>
-      </c>
-      <c r="D17" s="83" t="s">
-        <v>496</v>
-      </c>
-      <c r="E17" s="84" t="s">
-        <v>502</v>
       </c>
       <c r="F17" s="85" t="s">
         <v>54</v>
@@ -6186,13 +6599,13 @@
         <v>Dia</v>
       </c>
       <c r="P17" s="59" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="Q17" s="59" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="R17" s="51" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="S17" s="80" t="s">
         <v>1</v>
@@ -6210,7 +6623,7 @@
         <v>Calendários</v>
       </c>
       <c r="W17" s="51" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="X17" s="62" t="str">
         <f t="shared" ref="X17" si="19">CONCATENATE("Key-CRONO-",A17)</f>
@@ -6240,19 +6653,19 @@
         <v>18</v>
       </c>
       <c r="B18" s="82" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="C18" s="83" t="s">
+        <v>488</v>
+      </c>
+      <c r="D18" s="83" t="s">
+        <v>489</v>
+      </c>
+      <c r="E18" s="84" t="s">
         <v>495</v>
       </c>
-      <c r="D18" s="83" t="s">
-        <v>496</v>
-      </c>
-      <c r="E18" s="84" t="s">
-        <v>502</v>
-      </c>
       <c r="F18" s="85" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="G18" s="63" t="s">
         <v>1</v>
@@ -6286,13 +6699,13 @@
         <v>Data</v>
       </c>
       <c r="P18" s="59" t="s">
-        <v>506</v>
+        <v>499</v>
       </c>
       <c r="Q18" s="59" t="s">
+        <v>500</v>
+      </c>
+      <c r="R18" s="51" t="s">
         <v>507</v>
-      </c>
-      <c r="R18" s="51" t="s">
-        <v>514</v>
       </c>
       <c r="S18" s="80" t="s">
         <v>1</v>
@@ -6310,7 +6723,7 @@
         <v>Calendários</v>
       </c>
       <c r="W18" s="51" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="X18" s="62" t="str">
         <f t="shared" si="3"/>
@@ -6340,19 +6753,19 @@
         <v>19</v>
       </c>
       <c r="B19" s="82" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="C19" s="83" t="s">
+        <v>488</v>
+      </c>
+      <c r="D19" s="83" t="s">
+        <v>489</v>
+      </c>
+      <c r="E19" s="84" t="s">
         <v>495</v>
       </c>
-      <c r="D19" s="83" t="s">
-        <v>496</v>
-      </c>
-      <c r="E19" s="84" t="s">
-        <v>502</v>
-      </c>
       <c r="F19" s="85" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="G19" s="63" t="s">
         <v>1</v>
@@ -6386,13 +6799,13 @@
         <v>Jornada</v>
       </c>
       <c r="P19" s="59" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="Q19" s="59" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="R19" s="51" t="s">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="S19" s="80" t="s">
         <v>1</v>
@@ -6410,7 +6823,7 @@
         <v>Calendários</v>
       </c>
       <c r="W19" s="51" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="X19" s="62" t="str">
         <f t="shared" si="3"/>
@@ -6440,16 +6853,16 @@
         <v>20</v>
       </c>
       <c r="B20" s="82" t="s">
+        <v>487</v>
+      </c>
+      <c r="C20" s="83" t="s">
+        <v>488</v>
+      </c>
+      <c r="D20" s="83" t="s">
+        <v>489</v>
+      </c>
+      <c r="E20" s="84" t="s">
         <v>494</v>
-      </c>
-      <c r="C20" s="83" t="s">
-        <v>495</v>
-      </c>
-      <c r="D20" s="83" t="s">
-        <v>496</v>
-      </c>
-      <c r="E20" s="84" t="s">
-        <v>501</v>
       </c>
       <c r="F20" s="85" t="s">
         <v>55</v>
@@ -6486,13 +6899,13 @@
         <v>Hora</v>
       </c>
       <c r="P20" s="59" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="Q20" s="59" t="s">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="R20" s="51" t="s">
-        <v>457</v>
+        <v>450</v>
       </c>
       <c r="S20" s="80" t="s">
         <v>1</v>
@@ -6510,7 +6923,7 @@
         <v>Horários</v>
       </c>
       <c r="W20" s="51" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="X20" s="62" t="str">
         <f t="shared" si="3"/>
@@ -6540,16 +6953,16 @@
         <v>21</v>
       </c>
       <c r="B21" s="82" t="s">
+        <v>487</v>
+      </c>
+      <c r="C21" s="83" t="s">
+        <v>488</v>
+      </c>
+      <c r="D21" s="83" t="s">
+        <v>489</v>
+      </c>
+      <c r="E21" s="84" t="s">
         <v>494</v>
-      </c>
-      <c r="C21" s="83" t="s">
-        <v>495</v>
-      </c>
-      <c r="D21" s="83" t="s">
-        <v>496</v>
-      </c>
-      <c r="E21" s="84" t="s">
-        <v>501</v>
       </c>
       <c r="F21" s="85" t="s">
         <v>56</v>
@@ -6586,13 +6999,13 @@
         <v>Minuto</v>
       </c>
       <c r="P21" s="59" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="Q21" s="59" t="s">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="R21" s="51" t="s">
-        <v>458</v>
+        <v>451</v>
       </c>
       <c r="S21" s="80" t="s">
         <v>1</v>
@@ -6610,7 +7023,7 @@
         <v>Horários</v>
       </c>
       <c r="W21" s="51" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="X21" s="62" t="str">
         <f t="shared" si="3"/>
@@ -6640,16 +7053,16 @@
         <v>22</v>
       </c>
       <c r="B22" s="82" t="s">
+        <v>487</v>
+      </c>
+      <c r="C22" s="83" t="s">
+        <v>488</v>
+      </c>
+      <c r="D22" s="83" t="s">
+        <v>489</v>
+      </c>
+      <c r="E22" s="84" t="s">
         <v>494</v>
-      </c>
-      <c r="C22" s="83" t="s">
-        <v>495</v>
-      </c>
-      <c r="D22" s="83" t="s">
-        <v>496</v>
-      </c>
-      <c r="E22" s="84" t="s">
-        <v>501</v>
       </c>
       <c r="F22" s="85" t="s">
         <v>57</v>
@@ -6686,13 +7099,13 @@
         <v>Segundo</v>
       </c>
       <c r="P22" s="59" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="Q22" s="59" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="R22" s="51" t="s">
-        <v>459</v>
+        <v>452</v>
       </c>
       <c r="S22" s="80" t="s">
         <v>1</v>
@@ -6710,7 +7123,7 @@
         <v>Horários</v>
       </c>
       <c r="W22" s="51" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="X22" s="62" t="str">
         <f t="shared" si="3"/>
@@ -6740,16 +7153,16 @@
         <v>23</v>
       </c>
       <c r="B23" s="82" t="s">
+        <v>487</v>
+      </c>
+      <c r="C23" s="83" t="s">
+        <v>488</v>
+      </c>
+      <c r="D23" s="83" t="s">
+        <v>489</v>
+      </c>
+      <c r="E23" s="84" t="s">
         <v>494</v>
-      </c>
-      <c r="C23" s="83" t="s">
-        <v>495</v>
-      </c>
-      <c r="D23" s="83" t="s">
-        <v>496</v>
-      </c>
-      <c r="E23" s="84" t="s">
-        <v>501</v>
       </c>
       <c r="F23" s="85" t="s">
         <v>58</v>
@@ -6786,13 +7199,13 @@
         <v>Milisegundo</v>
       </c>
       <c r="P23" s="59" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="Q23" s="59" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="R23" s="51" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="S23" s="80" t="s">
         <v>1</v>
@@ -6810,7 +7223,7 @@
         <v>Horários</v>
       </c>
       <c r="W23" s="51" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="X23" s="62" t="str">
         <f t="shared" si="3"/>
@@ -6840,16 +7253,16 @@
         <v>24</v>
       </c>
       <c r="B24" s="82" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="C24" s="83" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="D24" s="83" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="E24" s="84" t="s">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="F24" s="85" t="s">
         <v>59</v>
@@ -6886,13 +7299,13 @@
         <v>Pulso</v>
       </c>
       <c r="P24" s="59" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="Q24" s="59" t="s">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="R24" s="51" t="s">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="S24" s="80" t="s">
         <v>1</v>
@@ -6910,7 +7323,7 @@
         <v>Microeventos</v>
       </c>
       <c r="W24" s="51" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="X24" s="62" t="str">
         <f t="shared" si="3"/>
@@ -6940,16 +7353,16 @@
         <v>25</v>
       </c>
       <c r="B25" s="82" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="C25" s="83" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="D25" s="83" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="E25" s="84" t="s">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="F25" s="85" t="s">
         <v>60</v>
@@ -6986,13 +7399,13 @@
         <v>Tick</v>
       </c>
       <c r="P25" s="59" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="Q25" s="59" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="R25" s="51" t="s">
-        <v>461</v>
+        <v>454</v>
       </c>
       <c r="S25" s="80" t="s">
         <v>1</v>
@@ -7010,7 +7423,7 @@
         <v>Microeventos</v>
       </c>
       <c r="W25" s="51" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="X25" s="62" t="str">
         <f t="shared" si="3"/>
@@ -7040,19 +7453,19 @@
         <v>26</v>
       </c>
       <c r="B26" s="82" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="C26" s="83" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="D26" s="83" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="E26" s="84" t="s">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="F26" s="85" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="G26" s="63" t="s">
         <v>1</v>
@@ -7086,13 +7499,13 @@
         <v>Inicial</v>
       </c>
       <c r="P26" s="59" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="Q26" s="59" t="s">
-        <v>417</v>
+        <v>410</v>
       </c>
       <c r="R26" s="51" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="S26" s="80" t="s">
         <v>1</v>
@@ -7110,7 +7523,7 @@
         <v>Cronometrados</v>
       </c>
       <c r="W26" s="51" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="X26" s="62" t="str">
         <f t="shared" si="3"/>
@@ -7140,19 +7553,19 @@
         <v>27</v>
       </c>
       <c r="B27" s="82" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="C27" s="83" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="D27" s="83" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="E27" s="84" t="s">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="F27" s="85" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="G27" s="63" t="s">
         <v>1</v>
@@ -7186,13 +7599,13 @@
         <v>Parcial</v>
       </c>
       <c r="P27" s="59" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="Q27" s="59" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="R27" s="51" t="s">
-        <v>463</v>
+        <v>456</v>
       </c>
       <c r="S27" s="80" t="s">
         <v>1</v>
@@ -7210,7 +7623,7 @@
         <v>Cronometrados</v>
       </c>
       <c r="W27" s="51" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="X27" s="62" t="str">
         <f t="shared" si="3"/>
@@ -7240,19 +7653,19 @@
         <v>28</v>
       </c>
       <c r="B28" s="82" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="C28" s="83" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="D28" s="83" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="E28" s="84" t="s">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="F28" s="85" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="G28" s="63" t="s">
         <v>1</v>
@@ -7286,13 +7699,13 @@
         <v>Final</v>
       </c>
       <c r="P28" s="59" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="Q28" s="59" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="R28" s="51" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="S28" s="80" t="s">
         <v>1</v>
@@ -7310,7 +7723,7 @@
         <v>Cronometrados</v>
       </c>
       <c r="W28" s="51" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="X28" s="62" t="str">
         <f t="shared" si="3"/>
@@ -7340,16 +7753,16 @@
         <v>29</v>
       </c>
       <c r="B29" s="82" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="C29" s="83" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="D29" s="83" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="E29" s="84" t="s">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="F29" s="85" t="s">
         <v>61</v>
@@ -7386,13 +7799,13 @@
         <v>DeltaT</v>
       </c>
       <c r="P29" s="59" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="Q29" s="59" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="R29" s="51" t="s">
-        <v>465</v>
+        <v>458</v>
       </c>
       <c r="S29" s="80" t="s">
         <v>1</v>
@@ -7410,7 +7823,7 @@
         <v>Cronometrados</v>
       </c>
       <c r="W29" s="51" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="X29" s="62" t="str">
         <f t="shared" si="3"/>
@@ -7440,16 +7853,16 @@
         <v>30</v>
       </c>
       <c r="B30" s="82" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="C30" s="83" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="D30" s="83" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="E30" s="83" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="F30" s="85" t="s">
         <v>62</v>
@@ -7486,13 +7899,13 @@
         <v>Ideação</v>
       </c>
       <c r="P30" s="59" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="Q30" s="59" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="R30" s="51" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
       <c r="S30" s="80" t="s">
         <v>1</v>
@@ -7510,7 +7923,7 @@
         <v>Etapas</v>
       </c>
       <c r="W30" s="51" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="X30" s="62" t="str">
         <f t="shared" si="3"/>
@@ -7540,16 +7953,16 @@
         <v>31</v>
       </c>
       <c r="B31" s="82" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="C31" s="83" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="D31" s="83" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="E31" s="83" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="F31" s="85" t="s">
         <v>67</v>
@@ -7586,13 +7999,13 @@
         <v>Projetual</v>
       </c>
       <c r="P31" s="59" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="Q31" s="59" t="s">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="R31" s="51" t="s">
-        <v>467</v>
+        <v>460</v>
       </c>
       <c r="S31" s="80" t="s">
         <v>1</v>
@@ -7610,7 +8023,7 @@
         <v>Etapas</v>
       </c>
       <c r="W31" s="51" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="X31" s="62" t="str">
         <f t="shared" si="3"/>
@@ -7640,16 +8053,16 @@
         <v>32</v>
       </c>
       <c r="B32" s="82" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="C32" s="83" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="D32" s="83" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="E32" s="83" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="F32" s="83" t="s">
         <v>63</v>
@@ -7686,13 +8099,13 @@
         <v>Simulação</v>
       </c>
       <c r="P32" s="59" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="Q32" s="59" t="s">
-        <v>423</v>
+        <v>416</v>
       </c>
       <c r="R32" s="51" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="S32" s="80" t="s">
         <v>1</v>
@@ -7710,7 +8123,7 @@
         <v>Etapas</v>
       </c>
       <c r="W32" s="51" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="X32" s="62" t="str">
         <f t="shared" si="3"/>
@@ -7740,16 +8153,16 @@
         <v>33</v>
       </c>
       <c r="B33" s="82" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="C33" s="83" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="D33" s="83" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="E33" s="83" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="F33" s="83" t="s">
         <v>64</v>
@@ -7786,13 +8199,13 @@
         <v>Planejamento</v>
       </c>
       <c r="P33" s="59" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="Q33" s="59" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="R33" s="51" t="s">
-        <v>469</v>
+        <v>462</v>
       </c>
       <c r="S33" s="80" t="s">
         <v>1</v>
@@ -7810,7 +8223,7 @@
         <v>Etapas</v>
       </c>
       <c r="W33" s="51" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="X33" s="62" t="str">
         <f t="shared" si="3"/>
@@ -7840,16 +8253,16 @@
         <v>34</v>
       </c>
       <c r="B34" s="82" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="C34" s="83" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="D34" s="83" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="E34" s="83" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="F34" s="83" t="s">
         <v>66</v>
@@ -7886,13 +8299,13 @@
         <v>Construção</v>
       </c>
       <c r="P34" s="59" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="Q34" s="59" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="R34" s="51" t="s">
-        <v>470</v>
+        <v>463</v>
       </c>
       <c r="S34" s="80" t="s">
         <v>1</v>
@@ -7910,7 +8323,7 @@
         <v>Etapas</v>
       </c>
       <c r="W34" s="51" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="X34" s="62" t="str">
         <f t="shared" si="3"/>
@@ -7940,16 +8353,16 @@
         <v>35</v>
       </c>
       <c r="B35" s="82" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="C35" s="83" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="D35" s="83" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="E35" s="83" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="F35" s="86" t="s">
         <v>65</v>
@@ -7986,13 +8399,13 @@
         <v>Operação</v>
       </c>
       <c r="P35" s="60" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="Q35" s="59" t="s">
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="R35" s="51" t="s">
-        <v>441</v>
+        <v>434</v>
       </c>
       <c r="S35" s="80" t="s">
         <v>1</v>
@@ -8010,7 +8423,7 @@
         <v>Etapas</v>
       </c>
       <c r="W35" s="51" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="X35" s="62" t="str">
         <f t="shared" si="3"/>
@@ -8040,19 +8453,19 @@
         <v>36</v>
       </c>
       <c r="B36" s="82" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="C36" s="83" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="D36" s="83" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="E36" s="87" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="F36" s="86" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="G36" s="63" t="s">
         <v>1</v>
@@ -8086,13 +8499,13 @@
         <v>Inaugural</v>
       </c>
       <c r="P36" s="60" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="Q36" s="59" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="R36" s="51" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="S36" s="80" t="s">
         <v>1</v>
@@ -8110,7 +8523,7 @@
         <v>Históricos</v>
       </c>
       <c r="W36" s="51" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="X36" s="62" t="str">
         <f t="shared" si="3"/>
@@ -8140,19 +8553,19 @@
         <v>37</v>
       </c>
       <c r="B37" s="82" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="C37" s="83" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="D37" s="83" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="E37" s="87" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="F37" s="86" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="G37" s="63" t="s">
         <v>1</v>
@@ -8186,13 +8599,13 @@
         <v>Modernizar</v>
       </c>
       <c r="P37" s="60" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="Q37" s="59" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="R37" s="51" t="s">
-        <v>472</v>
+        <v>465</v>
       </c>
       <c r="S37" s="80" t="s">
         <v>1</v>
@@ -8210,7 +8623,7 @@
         <v>Históricos</v>
       </c>
       <c r="W37" s="51" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="X37" s="62" t="str">
         <f t="shared" si="3"/>
@@ -8240,19 +8653,19 @@
         <v>38</v>
       </c>
       <c r="B38" s="82" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="C38" s="83" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="D38" s="83" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="E38" s="87" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="F38" s="86" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="G38" s="63" t="s">
         <v>1</v>
@@ -8286,13 +8699,13 @@
         <v>Troca</v>
       </c>
       <c r="P38" s="60" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="Q38" s="59" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="R38" s="51" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="S38" s="80" t="s">
         <v>1</v>
@@ -8310,7 +8723,7 @@
         <v>Históricos</v>
       </c>
       <c r="W38" s="51" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="X38" s="62" t="str">
         <f t="shared" si="3"/>
@@ -8340,16 +8753,16 @@
         <v>39</v>
       </c>
       <c r="B39" s="82" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="C39" s="83" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="D39" s="83" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="E39" s="87" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="F39" s="86" t="s">
         <v>103</v>
@@ -8386,13 +8799,13 @@
         <v>Operacional</v>
       </c>
       <c r="P39" s="60" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="Q39" s="59" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="R39" s="51" t="s">
-        <v>474</v>
+        <v>467</v>
       </c>
       <c r="S39" s="80" t="s">
         <v>1</v>
@@ -8410,7 +8823,7 @@
         <v>Históricos</v>
       </c>
       <c r="W39" s="51" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="X39" s="62" t="str">
         <f t="shared" si="3"/>
@@ -8440,19 +8853,19 @@
         <v>40</v>
       </c>
       <c r="B40" s="82" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="C40" s="83" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="D40" s="83" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="E40" s="87" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="F40" s="88" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="G40" s="63" t="s">
         <v>1</v>
@@ -8486,13 +8899,13 @@
         <v>Reforma</v>
       </c>
       <c r="P40" s="60" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="Q40" s="59" t="s">
-        <v>430</v>
+        <v>423</v>
       </c>
       <c r="R40" s="51" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="S40" s="80" t="s">
         <v>1</v>
@@ -8510,7 +8923,7 @@
         <v>Históricos</v>
       </c>
       <c r="W40" s="51" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="X40" s="62" t="str">
         <f t="shared" si="3"/>
@@ -8540,19 +8953,19 @@
         <v>41</v>
       </c>
       <c r="B41" s="82" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="C41" s="83" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="D41" s="83" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="E41" s="87" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="F41" s="88" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="G41" s="63" t="s">
         <v>1</v>
@@ -8586,13 +8999,13 @@
         <v>Pericial</v>
       </c>
       <c r="P41" s="60" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="Q41" s="59" t="s">
-        <v>431</v>
+        <v>424</v>
       </c>
       <c r="R41" s="51" t="s">
-        <v>476</v>
+        <v>469</v>
       </c>
       <c r="S41" s="80" t="s">
         <v>1</v>
@@ -8610,7 +9023,7 @@
         <v>Históricos</v>
       </c>
       <c r="W41" s="51" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="X41" s="62" t="str">
         <f t="shared" si="3"/>
@@ -8640,19 +9053,19 @@
         <v>42</v>
       </c>
       <c r="B42" s="82" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="C42" s="83" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="D42" s="83" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="E42" s="87" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="F42" s="88" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="G42" s="63" t="s">
         <v>1</v>
@@ -8686,13 +9099,13 @@
         <v>Congresso</v>
       </c>
       <c r="P42" s="60" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="Q42" s="59" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="R42" s="51" t="s">
-        <v>477</v>
+        <v>470</v>
       </c>
       <c r="S42" s="80" t="s">
         <v>1</v>
@@ -8710,7 +9123,7 @@
         <v>Agendados</v>
       </c>
       <c r="W42" s="51" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="X42" s="62" t="str">
         <f t="shared" si="3"/>
@@ -8740,19 +9153,19 @@
         <v>43</v>
       </c>
       <c r="B43" s="82" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="C43" s="83" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="D43" s="83" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="E43" s="87" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="F43" s="88" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="G43" s="63" t="s">
         <v>1</v>
@@ -8786,13 +9199,13 @@
         <v>Reunião</v>
       </c>
       <c r="P43" s="60" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="Q43" s="59" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="R43" s="51" t="s">
-        <v>478</v>
+        <v>471</v>
       </c>
       <c r="S43" s="80" t="s">
         <v>1</v>
@@ -8810,7 +9223,7 @@
         <v>Agendados</v>
       </c>
       <c r="W43" s="51" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="X43" s="62" t="str">
         <f t="shared" si="3"/>
@@ -8840,16 +9253,16 @@
         <v>44</v>
       </c>
       <c r="B44" s="82" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="C44" s="83" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="D44" s="83" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="E44" s="87" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="F44" s="88" t="s">
         <v>101</v>
@@ -8886,13 +9299,13 @@
         <v>Entrega</v>
       </c>
       <c r="P44" s="60" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="Q44" s="59" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="R44" s="51" t="s">
-        <v>442</v>
+        <v>435</v>
       </c>
       <c r="S44" s="80" t="s">
         <v>1</v>
@@ -8910,7 +9323,7 @@
         <v>Agendados</v>
       </c>
       <c r="W44" s="51" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="X44" s="62" t="str">
         <f t="shared" si="3"/>
@@ -8940,19 +9353,19 @@
         <v>45</v>
       </c>
       <c r="B45" s="82" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="C45" s="87" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="D45" s="87" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="E45" s="87" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="F45" s="88" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="G45" s="63" t="s">
         <v>1</v>
@@ -8986,13 +9399,13 @@
         <v>Exame</v>
       </c>
       <c r="P45" s="60" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="Q45" s="59" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="R45" s="51" t="s">
-        <v>479</v>
+        <v>472</v>
       </c>
       <c r="S45" s="80" t="s">
         <v>1</v>
@@ -9010,7 +9423,7 @@
         <v>Agendados</v>
       </c>
       <c r="W45" s="51" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="X45" s="62" t="str">
         <f t="shared" si="3"/>
@@ -9040,19 +9453,19 @@
         <v>46</v>
       </c>
       <c r="B46" s="82" t="s">
-        <v>508</v>
+        <v>501</v>
       </c>
       <c r="C46" s="87" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="D46" s="87" t="s">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="E46" s="87" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="F46" s="88" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="G46" s="63" t="s">
         <v>1</v>
@@ -9086,14 +9499,14 @@
         <v>Evento.Projetual</v>
       </c>
       <c r="P46" s="60" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="Q46" s="59" t="str">
         <f>_xlfn.TRANSLATE(P46,"pt","es")</f>
         <v>Evento relacionado con el proyecto que ocurrió.</v>
       </c>
       <c r="R46" s="59" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="S46" s="80" t="s">
         <v>1</v>
@@ -9111,7 +9524,7 @@
         <v>Cronologia</v>
       </c>
       <c r="W46" s="51" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="X46" s="62" t="str">
         <f t="shared" si="3"/>
@@ -9141,19 +9554,19 @@
         <v>47</v>
       </c>
       <c r="B47" s="82" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="C47" s="89" t="s">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="D47" s="89" t="s">
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="E47" s="89" t="s">
-        <v>565</v>
+        <v>558</v>
       </c>
       <c r="F47" s="89" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="G47" s="68" t="s">
         <v>1</v>
@@ -9187,13 +9600,13 @@
         <v>Função Auxiliar</v>
       </c>
       <c r="P47" s="51" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="Q47" s="51" t="s">
-        <v>543</v>
+        <v>536</v>
       </c>
       <c r="R47" s="51" t="s">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="S47" s="80" t="s">
         <v>1</v>
@@ -9211,7 +9624,7 @@
         <v>API Método</v>
       </c>
       <c r="W47" s="51" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="X47" s="62" t="str">
         <f t="shared" ref="X47:X51" si="34">CONCATENATE("Key-CRONO-",A47)</f>
@@ -9241,19 +9654,19 @@
         <v>48</v>
       </c>
       <c r="B48" s="82" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="C48" s="89" t="s">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="D48" s="89" t="s">
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="E48" s="89" t="s">
-        <v>565</v>
+        <v>558</v>
       </c>
       <c r="F48" s="89" t="s">
-        <v>545</v>
+        <v>538</v>
       </c>
       <c r="G48" s="68" t="s">
         <v>1</v>
@@ -9287,13 +9700,13 @@
         <v>Função Global</v>
       </c>
       <c r="P48" s="51" t="s">
-        <v>546</v>
+        <v>539</v>
       </c>
       <c r="Q48" s="51" t="s">
-        <v>547</v>
+        <v>540</v>
       </c>
       <c r="R48" s="51" t="s">
-        <v>548</v>
+        <v>541</v>
       </c>
       <c r="S48" s="80" t="s">
         <v>1</v>
@@ -9311,7 +9724,7 @@
         <v>API Método</v>
       </c>
       <c r="W48" s="51" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="X48" s="62" t="str">
         <f t="shared" si="34"/>
@@ -9341,19 +9754,19 @@
         <v>49</v>
       </c>
       <c r="B49" s="82" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="C49" s="89" t="s">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="D49" s="89" t="s">
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="E49" s="89" t="s">
-        <v>565</v>
+        <v>558</v>
       </c>
       <c r="F49" s="89" t="s">
-        <v>549</v>
+        <v>542</v>
       </c>
       <c r="G49" s="68" t="s">
         <v>1</v>
@@ -9387,13 +9800,13 @@
         <v>Função Local</v>
       </c>
       <c r="P49" s="51" t="s">
-        <v>550</v>
+        <v>543</v>
       </c>
       <c r="Q49" s="51" t="s">
-        <v>551</v>
+        <v>544</v>
       </c>
       <c r="R49" s="51" t="s">
-        <v>552</v>
+        <v>545</v>
       </c>
       <c r="S49" s="80" t="s">
         <v>1</v>
@@ -9411,7 +9824,7 @@
         <v>API Método</v>
       </c>
       <c r="W49" s="51" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="X49" s="62" t="str">
         <f t="shared" si="34"/>
@@ -9441,19 +9854,19 @@
         <v>50</v>
       </c>
       <c r="B50" s="82" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="C50" s="89" t="s">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="D50" s="89" t="s">
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="E50" s="89" t="s">
-        <v>565</v>
+        <v>558</v>
       </c>
       <c r="F50" s="89" t="s">
-        <v>553</v>
+        <v>546</v>
       </c>
       <c r="G50" s="68" t="s">
         <v>1</v>
@@ -9487,13 +9900,13 @@
         <v>Função Filtro</v>
       </c>
       <c r="P50" s="51" t="s">
-        <v>554</v>
+        <v>547</v>
       </c>
       <c r="Q50" s="51" t="s">
-        <v>555</v>
+        <v>548</v>
       </c>
       <c r="R50" s="51" t="s">
-        <v>556</v>
+        <v>549</v>
       </c>
       <c r="S50" s="80" t="s">
         <v>1</v>
@@ -9511,7 +9924,7 @@
         <v>API Método</v>
       </c>
       <c r="W50" s="51" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="X50" s="62" t="str">
         <f t="shared" si="34"/>
@@ -9541,19 +9954,19 @@
         <v>51</v>
       </c>
       <c r="B51" s="82" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="C51" s="89" t="s">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="D51" s="89" t="s">
-        <v>566</v>
+        <v>559</v>
       </c>
       <c r="E51" s="89" t="s">
-        <v>567</v>
+        <v>560</v>
       </c>
       <c r="F51" s="89" t="s">
-        <v>557</v>
+        <v>550</v>
       </c>
       <c r="G51" s="68" t="s">
         <v>1</v>
@@ -9587,13 +10000,13 @@
         <v>Bloco de Código</v>
       </c>
       <c r="P51" s="51" t="s">
-        <v>558</v>
+        <v>551</v>
       </c>
       <c r="Q51" s="51" t="s">
-        <v>559</v>
+        <v>552</v>
       </c>
       <c r="R51" s="51" t="s">
-        <v>560</v>
+        <v>553</v>
       </c>
       <c r="S51" s="80" t="s">
         <v>1</v>
@@ -9611,7 +10024,7 @@
         <v>API Método Visual</v>
       </c>
       <c r="W51" s="51" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="X51" s="62" t="str">
         <f t="shared" si="34"/>
@@ -9638,29 +10051,29 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:B46 A47:A51">
-    <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F39">
-    <cfRule type="duplicateValues" dxfId="24" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F46">
-    <cfRule type="duplicateValues" dxfId="23" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="35"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F47:F51">
+    <cfRule type="duplicateValues" dxfId="18" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1:R45">
-    <cfRule type="cellIs" dxfId="21" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="12" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W51">
-    <cfRule type="cellIs" dxfId="20" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="18" operator="equal">
       <formula>"null"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F47:F51">
-    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <ignoredErrors>
@@ -9878,7 +10291,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="19" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9902,10 +10315,10 @@
         <v>1</v>
       </c>
       <c r="B1" s="41" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="C1" s="41" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -9916,7 +10329,7 @@
         <v>54</v>
       </c>
       <c r="C2" s="46" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -9924,10 +10337,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="45" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="C3" s="46" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -9935,15 +10348,15 @@
         <v>4</v>
       </c>
       <c r="B4" s="45" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="C4" s="46" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A4">
-    <cfRule type="cellIs" dxfId="18" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9995,7 +10408,7 @@
   <sheetData>
     <row r="1" spans="1:35" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="38" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="B1" s="30" t="s">
         <v>68</v>
@@ -10007,97 +10420,97 @@
         <v>48</v>
       </c>
       <c r="E1" s="30" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="F1" s="30" t="s">
         <v>48</v>
       </c>
       <c r="G1" s="30" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="H1" s="30" t="s">
         <v>48</v>
       </c>
       <c r="I1" s="30" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="J1" s="30" t="s">
         <v>48</v>
       </c>
       <c r="K1" s="30" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="L1" s="30" t="s">
         <v>48</v>
       </c>
       <c r="M1" s="30" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="N1" s="39" t="s">
         <v>48</v>
       </c>
       <c r="O1" s="30" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="P1" s="30" t="s">
         <v>48</v>
       </c>
       <c r="Q1" s="30" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="R1" s="30" t="s">
         <v>48</v>
       </c>
       <c r="S1" s="30" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="T1" s="44" t="s">
         <v>48</v>
       </c>
       <c r="U1" s="44" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="V1" s="30" t="s">
         <v>48</v>
       </c>
       <c r="W1" s="30" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="X1" s="30" t="s">
         <v>48</v>
       </c>
       <c r="Y1" s="30" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="Z1" s="30" t="s">
         <v>48</v>
       </c>
       <c r="AA1" s="30" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="AB1" s="30" t="s">
         <v>48</v>
       </c>
       <c r="AC1" s="30" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="AD1" s="30" t="s">
         <v>48</v>
       </c>
       <c r="AE1" s="30" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="AF1" s="30" t="s">
         <v>48</v>
       </c>
       <c r="AG1" s="30" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="AH1" s="30" t="s">
         <v>48</v>
       </c>
       <c r="AI1" s="30" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
     </row>
     <row r="2" spans="1:35" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
@@ -10144,7 +10557,7 @@
         <v>72</v>
       </c>
       <c r="O2" s="33" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="P2" s="29" t="s">
         <v>1</v>
@@ -10165,16 +10578,16 @@
         <v>1</v>
       </c>
       <c r="V2" s="29" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="W2" s="33" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="X2" s="29" t="s">
+        <v>366</v>
+      </c>
+      <c r="Y2" s="33" t="s">
         <v>373</v>
-      </c>
-      <c r="Y2" s="33" t="s">
-        <v>380</v>
       </c>
       <c r="Z2" s="28" t="s">
         <v>1</v>
@@ -10212,7 +10625,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="47" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="C3" s="25" t="s">
         <v>51</v>
@@ -10251,7 +10664,7 @@
         <v>72</v>
       </c>
       <c r="O3" s="33" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="P3" s="29" t="s">
         <v>1</v>
@@ -10272,16 +10685,16 @@
         <v>1</v>
       </c>
       <c r="V3" s="29" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="W3" s="33" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="X3" s="29" t="s">
+        <v>366</v>
+      </c>
+      <c r="Y3" s="33" t="s">
         <v>373</v>
-      </c>
-      <c r="Y3" s="33" t="s">
-        <v>380</v>
       </c>
       <c r="Z3" s="28" t="s">
         <v>1</v>
@@ -10319,7 +10732,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="47" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="C4" s="25" t="s">
         <v>51</v>
@@ -10358,7 +10771,7 @@
         <v>72</v>
       </c>
       <c r="O4" s="33" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="P4" s="29" t="s">
         <v>1</v>
@@ -10379,16 +10792,16 @@
         <v>1</v>
       </c>
       <c r="V4" s="29" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="W4" s="33" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="X4" s="29" t="s">
+        <v>366</v>
+      </c>
+      <c r="Y4" s="33" t="s">
         <v>373</v>
-      </c>
-      <c r="Y4" s="33" t="s">
-        <v>380</v>
       </c>
       <c r="Z4" s="28" t="s">
         <v>1</v>
@@ -10426,16 +10839,16 @@
         <v>5</v>
       </c>
       <c r="B5" s="47" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="C5" s="25" t="s">
         <v>51</v>
       </c>
       <c r="D5" s="28" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="E5" s="32" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="F5" s="28" t="s">
         <v>1</v>
@@ -10465,7 +10878,7 @@
         <v>72</v>
       </c>
       <c r="O5" s="33" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="P5" s="29" t="s">
         <v>1</v>
@@ -10486,16 +10899,16 @@
         <v>1</v>
       </c>
       <c r="V5" s="29" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="W5" s="33" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="X5" s="29" t="s">
+        <v>366</v>
+      </c>
+      <c r="Y5" s="33" t="s">
         <v>373</v>
-      </c>
-      <c r="Y5" s="33" t="s">
-        <v>380</v>
       </c>
       <c r="Z5" s="28" t="s">
         <v>1</v>
@@ -10533,22 +10946,22 @@
         <v>6</v>
       </c>
       <c r="B6" s="34" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="C6" s="26" t="s">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="D6" s="28" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="E6" s="49" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="F6" s="28" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="G6" s="32" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="H6" s="28" t="s">
         <v>1</v>
@@ -10572,7 +10985,7 @@
         <v>72</v>
       </c>
       <c r="O6" s="33" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="P6" s="29" t="s">
         <v>1</v>
@@ -10593,16 +11006,16 @@
         <v>1</v>
       </c>
       <c r="V6" s="29" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="W6" s="33" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="X6" s="29" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="Y6" s="33" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="Z6" s="28" t="s">
         <v>1</v>
@@ -10640,22 +11053,22 @@
         <v>7</v>
       </c>
       <c r="B7" s="34" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="C7" s="26" t="s">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="D7" s="28" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="E7" s="49" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="F7" s="28" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="G7" s="32" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="H7" s="28" t="s">
         <v>1</v>
@@ -10679,7 +11092,7 @@
         <v>72</v>
       </c>
       <c r="O7" s="33" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="P7" s="29" t="s">
         <v>1</v>
@@ -10700,16 +11113,16 @@
         <v>1</v>
       </c>
       <c r="V7" s="29" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="W7" s="33" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="X7" s="29" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="Y7" s="33" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="Z7" s="28" t="s">
         <v>1</v>
@@ -10747,10 +11160,10 @@
         <v>8</v>
       </c>
       <c r="B8" s="31" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="D8" s="28" t="s">
         <v>1</v>
@@ -10789,10 +11202,10 @@
         <v>81</v>
       </c>
       <c r="P8" s="29" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="Q8" s="33" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="R8" s="29" t="s">
         <v>1</v>
@@ -10807,16 +11220,16 @@
         <v>1</v>
       </c>
       <c r="V8" s="29" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="W8" s="33" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="X8" s="29" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="Y8" s="33" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="Z8" s="28" t="s">
         <v>1</v>
@@ -10854,10 +11267,10 @@
         <v>9</v>
       </c>
       <c r="B9" s="31" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="D9" s="28" t="s">
         <v>1</v>
@@ -10896,10 +11309,10 @@
         <v>78</v>
       </c>
       <c r="P9" s="29" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="Q9" s="33" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="R9" s="29" t="s">
         <v>1</v>
@@ -10914,16 +11327,16 @@
         <v>1</v>
       </c>
       <c r="V9" s="29" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="W9" s="33" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="X9" s="29" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="Y9" s="33" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="Z9" s="28" t="s">
         <v>1</v>
@@ -10961,7 +11374,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="C10" s="26" t="s">
         <v>66</v>
@@ -11000,13 +11413,13 @@
         <v>72</v>
       </c>
       <c r="O10" s="33" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="P10" s="29" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="Q10" s="33" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="R10" s="29" t="s">
         <v>1</v>
@@ -11021,16 +11434,16 @@
         <v>1</v>
       </c>
       <c r="V10" s="29" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="W10" s="33" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="X10" s="29" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="Y10" s="33" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="Z10" s="28" t="s">
         <v>1</v>
@@ -11068,7 +11481,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="C11" s="26" t="s">
         <v>66</v>
@@ -11107,13 +11520,13 @@
         <v>72</v>
       </c>
       <c r="O11" s="33" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="P11" s="29" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="Q11" s="33" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="R11" s="29" t="s">
         <v>1</v>
@@ -11128,16 +11541,16 @@
         <v>1</v>
       </c>
       <c r="V11" s="29" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="W11" s="33" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="X11" s="29" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="Y11" s="33" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="Z11" s="28" t="s">
         <v>1</v>
@@ -11217,10 +11630,10 @@
         <v>73</v>
       </c>
       <c r="P12" s="29" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="Q12" s="33" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="R12" s="29" t="s">
         <v>1</v>
@@ -11235,16 +11648,16 @@
         <v>1</v>
       </c>
       <c r="V12" s="29" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="W12" s="33" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="X12" s="29" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="Y12" s="33" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="Z12" s="28" t="s">
         <v>1</v>
@@ -11324,10 +11737,10 @@
         <v>75</v>
       </c>
       <c r="P13" s="29" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="Q13" s="33" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="R13" s="29" t="s">
         <v>1</v>
@@ -11342,16 +11755,16 @@
         <v>1</v>
       </c>
       <c r="V13" s="29" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="W13" s="33" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="X13" s="29" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="Y13" s="33" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="Z13" s="28" t="s">
         <v>1</v>
@@ -11389,7 +11802,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="47" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="C14" s="25" t="s">
         <v>54</v>
@@ -11428,7 +11841,7 @@
         <v>72</v>
       </c>
       <c r="O14" s="33" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="P14" s="29" t="s">
         <v>1</v>
@@ -11449,16 +11862,16 @@
         <v>1</v>
       </c>
       <c r="V14" s="29" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="W14" s="33" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="X14" s="29" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="Y14" s="33" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="Z14" s="28" t="s">
         <v>1</v>
@@ -11496,7 +11909,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="47" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="C15" s="25" t="s">
         <v>54</v>
@@ -11535,7 +11948,7 @@
         <v>72</v>
       </c>
       <c r="O15" s="33" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="P15" s="29" t="s">
         <v>1</v>
@@ -11556,16 +11969,16 @@
         <v>1</v>
       </c>
       <c r="V15" s="29" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="W15" s="33" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="X15" s="29" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="Y15" s="33" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="Z15" s="28" t="s">
         <v>1</v>
@@ -11603,7 +12016,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="47" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="C16" s="25" t="s">
         <v>54</v>
@@ -11642,7 +12055,7 @@
         <v>72</v>
       </c>
       <c r="O16" s="33" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="P16" s="29" t="s">
         <v>1</v>
@@ -11663,16 +12076,16 @@
         <v>1</v>
       </c>
       <c r="V16" s="29" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="W16" s="33" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="X16" s="29" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="Y16" s="33" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="Z16" s="28" t="s">
         <v>1</v>
@@ -11710,7 +12123,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="47" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="C17" s="25" t="s">
         <v>54</v>
@@ -11749,7 +12162,7 @@
         <v>72</v>
       </c>
       <c r="O17" s="33" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="P17" s="29" t="s">
         <v>1</v>
@@ -11770,16 +12183,16 @@
         <v>1</v>
       </c>
       <c r="V17" s="29" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="W17" s="33" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="X17" s="29" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="Y17" s="33" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="Z17" s="28" t="s">
         <v>1</v>
@@ -11817,7 +12230,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="47" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="C18" s="25" t="s">
         <v>54</v>
@@ -11856,7 +12269,7 @@
         <v>72</v>
       </c>
       <c r="O18" s="33" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="P18" s="29" t="s">
         <v>1</v>
@@ -11877,16 +12290,16 @@
         <v>1</v>
       </c>
       <c r="V18" s="29" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="W18" s="33" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="X18" s="29" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="Y18" s="33" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="Z18" s="28" t="s">
         <v>1</v>
@@ -11924,7 +12337,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="47" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="C19" s="25" t="s">
         <v>54</v>
@@ -11963,7 +12376,7 @@
         <v>72</v>
       </c>
       <c r="O19" s="33" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="P19" s="29" t="s">
         <v>1</v>
@@ -11984,16 +12397,16 @@
         <v>1</v>
       </c>
       <c r="V19" s="29" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="W19" s="33" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="X19" s="29" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="Y19" s="33" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="Z19" s="28" t="s">
         <v>1</v>
@@ -12031,7 +12444,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="47" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="C20" s="25" t="s">
         <v>54</v>
@@ -12070,7 +12483,7 @@
         <v>72</v>
       </c>
       <c r="O20" s="33" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="P20" s="29" t="s">
         <v>1</v>
@@ -12091,16 +12504,16 @@
         <v>1</v>
       </c>
       <c r="V20" s="29" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="W20" s="33" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="X20" s="29" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="Y20" s="33" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="Z20" s="28" t="s">
         <v>1</v>
@@ -12141,7 +12554,7 @@
         <v>71</v>
       </c>
       <c r="C21" s="26" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="D21" s="28" t="s">
         <v>1</v>
@@ -12180,10 +12593,10 @@
         <v>90</v>
       </c>
       <c r="P21" s="29" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="Q21" s="33" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="R21" s="29" t="s">
         <v>1</v>
@@ -12198,16 +12611,16 @@
         <v>1</v>
       </c>
       <c r="V21" s="29" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="W21" s="33" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="X21" s="29" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="Y21" s="33" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="Z21" s="28" t="s">
         <v>1</v>
@@ -12248,7 +12661,7 @@
         <v>91</v>
       </c>
       <c r="C22" s="26" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="D22" s="28" t="s">
         <v>1</v>
@@ -12287,10 +12700,10 @@
         <v>92</v>
       </c>
       <c r="P22" s="29" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="Q22" s="33" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="R22" s="29" t="s">
         <v>1</v>
@@ -12305,16 +12718,16 @@
         <v>1</v>
       </c>
       <c r="V22" s="29" t="s">
+        <v>364</v>
+      </c>
+      <c r="W22" s="33" t="s">
+        <v>365</v>
+      </c>
+      <c r="X22" s="29" t="s">
+        <v>366</v>
+      </c>
+      <c r="Y22" s="33" t="s">
         <v>371</v>
-      </c>
-      <c r="W22" s="33" t="s">
-        <v>372</v>
-      </c>
-      <c r="X22" s="29" t="s">
-        <v>373</v>
-      </c>
-      <c r="Y22" s="33" t="s">
-        <v>378</v>
       </c>
       <c r="Z22" s="28" t="s">
         <v>1</v>
@@ -12355,10 +12768,10 @@
         <v>93</v>
       </c>
       <c r="C23" s="26" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="D23" s="28" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="E23" s="32" t="s">
         <v>91</v>
@@ -12394,10 +12807,10 @@
         <v>94</v>
       </c>
       <c r="P23" s="29" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="Q23" s="33" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="R23" s="29" t="s">
         <v>1</v>
@@ -12412,16 +12825,16 @@
         <v>1</v>
       </c>
       <c r="V23" s="29" t="s">
+        <v>364</v>
+      </c>
+      <c r="W23" s="33" t="s">
+        <v>365</v>
+      </c>
+      <c r="X23" s="29" t="s">
+        <v>366</v>
+      </c>
+      <c r="Y23" s="33" t="s">
         <v>371</v>
-      </c>
-      <c r="W23" s="33" t="s">
-        <v>372</v>
-      </c>
-      <c r="X23" s="29" t="s">
-        <v>373</v>
-      </c>
-      <c r="Y23" s="33" t="s">
-        <v>378</v>
       </c>
       <c r="Z23" s="28" t="s">
         <v>1</v>
@@ -12462,10 +12875,10 @@
         <v>95</v>
       </c>
       <c r="C24" s="26" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="D24" s="28" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="E24" s="32" t="s">
         <v>91</v>
@@ -12501,10 +12914,10 @@
         <v>96</v>
       </c>
       <c r="P24" s="29" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="Q24" s="33" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="R24" s="29" t="s">
         <v>1</v>
@@ -12519,16 +12932,16 @@
         <v>1</v>
       </c>
       <c r="V24" s="29" t="s">
+        <v>364</v>
+      </c>
+      <c r="W24" s="33" t="s">
+        <v>365</v>
+      </c>
+      <c r="X24" s="29" t="s">
+        <v>366</v>
+      </c>
+      <c r="Y24" s="33" t="s">
         <v>371</v>
-      </c>
-      <c r="W24" s="33" t="s">
-        <v>372</v>
-      </c>
-      <c r="X24" s="29" t="s">
-        <v>373</v>
-      </c>
-      <c r="Y24" s="33" t="s">
-        <v>378</v>
       </c>
       <c r="Z24" s="28" t="s">
         <v>1</v>
@@ -12569,10 +12982,10 @@
         <v>97</v>
       </c>
       <c r="C25" s="26" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="D25" s="28" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="E25" s="32" t="s">
         <v>91</v>
@@ -12608,10 +13021,10 @@
         <v>98</v>
       </c>
       <c r="P25" s="29" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="Q25" s="33" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="R25" s="29" t="s">
         <v>1</v>
@@ -12626,16 +13039,16 @@
         <v>1</v>
       </c>
       <c r="V25" s="29" t="s">
+        <v>364</v>
+      </c>
+      <c r="W25" s="33" t="s">
+        <v>365</v>
+      </c>
+      <c r="X25" s="29" t="s">
+        <v>366</v>
+      </c>
+      <c r="Y25" s="33" t="s">
         <v>371</v>
-      </c>
-      <c r="W25" s="33" t="s">
-        <v>372</v>
-      </c>
-      <c r="X25" s="29" t="s">
-        <v>373</v>
-      </c>
-      <c r="Y25" s="33" t="s">
-        <v>378</v>
       </c>
       <c r="Z25" s="28" t="s">
         <v>1</v>
@@ -12676,10 +13089,10 @@
         <v>99</v>
       </c>
       <c r="C26" s="26" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="D26" s="28" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="E26" s="32" t="s">
         <v>95</v>
@@ -12715,10 +13128,10 @@
         <v>100</v>
       </c>
       <c r="P26" s="29" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="Q26" s="33" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="R26" s="29" t="s">
         <v>1</v>
@@ -12733,16 +13146,16 @@
         <v>1</v>
       </c>
       <c r="V26" s="29" t="s">
+        <v>364</v>
+      </c>
+      <c r="W26" s="33" t="s">
+        <v>365</v>
+      </c>
+      <c r="X26" s="29" t="s">
+        <v>366</v>
+      </c>
+      <c r="Y26" s="33" t="s">
         <v>371</v>
-      </c>
-      <c r="W26" s="33" t="s">
-        <v>372</v>
-      </c>
-      <c r="X26" s="29" t="s">
-        <v>373</v>
-      </c>
-      <c r="Y26" s="33" t="s">
-        <v>378</v>
       </c>
       <c r="Z26" s="28" t="s">
         <v>1</v>
@@ -12783,10 +13196,10 @@
         <v>101</v>
       </c>
       <c r="C27" s="26" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="D27" s="28" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="E27" s="32" t="s">
         <v>99</v>
@@ -12822,10 +13235,10 @@
         <v>102</v>
       </c>
       <c r="P27" s="29" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="Q27" s="33" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="R27" s="29" t="s">
         <v>1</v>
@@ -12840,16 +13253,16 @@
         <v>1</v>
       </c>
       <c r="V27" s="29" t="s">
+        <v>364</v>
+      </c>
+      <c r="W27" s="33" t="s">
+        <v>365</v>
+      </c>
+      <c r="X27" s="29" t="s">
+        <v>366</v>
+      </c>
+      <c r="Y27" s="33" t="s">
         <v>371</v>
-      </c>
-      <c r="W27" s="33" t="s">
-        <v>372</v>
-      </c>
-      <c r="X27" s="29" t="s">
-        <v>373</v>
-      </c>
-      <c r="Y27" s="33" t="s">
-        <v>378</v>
       </c>
       <c r="Z27" s="28" t="s">
         <v>1</v>
@@ -12890,10 +13303,10 @@
         <v>103</v>
       </c>
       <c r="C28" s="26" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="D28" s="28" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="E28" s="32" t="s">
         <v>99</v>
@@ -12929,10 +13342,10 @@
         <v>104</v>
       </c>
       <c r="P28" s="29" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="Q28" s="33" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="R28" s="29" t="s">
         <v>1</v>
@@ -12947,16 +13360,16 @@
         <v>1</v>
       </c>
       <c r="V28" s="29" t="s">
+        <v>364</v>
+      </c>
+      <c r="W28" s="33" t="s">
+        <v>365</v>
+      </c>
+      <c r="X28" s="29" t="s">
+        <v>366</v>
+      </c>
+      <c r="Y28" s="33" t="s">
         <v>371</v>
-      </c>
-      <c r="W28" s="33" t="s">
-        <v>372</v>
-      </c>
-      <c r="X28" s="29" t="s">
-        <v>373</v>
-      </c>
-      <c r="Y28" s="33" t="s">
-        <v>378</v>
       </c>
       <c r="Z28" s="28" t="s">
         <v>1</v>
@@ -12997,7 +13410,7 @@
         <v>121</v>
       </c>
       <c r="C29" s="26" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="D29" s="28" t="s">
         <v>1</v>
@@ -13036,10 +13449,10 @@
         <v>122</v>
       </c>
       <c r="P29" s="29" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="Q29" s="33" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="R29" s="29" t="s">
         <v>1</v>
@@ -13054,16 +13467,16 @@
         <v>1</v>
       </c>
       <c r="V29" s="29" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="W29" s="33" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="X29" s="29" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="Y29" s="33" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="Z29" s="28" t="s">
         <v>1</v>
@@ -13104,7 +13517,7 @@
         <v>123</v>
       </c>
       <c r="C30" s="26" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="D30" s="28" t="s">
         <v>1</v>
@@ -13143,10 +13556,10 @@
         <v>124</v>
       </c>
       <c r="P30" s="29" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="Q30" s="33" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="R30" s="29" t="s">
         <v>1</v>
@@ -13161,16 +13574,16 @@
         <v>1</v>
       </c>
       <c r="V30" s="29" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="W30" s="33" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="X30" s="29" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="Y30" s="33" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="Z30" s="28" t="s">
         <v>1</v>
@@ -13211,7 +13624,7 @@
         <v>125</v>
       </c>
       <c r="C31" s="26" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="D31" s="28" t="s">
         <v>1</v>
@@ -13250,11 +13663,11 @@
         <v>126</v>
       </c>
       <c r="P31" s="29" t="s">
+        <v>176</v>
+      </c>
+      <c r="Q31" s="33" t="s">
         <v>183</v>
       </c>
-      <c r="Q31" s="33" t="s">
-        <v>190</v>
-      </c>
       <c r="R31" s="29" t="s">
         <v>1</v>
       </c>
@@ -13268,16 +13681,16 @@
         <v>1</v>
       </c>
       <c r="V31" s="29" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="W31" s="33" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="X31" s="29" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="Y31" s="33" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="Z31" s="28" t="s">
         <v>1</v>
@@ -13318,7 +13731,7 @@
         <v>127</v>
       </c>
       <c r="C32" s="26" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="D32" s="28" t="s">
         <v>1</v>
@@ -13357,10 +13770,10 @@
         <v>128</v>
       </c>
       <c r="P32" s="29" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="Q32" s="33" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="R32" s="29" t="s">
         <v>1</v>
@@ -13375,16 +13788,16 @@
         <v>1</v>
       </c>
       <c r="V32" s="29" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="W32" s="33" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="X32" s="29" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="Y32" s="33" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="Z32" s="28" t="s">
         <v>1</v>
@@ -13425,7 +13838,7 @@
         <v>129</v>
       </c>
       <c r="C33" s="26" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="D33" s="28" t="s">
         <v>1</v>
@@ -13464,10 +13877,10 @@
         <v>130</v>
       </c>
       <c r="P33" s="29" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="Q33" s="33" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="R33" s="29" t="s">
         <v>1</v>
@@ -13482,16 +13895,16 @@
         <v>1</v>
       </c>
       <c r="V33" s="29" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="W33" s="33" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="X33" s="29" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="Y33" s="33" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="Z33" s="28" t="s">
         <v>1</v>
@@ -13532,7 +13945,7 @@
         <v>131</v>
       </c>
       <c r="C34" s="26" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="D34" s="28" t="s">
         <v>1</v>
@@ -13571,10 +13984,10 @@
         <v>132</v>
       </c>
       <c r="P34" s="29" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="Q34" s="33" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="R34" s="29" t="s">
         <v>1</v>
@@ -13589,16 +14002,16 @@
         <v>1</v>
       </c>
       <c r="V34" s="29" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="W34" s="33" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="X34" s="29" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="Y34" s="33" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="Z34" s="28" t="s">
         <v>1</v>
@@ -13639,7 +14052,7 @@
         <v>133</v>
       </c>
       <c r="C35" s="26" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="D35" s="28" t="s">
         <v>1</v>
@@ -13678,10 +14091,10 @@
         <v>134</v>
       </c>
       <c r="P35" s="29" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="Q35" s="33" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="R35" s="29" t="s">
         <v>1</v>
@@ -13696,16 +14109,16 @@
         <v>1</v>
       </c>
       <c r="V35" s="29" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="W35" s="33" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="X35" s="29" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="Y35" s="33" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="Z35" s="28" t="s">
         <v>1</v>
@@ -13746,7 +14159,7 @@
         <v>135</v>
       </c>
       <c r="C36" s="26" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="D36" s="28" t="s">
         <v>1</v>
@@ -13785,10 +14198,10 @@
         <v>136</v>
       </c>
       <c r="P36" s="29" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="Q36" s="33" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="R36" s="29" t="s">
         <v>1</v>
@@ -13803,16 +14216,16 @@
         <v>1</v>
       </c>
       <c r="V36" s="29" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="W36" s="33" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="X36" s="29" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="Y36" s="33" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="Z36" s="28" t="s">
         <v>1</v>
@@ -13850,10 +14263,10 @@
         <v>37</v>
       </c>
       <c r="B37" s="36" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="C37" s="48" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="D37" s="28" t="s">
         <v>1</v>
@@ -13892,10 +14305,10 @@
         <v>87</v>
       </c>
       <c r="P37" s="29" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="Q37" s="33" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="R37" s="29" t="s">
         <v>1</v>
@@ -13910,16 +14323,16 @@
         <v>1</v>
       </c>
       <c r="V37" s="29" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="W37" s="33" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="X37" s="29" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="Y37" s="33" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="Z37" s="28" t="s">
         <v>1</v>
@@ -13957,10 +14370,10 @@
         <v>38</v>
       </c>
       <c r="B38" s="36" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="C38" s="48" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="D38" s="28" t="s">
         <v>1</v>
@@ -13999,10 +14412,10 @@
         <v>89</v>
       </c>
       <c r="P38" s="29" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="Q38" s="33" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="R38" s="29" t="s">
         <v>1</v>
@@ -14017,16 +14430,16 @@
         <v>1</v>
       </c>
       <c r="V38" s="29" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="W38" s="33" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="X38" s="29" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="Y38" s="33" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="Z38" s="28" t="s">
         <v>1</v>
@@ -14067,7 +14480,7 @@
         <v>76</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>501</v>
+        <v>494</v>
       </c>
       <c r="D39" s="28" t="s">
         <v>1</v>
@@ -14106,10 +14519,10 @@
         <v>77</v>
       </c>
       <c r="P39" s="29" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="Q39" s="33" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="R39" s="29" t="s">
         <v>1</v>
@@ -14124,16 +14537,16 @@
         <v>1</v>
       </c>
       <c r="V39" s="29" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="W39" s="33" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="X39" s="29" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="Y39" s="33" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="Z39" s="28" t="s">
         <v>1</v>
@@ -14174,7 +14587,7 @@
         <v>79</v>
       </c>
       <c r="C40" s="21" t="s">
-        <v>501</v>
+        <v>494</v>
       </c>
       <c r="D40" s="28" t="s">
         <v>1</v>
@@ -14213,10 +14626,10 @@
         <v>80</v>
       </c>
       <c r="P40" s="29" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="Q40" s="33" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="R40" s="29" t="s">
         <v>1</v>
@@ -14231,16 +14644,16 @@
         <v>1</v>
       </c>
       <c r="V40" s="29" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="W40" s="33" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="X40" s="29" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="Y40" s="33" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="Z40" s="28" t="s">
         <v>1</v>
@@ -14281,7 +14694,7 @@
         <v>82</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>501</v>
+        <v>494</v>
       </c>
       <c r="D41" s="28" t="s">
         <v>1</v>
@@ -14320,10 +14733,10 @@
         <v>83</v>
       </c>
       <c r="P41" s="29" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="Q41" s="33" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="R41" s="29" t="s">
         <v>1</v>
@@ -14338,16 +14751,16 @@
         <v>1</v>
       </c>
       <c r="V41" s="29" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="W41" s="33" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="X41" s="29" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="Y41" s="33" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="Z41" s="28" t="s">
         <v>1</v>
@@ -14388,7 +14801,7 @@
         <v>84</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>501</v>
+        <v>494</v>
       </c>
       <c r="D42" s="28" t="s">
         <v>1</v>
@@ -14427,10 +14840,10 @@
         <v>85</v>
       </c>
       <c r="P42" s="29" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="Q42" s="33" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="R42" s="29" t="s">
         <v>1</v>
@@ -14445,16 +14858,16 @@
         <v>1</v>
       </c>
       <c r="V42" s="29" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="W42" s="33" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="X42" s="29" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="Y42" s="33" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="Z42" s="28" t="s">
         <v>1</v>
@@ -14534,10 +14947,10 @@
         <v>106</v>
       </c>
       <c r="P43" s="29" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="Q43" s="33" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="R43" s="29" t="s">
         <v>1</v>
@@ -14552,16 +14965,16 @@
         <v>1</v>
       </c>
       <c r="V43" s="29" t="s">
+        <v>364</v>
+      </c>
+      <c r="W43" s="33" t="s">
+        <v>365</v>
+      </c>
+      <c r="X43" s="29" t="s">
+        <v>366</v>
+      </c>
+      <c r="Y43" s="33" t="s">
         <v>371</v>
-      </c>
-      <c r="W43" s="33" t="s">
-        <v>372</v>
-      </c>
-      <c r="X43" s="29" t="s">
-        <v>373</v>
-      </c>
-      <c r="Y43" s="33" t="s">
-        <v>378</v>
       </c>
       <c r="Z43" s="28" t="s">
         <v>1</v>
@@ -14641,10 +15054,10 @@
         <v>108</v>
       </c>
       <c r="P44" s="29" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="Q44" s="33" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="R44" s="29" t="s">
         <v>1</v>
@@ -14659,16 +15072,16 @@
         <v>1</v>
       </c>
       <c r="V44" s="29" t="s">
+        <v>364</v>
+      </c>
+      <c r="W44" s="33" t="s">
+        <v>365</v>
+      </c>
+      <c r="X44" s="29" t="s">
+        <v>366</v>
+      </c>
+      <c r="Y44" s="33" t="s">
         <v>371</v>
-      </c>
-      <c r="W44" s="33" t="s">
-        <v>372</v>
-      </c>
-      <c r="X44" s="29" t="s">
-        <v>373</v>
-      </c>
-      <c r="Y44" s="33" t="s">
-        <v>378</v>
       </c>
       <c r="Z44" s="28" t="s">
         <v>1</v>
@@ -14748,10 +15161,10 @@
         <v>108</v>
       </c>
       <c r="P45" s="29" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="Q45" s="33" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="R45" s="29" t="s">
         <v>1</v>
@@ -14766,16 +15179,16 @@
         <v>1</v>
       </c>
       <c r="V45" s="29" t="s">
+        <v>364</v>
+      </c>
+      <c r="W45" s="33" t="s">
+        <v>365</v>
+      </c>
+      <c r="X45" s="29" t="s">
+        <v>366</v>
+      </c>
+      <c r="Y45" s="33" t="s">
         <v>371</v>
-      </c>
-      <c r="W45" s="33" t="s">
-        <v>372</v>
-      </c>
-      <c r="X45" s="29" t="s">
-        <v>373</v>
-      </c>
-      <c r="Y45" s="33" t="s">
-        <v>378</v>
       </c>
       <c r="Z45" s="28" t="s">
         <v>1</v>
@@ -14855,10 +15268,10 @@
         <v>108</v>
       </c>
       <c r="P46" s="29" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="Q46" s="33" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="R46" s="29" t="s">
         <v>1</v>
@@ -14873,16 +15286,16 @@
         <v>1</v>
       </c>
       <c r="V46" s="29" t="s">
+        <v>364</v>
+      </c>
+      <c r="W46" s="33" t="s">
+        <v>365</v>
+      </c>
+      <c r="X46" s="29" t="s">
+        <v>366</v>
+      </c>
+      <c r="Y46" s="33" t="s">
         <v>371</v>
-      </c>
-      <c r="W46" s="33" t="s">
-        <v>372</v>
-      </c>
-      <c r="X46" s="29" t="s">
-        <v>373</v>
-      </c>
-      <c r="Y46" s="33" t="s">
-        <v>378</v>
       </c>
       <c r="Z46" s="28" t="s">
         <v>1</v>
@@ -14920,16 +15333,16 @@
         <v>47</v>
       </c>
       <c r="B47" s="36" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="C47" s="20" t="s">
+        <v>246</v>
+      </c>
+      <c r="D47" s="28" t="s">
         <v>253</v>
       </c>
-      <c r="D47" s="28" t="s">
-        <v>260</v>
-      </c>
       <c r="E47" s="32" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="F47" s="28" t="s">
         <v>1</v>
@@ -14959,7 +15372,7 @@
         <v>72</v>
       </c>
       <c r="O47" s="33" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="P47" s="29" t="s">
         <v>1</v>
@@ -14980,16 +15393,16 @@
         <v>1</v>
       </c>
       <c r="V47" s="29" t="s">
+        <v>364</v>
+      </c>
+      <c r="W47" s="33" t="s">
+        <v>365</v>
+      </c>
+      <c r="X47" s="29" t="s">
+        <v>366</v>
+      </c>
+      <c r="Y47" s="33" t="s">
         <v>371</v>
-      </c>
-      <c r="W47" s="33" t="s">
-        <v>372</v>
-      </c>
-      <c r="X47" s="29" t="s">
-        <v>373</v>
-      </c>
-      <c r="Y47" s="33" t="s">
-        <v>378</v>
       </c>
       <c r="Z47" s="28" t="s">
         <v>1</v>
@@ -15027,10 +15440,10 @@
         <v>48</v>
       </c>
       <c r="B48" s="36" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="C48" s="20" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="D48" s="28" t="s">
         <v>1</v>
@@ -15069,10 +15482,10 @@
         <v>86</v>
       </c>
       <c r="P48" s="29" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="Q48" s="33" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="R48" s="29" t="s">
         <v>1</v>
@@ -15087,16 +15500,16 @@
         <v>1</v>
       </c>
       <c r="V48" s="29" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="W48" s="33" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="X48" s="29" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="Y48" s="33" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="Z48" s="28" t="s">
         <v>1</v>
@@ -15134,10 +15547,10 @@
         <v>49</v>
       </c>
       <c r="B49" s="36" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="C49" s="20" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="D49" s="28" t="s">
         <v>1</v>
@@ -15176,10 +15589,10 @@
         <v>88</v>
       </c>
       <c r="P49" s="29" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="Q49" s="33" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="R49" s="29" t="s">
         <v>1</v>
@@ -15194,16 +15607,16 @@
         <v>1</v>
       </c>
       <c r="V49" s="29" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="W49" s="33" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="X49" s="29" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="Y49" s="33" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="Z49" s="28" t="s">
         <v>1</v>
@@ -15241,22 +15654,22 @@
         <v>50</v>
       </c>
       <c r="B50" s="47" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="C50" s="20" t="s">
         <v>52</v>
       </c>
       <c r="D50" s="28" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="E50" s="32" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="F50" s="28" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="G50" s="49" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="H50" s="28" t="s">
         <v>1</v>
@@ -15280,7 +15693,7 @@
         <v>72</v>
       </c>
       <c r="O50" s="33" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="P50" s="29" t="s">
         <v>1</v>
@@ -15301,16 +15714,16 @@
         <v>1</v>
       </c>
       <c r="V50" s="29" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="W50" s="33" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="X50" s="29" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="Y50" s="33" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="Z50" s="28" t="s">
         <v>1</v>
@@ -15348,22 +15761,22 @@
         <v>51</v>
       </c>
       <c r="B51" s="47" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="C51" s="20" t="s">
         <v>52</v>
       </c>
       <c r="D51" s="28" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="E51" s="32" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="F51" s="28" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="G51" s="49" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="H51" s="28" t="s">
         <v>1</v>
@@ -15387,7 +15800,7 @@
         <v>72</v>
       </c>
       <c r="O51" s="33" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="P51" s="29" t="s">
         <v>1</v>
@@ -15408,16 +15821,16 @@
         <v>1</v>
       </c>
       <c r="V51" s="29" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="W51" s="33" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="X51" s="29" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="Y51" s="33" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="Z51" s="28" t="s">
         <v>1</v>
@@ -15455,22 +15868,22 @@
         <v>52</v>
       </c>
       <c r="B52" s="47" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="C52" s="20" t="s">
         <v>52</v>
       </c>
       <c r="D52" s="28" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="E52" s="32" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="F52" s="28" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="G52" s="49" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="H52" s="28" t="s">
         <v>1</v>
@@ -15494,7 +15907,7 @@
         <v>72</v>
       </c>
       <c r="O52" s="33" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="P52" s="29" t="s">
         <v>1</v>
@@ -15515,16 +15928,16 @@
         <v>1</v>
       </c>
       <c r="V52" s="29" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="W52" s="33" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="X52" s="29" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="Y52" s="33" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="Z52" s="28" t="s">
         <v>1</v>
@@ -15562,22 +15975,22 @@
         <v>53</v>
       </c>
       <c r="B53" s="47" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="C53" s="20" t="s">
         <v>52</v>
       </c>
       <c r="D53" s="28" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="E53" s="32" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="F53" s="28" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="G53" s="49" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="H53" s="28" t="s">
         <v>1</v>
@@ -15601,7 +16014,7 @@
         <v>72</v>
       </c>
       <c r="O53" s="33" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="P53" s="29" t="s">
         <v>1</v>
@@ -15622,16 +16035,16 @@
         <v>1</v>
       </c>
       <c r="V53" s="29" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="W53" s="33" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="X53" s="29" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="Y53" s="33" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="Z53" s="28" t="s">
         <v>1</v>
@@ -15669,22 +16082,22 @@
         <v>54</v>
       </c>
       <c r="B54" s="47" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="C54" s="20" t="s">
         <v>52</v>
       </c>
       <c r="D54" s="28" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="E54" s="32" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="F54" s="28" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="G54" s="49" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="H54" s="28" t="s">
         <v>1</v>
@@ -15708,7 +16121,7 @@
         <v>72</v>
       </c>
       <c r="O54" s="33" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="P54" s="29" t="s">
         <v>1</v>
@@ -15729,16 +16142,16 @@
         <v>1</v>
       </c>
       <c r="V54" s="29" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="W54" s="33" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="X54" s="29" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="Y54" s="33" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="Z54" s="28" t="s">
         <v>1</v>
@@ -15776,22 +16189,22 @@
         <v>55</v>
       </c>
       <c r="B55" s="47" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="C55" s="20" t="s">
         <v>52</v>
       </c>
       <c r="D55" s="28" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="E55" s="32" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="F55" s="28" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="G55" s="49" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="H55" s="28" t="s">
         <v>1</v>
@@ -15815,7 +16228,7 @@
         <v>72</v>
       </c>
       <c r="O55" s="33" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="P55" s="29" t="s">
         <v>1</v>
@@ -15836,16 +16249,16 @@
         <v>1</v>
       </c>
       <c r="V55" s="29" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="W55" s="33" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="X55" s="29" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="Y55" s="33" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="Z55" s="28" t="s">
         <v>1</v>
@@ -15883,22 +16296,22 @@
         <v>56</v>
       </c>
       <c r="B56" s="47" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="C56" s="20" t="s">
         <v>52</v>
       </c>
       <c r="D56" s="28" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="E56" s="32" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="F56" s="28" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="G56" s="49" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="H56" s="28" t="s">
         <v>1</v>
@@ -15922,7 +16335,7 @@
         <v>72</v>
       </c>
       <c r="O56" s="33" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="P56" s="29" t="s">
         <v>1</v>
@@ -15943,16 +16356,16 @@
         <v>1</v>
       </c>
       <c r="V56" s="29" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="W56" s="33" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="X56" s="29" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="Y56" s="33" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="Z56" s="28" t="s">
         <v>1</v>
@@ -15990,22 +16403,22 @@
         <v>57</v>
       </c>
       <c r="B57" s="47" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="C57" s="20" t="s">
         <v>52</v>
       </c>
       <c r="D57" s="28" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="E57" s="32" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="F57" s="28" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="G57" s="49" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="H57" s="28" t="s">
         <v>1</v>
@@ -16029,7 +16442,7 @@
         <v>72</v>
       </c>
       <c r="O57" s="33" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="P57" s="29" t="s">
         <v>1</v>
@@ -16050,16 +16463,16 @@
         <v>1</v>
       </c>
       <c r="V57" s="29" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="W57" s="33" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="X57" s="29" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="Y57" s="33" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="Z57" s="28" t="s">
         <v>1</v>
@@ -16097,22 +16510,22 @@
         <v>58</v>
       </c>
       <c r="B58" s="47" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="C58" s="20" t="s">
         <v>52</v>
       </c>
       <c r="D58" s="28" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="E58" s="32" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="F58" s="28" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="G58" s="49" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="H58" s="28" t="s">
         <v>1</v>
@@ -16136,7 +16549,7 @@
         <v>72</v>
       </c>
       <c r="O58" s="33" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="P58" s="29" t="s">
         <v>1</v>
@@ -16157,16 +16570,16 @@
         <v>1</v>
       </c>
       <c r="V58" s="29" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="W58" s="33" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="X58" s="29" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="Y58" s="33" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="Z58" s="28" t="s">
         <v>1</v>
@@ -16204,22 +16617,22 @@
         <v>59</v>
       </c>
       <c r="B59" s="47" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="C59" s="20" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="28" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="E59" s="32" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="F59" s="28" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="G59" s="49" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="H59" s="28" t="s">
         <v>1</v>
@@ -16243,7 +16656,7 @@
         <v>72</v>
       </c>
       <c r="O59" s="33" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="P59" s="29" t="s">
         <v>1</v>
@@ -16264,16 +16677,16 @@
         <v>1</v>
       </c>
       <c r="V59" s="29" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="W59" s="33" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="X59" s="29" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="Y59" s="33" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="Z59" s="28" t="s">
         <v>1</v>
@@ -16311,22 +16724,22 @@
         <v>60</v>
       </c>
       <c r="B60" s="47" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="C60" s="20" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="28" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="E60" s="32" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="F60" s="28" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="G60" s="49" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="H60" s="28" t="s">
         <v>1</v>
@@ -16350,7 +16763,7 @@
         <v>72</v>
       </c>
       <c r="O60" s="33" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="P60" s="29" t="s">
         <v>1</v>
@@ -16371,16 +16784,16 @@
         <v>1</v>
       </c>
       <c r="V60" s="29" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="W60" s="33" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="X60" s="29" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="Y60" s="33" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="Z60" s="28" t="s">
         <v>1</v>
@@ -16418,16 +16831,16 @@
         <v>61</v>
       </c>
       <c r="B61" s="47" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="C61" s="20" t="s">
         <v>52</v>
       </c>
       <c r="D61" s="28" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="E61" s="32" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="F61" s="28" t="s">
         <v>1</v>
@@ -16457,7 +16870,7 @@
         <v>72</v>
       </c>
       <c r="O61" s="33" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="P61" s="29" t="s">
         <v>1</v>
@@ -16478,16 +16891,16 @@
         <v>1</v>
       </c>
       <c r="V61" s="29" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="W61" s="33" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="X61" s="29" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="Y61" s="33" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="Z61" s="28" t="s">
         <v>1</v>
@@ -16567,10 +16980,10 @@
         <v>116</v>
       </c>
       <c r="P62" s="29" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="Q62" s="33" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="R62" s="29" t="s">
         <v>1</v>
@@ -16585,16 +16998,16 @@
         <v>1</v>
       </c>
       <c r="V62" s="29" t="s">
+        <v>364</v>
+      </c>
+      <c r="W62" s="33" t="s">
+        <v>365</v>
+      </c>
+      <c r="X62" s="29" t="s">
+        <v>366</v>
+      </c>
+      <c r="Y62" s="33" t="s">
         <v>371</v>
-      </c>
-      <c r="W62" s="33" t="s">
-        <v>372</v>
-      </c>
-      <c r="X62" s="29" t="s">
-        <v>373</v>
-      </c>
-      <c r="Y62" s="33" t="s">
-        <v>378</v>
       </c>
       <c r="Z62" s="28" t="s">
         <v>1</v>
@@ -16674,10 +17087,10 @@
         <v>116</v>
       </c>
       <c r="P63" s="29" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="Q63" s="33" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="R63" s="29" t="s">
         <v>1</v>
@@ -16692,16 +17105,16 @@
         <v>1</v>
       </c>
       <c r="V63" s="29" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="W63" s="33" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="X63" s="29" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="Y63" s="33" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="Z63" s="28" t="s">
         <v>1</v>
@@ -16781,10 +17194,10 @@
         <v>108</v>
       </c>
       <c r="P64" s="29" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="Q64" s="33" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="R64" s="29" t="s">
         <v>1</v>
@@ -16799,16 +17212,16 @@
         <v>1</v>
       </c>
       <c r="V64" s="29" t="s">
+        <v>364</v>
+      </c>
+      <c r="W64" s="33" t="s">
+        <v>365</v>
+      </c>
+      <c r="X64" s="29" t="s">
+        <v>366</v>
+      </c>
+      <c r="Y64" s="33" t="s">
         <v>371</v>
-      </c>
-      <c r="W64" s="33" t="s">
-        <v>372</v>
-      </c>
-      <c r="X64" s="29" t="s">
-        <v>373</v>
-      </c>
-      <c r="Y64" s="33" t="s">
-        <v>378</v>
       </c>
       <c r="Z64" s="28" t="s">
         <v>1</v>
@@ -16852,7 +17265,7 @@
         <v>67</v>
       </c>
       <c r="D65" s="28" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="E65" s="32" t="s">
         <v>111</v>
@@ -16888,10 +17301,10 @@
         <v>108</v>
       </c>
       <c r="P65" s="29" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="Q65" s="33" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="R65" s="29" t="s">
         <v>1</v>
@@ -16906,16 +17319,16 @@
         <v>1</v>
       </c>
       <c r="V65" s="29" t="s">
+        <v>364</v>
+      </c>
+      <c r="W65" s="33" t="s">
+        <v>365</v>
+      </c>
+      <c r="X65" s="29" t="s">
+        <v>366</v>
+      </c>
+      <c r="Y65" s="33" t="s">
         <v>371</v>
-      </c>
-      <c r="W65" s="33" t="s">
-        <v>372</v>
-      </c>
-      <c r="X65" s="29" t="s">
-        <v>373</v>
-      </c>
-      <c r="Y65" s="33" t="s">
-        <v>378</v>
       </c>
       <c r="Z65" s="28" t="s">
         <v>1</v>
@@ -16953,13 +17366,13 @@
         <v>66</v>
       </c>
       <c r="B66" s="37" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="C66" s="21" t="s">
         <v>67</v>
       </c>
       <c r="D66" s="28" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="E66" s="32" t="s">
         <v>111</v>
@@ -16995,10 +17408,10 @@
         <v>108</v>
       </c>
       <c r="P66" s="29" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="Q66" s="33" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="R66" s="29" t="s">
         <v>1</v>
@@ -17013,16 +17426,16 @@
         <v>1</v>
       </c>
       <c r="V66" s="29" t="s">
+        <v>364</v>
+      </c>
+      <c r="W66" s="33" t="s">
+        <v>365</v>
+      </c>
+      <c r="X66" s="29" t="s">
+        <v>366</v>
+      </c>
+      <c r="Y66" s="33" t="s">
         <v>371</v>
-      </c>
-      <c r="W66" s="33" t="s">
-        <v>372</v>
-      </c>
-      <c r="X66" s="29" t="s">
-        <v>373</v>
-      </c>
-      <c r="Y66" s="33" t="s">
-        <v>378</v>
       </c>
       <c r="Z66" s="28" t="s">
         <v>1</v>
@@ -17066,7 +17479,7 @@
         <v>67</v>
       </c>
       <c r="D67" s="28" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="E67" s="32" t="s">
         <v>111</v>
@@ -17102,10 +17515,10 @@
         <v>108</v>
       </c>
       <c r="P67" s="29" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="Q67" s="33" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="R67" s="29" t="s">
         <v>1</v>
@@ -17120,16 +17533,16 @@
         <v>1</v>
       </c>
       <c r="V67" s="29" t="s">
+        <v>364</v>
+      </c>
+      <c r="W67" s="33" t="s">
+        <v>365</v>
+      </c>
+      <c r="X67" s="29" t="s">
+        <v>366</v>
+      </c>
+      <c r="Y67" s="33" t="s">
         <v>371</v>
-      </c>
-      <c r="W67" s="33" t="s">
-        <v>372</v>
-      </c>
-      <c r="X67" s="29" t="s">
-        <v>373</v>
-      </c>
-      <c r="Y67" s="33" t="s">
-        <v>378</v>
       </c>
       <c r="Z67" s="28" t="s">
         <v>1</v>
@@ -17167,16 +17580,16 @@
         <v>68</v>
       </c>
       <c r="B68" s="36" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="C68" s="21" t="s">
         <v>67</v>
       </c>
       <c r="D68" s="28" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="E68" s="32" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="F68" s="28" t="s">
         <v>1</v>
@@ -17209,10 +17622,10 @@
         <v>108</v>
       </c>
       <c r="P68" s="29" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="Q68" s="33" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="R68" s="29" t="s">
         <v>1</v>
@@ -17227,16 +17640,16 @@
         <v>1</v>
       </c>
       <c r="V68" s="29" t="s">
+        <v>364</v>
+      </c>
+      <c r="W68" s="33" t="s">
+        <v>365</v>
+      </c>
+      <c r="X68" s="29" t="s">
+        <v>366</v>
+      </c>
+      <c r="Y68" s="33" t="s">
         <v>371</v>
-      </c>
-      <c r="W68" s="33" t="s">
-        <v>372</v>
-      </c>
-      <c r="X68" s="29" t="s">
-        <v>373</v>
-      </c>
-      <c r="Y68" s="33" t="s">
-        <v>378</v>
       </c>
       <c r="Z68" s="28" t="s">
         <v>1</v>
@@ -17274,16 +17687,16 @@
         <v>69</v>
       </c>
       <c r="B69" s="36" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="C69" s="21" t="s">
         <v>67</v>
       </c>
       <c r="D69" s="28" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="E69" s="32" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="F69" s="28" t="s">
         <v>1</v>
@@ -17316,10 +17729,10 @@
         <v>108</v>
       </c>
       <c r="P69" s="29" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="Q69" s="33" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="R69" s="29" t="s">
         <v>1</v>
@@ -17334,16 +17747,16 @@
         <v>1</v>
       </c>
       <c r="V69" s="29" t="s">
+        <v>364</v>
+      </c>
+      <c r="W69" s="33" t="s">
+        <v>365</v>
+      </c>
+      <c r="X69" s="29" t="s">
+        <v>366</v>
+      </c>
+      <c r="Y69" s="33" t="s">
         <v>371</v>
-      </c>
-      <c r="W69" s="33" t="s">
-        <v>372</v>
-      </c>
-      <c r="X69" s="29" t="s">
-        <v>373</v>
-      </c>
-      <c r="Y69" s="33" t="s">
-        <v>378</v>
       </c>
       <c r="Z69" s="28" t="s">
         <v>1</v>
@@ -17381,34 +17794,34 @@
         <v>70</v>
       </c>
       <c r="B70" s="47" t="s">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="C70" s="20" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="D70" s="28" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="E70" s="32" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="F70" s="28" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="G70" s="32" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="H70" s="28" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="I70" s="32" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="J70" s="28" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="K70" s="32" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="L70" s="28" t="s">
         <v>1</v>
@@ -17420,7 +17833,7 @@
         <v>72</v>
       </c>
       <c r="O70" s="33" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="P70" s="29" t="s">
         <v>1</v>
@@ -17441,16 +17854,16 @@
         <v>1</v>
       </c>
       <c r="V70" s="29" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="W70" s="33" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="X70" s="29" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="Y70" s="33" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="Z70" s="28" t="s">
         <v>1</v>
@@ -17488,34 +17901,34 @@
         <v>71</v>
       </c>
       <c r="B71" s="47" t="s">
-        <v>486</v>
+        <v>479</v>
       </c>
       <c r="C71" s="20" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="D71" s="28" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="E71" s="32" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="F71" s="28" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="G71" s="32" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="H71" s="28" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="I71" s="32" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="J71" s="28" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="K71" s="32" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="L71" s="28" t="s">
         <v>1</v>
@@ -17527,7 +17940,7 @@
         <v>72</v>
       </c>
       <c r="O71" s="33" t="s">
-        <v>483</v>
+        <v>476</v>
       </c>
       <c r="P71" s="29" t="s">
         <v>1</v>
@@ -17548,16 +17961,16 @@
         <v>1</v>
       </c>
       <c r="V71" s="29" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="W71" s="33" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="X71" s="29" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="Y71" s="33" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="Z71" s="28" t="s">
         <v>1</v>
@@ -17595,34 +18008,34 @@
         <v>72</v>
       </c>
       <c r="B72" s="47" t="s">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="C72" s="20" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="D72" s="28" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="E72" s="32" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="F72" s="28" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="G72" s="32" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="H72" s="28" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="I72" s="32" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="J72" s="28" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="K72" s="32" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="L72" s="28" t="s">
         <v>1</v>
@@ -17634,7 +18047,7 @@
         <v>72</v>
       </c>
       <c r="O72" s="33" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="P72" s="29" t="s">
         <v>1</v>
@@ -17655,16 +18068,16 @@
         <v>1</v>
       </c>
       <c r="V72" s="29" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="W72" s="33" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="X72" s="29" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="Y72" s="33" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="Z72" s="28" t="s">
         <v>1</v>
@@ -17702,22 +18115,22 @@
         <v>73</v>
       </c>
       <c r="B73" s="47" t="s">
-        <v>492</v>
+        <v>485</v>
       </c>
       <c r="C73" s="20" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="D73" s="28" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="E73" s="32" t="s">
-        <v>488</v>
+        <v>481</v>
       </c>
       <c r="F73" s="28" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="G73" s="32" t="s">
-        <v>489</v>
+        <v>482</v>
       </c>
       <c r="H73" s="28" t="s">
         <v>1</v>
@@ -17741,7 +18154,7 @@
         <v>72</v>
       </c>
       <c r="O73" s="33" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="P73" s="29" t="s">
         <v>1</v>
@@ -17762,16 +18175,16 @@
         <v>1</v>
       </c>
       <c r="V73" s="29" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="W73" s="33" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="X73" s="29" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="Y73" s="33" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="Z73" s="28" t="s">
         <v>1</v>
@@ -17809,22 +18222,22 @@
         <v>74</v>
       </c>
       <c r="B74" s="47" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="C74" s="20" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="D74" s="28" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="E74" s="32" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="F74" s="28" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="G74" s="32" t="s">
-        <v>491</v>
+        <v>484</v>
       </c>
       <c r="H74" s="28" t="s">
         <v>1</v>
@@ -17848,7 +18261,7 @@
         <v>72</v>
       </c>
       <c r="O74" s="33" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="P74" s="29" t="s">
         <v>1</v>
@@ -17869,16 +18282,16 @@
         <v>1</v>
       </c>
       <c r="V74" s="29" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="W74" s="33" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="X74" s="29" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="Y74" s="33" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="Z74" s="28" t="s">
         <v>1</v>
@@ -17916,28 +18329,28 @@
         <v>75</v>
       </c>
       <c r="B75" s="47" t="s">
-        <v>488</v>
+        <v>481</v>
       </c>
       <c r="C75" s="20" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="D75" s="28" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="E75" s="32" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="F75" s="28" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="G75" s="32" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="H75" s="28" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="I75" s="32" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="J75" s="28" t="s">
         <v>1</v>
@@ -17955,7 +18368,7 @@
         <v>72</v>
       </c>
       <c r="O75" s="33" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="P75" s="29" t="s">
         <v>1</v>
@@ -17976,16 +18389,16 @@
         <v>1</v>
       </c>
       <c r="V75" s="29" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="W75" s="33" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="X75" s="29" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="Y75" s="33" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="Z75" s="28" t="s">
         <v>1</v>
@@ -18023,28 +18436,28 @@
         <v>76</v>
       </c>
       <c r="B76" s="47" t="s">
-        <v>489</v>
+        <v>482</v>
       </c>
       <c r="C76" s="20" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="D76" s="28" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="E76" s="32" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="F76" s="28" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="G76" s="32" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="H76" s="28" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="I76" s="32" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="J76" s="28" t="s">
         <v>1</v>
@@ -18062,7 +18475,7 @@
         <v>72</v>
       </c>
       <c r="O76" s="33" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="P76" s="29" t="s">
         <v>1</v>
@@ -18083,16 +18496,16 @@
         <v>1</v>
       </c>
       <c r="V76" s="29" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="W76" s="33" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="X76" s="29" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="Y76" s="33" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="Z76" s="28" t="s">
         <v>1</v>
@@ -18130,28 +18543,28 @@
         <v>77</v>
       </c>
       <c r="B77" s="47" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C77" s="20" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="D77" s="28" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="E77" s="32" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="F77" s="28" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="G77" s="32" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="H77" s="28" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="I77" s="32" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="J77" s="28" t="s">
         <v>1</v>
@@ -18169,7 +18582,7 @@
         <v>72</v>
       </c>
       <c r="O77" s="33" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="P77" s="29" t="s">
         <v>1</v>
@@ -18190,16 +18603,16 @@
         <v>1</v>
       </c>
       <c r="V77" s="29" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="W77" s="33" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="X77" s="29" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="Y77" s="33" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="Z77" s="28" t="s">
         <v>1</v>
@@ -18237,28 +18650,28 @@
         <v>78</v>
       </c>
       <c r="B78" s="47" t="s">
-        <v>491</v>
+        <v>484</v>
       </c>
       <c r="C78" s="20" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="D78" s="28" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="E78" s="32" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="F78" s="28" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="G78" s="32" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="H78" s="28" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="I78" s="32" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="J78" s="28" t="s">
         <v>1</v>
@@ -18276,7 +18689,7 @@
         <v>72</v>
       </c>
       <c r="O78" s="33" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="P78" s="29" t="s">
         <v>1</v>
@@ -18297,16 +18710,16 @@
         <v>1</v>
       </c>
       <c r="V78" s="29" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="W78" s="33" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="X78" s="29" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="Y78" s="33" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="Z78" s="28" t="s">
         <v>1</v>
@@ -18344,16 +18757,16 @@
         <v>79</v>
       </c>
       <c r="B79" s="47" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="C79" s="48" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="D79" s="28" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="E79" s="32" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="F79" s="28" t="s">
         <v>1</v>
@@ -18383,7 +18796,7 @@
         <v>72</v>
       </c>
       <c r="O79" s="33" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="P79" s="29" t="s">
         <v>1</v>
@@ -18404,16 +18817,16 @@
         <v>1</v>
       </c>
       <c r="V79" s="29" t="s">
+        <v>364</v>
+      </c>
+      <c r="W79" s="33" t="s">
+        <v>365</v>
+      </c>
+      <c r="X79" s="29" t="s">
+        <v>366</v>
+      </c>
+      <c r="Y79" s="33" t="s">
         <v>371</v>
-      </c>
-      <c r="W79" s="33" t="s">
-        <v>372</v>
-      </c>
-      <c r="X79" s="29" t="s">
-        <v>373</v>
-      </c>
-      <c r="Y79" s="33" t="s">
-        <v>378</v>
       </c>
       <c r="Z79" s="28" t="s">
         <v>1</v>
@@ -18457,10 +18870,10 @@
         <v>63</v>
       </c>
       <c r="D80" s="28" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="E80" s="32" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="F80" s="28" t="s">
         <v>1</v>
@@ -18490,13 +18903,13 @@
         <v>72</v>
       </c>
       <c r="O80" s="33" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="P80" s="29" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="Q80" s="33" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="R80" s="29" t="s">
         <v>1</v>
@@ -18511,16 +18924,16 @@
         <v>1</v>
       </c>
       <c r="V80" s="29" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="W80" s="33" t="s">
+        <v>365</v>
+      </c>
+      <c r="X80" s="29" t="s">
+        <v>366</v>
+      </c>
+      <c r="Y80" s="33" t="s">
         <v>372</v>
-      </c>
-      <c r="X80" s="29" t="s">
-        <v>373</v>
-      </c>
-      <c r="Y80" s="33" t="s">
-        <v>379</v>
       </c>
       <c r="Z80" s="28" t="s">
         <v>1</v>
@@ -18558,16 +18971,16 @@
         <v>81</v>
       </c>
       <c r="B81" s="36" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="C81" s="21" t="s">
         <v>63</v>
       </c>
       <c r="D81" s="28" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="E81" s="32" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="F81" s="28" t="s">
         <v>1</v>
@@ -18597,13 +19010,13 @@
         <v>72</v>
       </c>
       <c r="O81" s="33" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="P81" s="29" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="Q81" s="33" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="R81" s="29" t="s">
         <v>1</v>
@@ -18618,16 +19031,16 @@
         <v>1</v>
       </c>
       <c r="V81" s="29" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="W81" s="33" t="s">
+        <v>365</v>
+      </c>
+      <c r="X81" s="29" t="s">
+        <v>366</v>
+      </c>
+      <c r="Y81" s="33" t="s">
         <v>372</v>
-      </c>
-      <c r="X81" s="29" t="s">
-        <v>373</v>
-      </c>
-      <c r="Y81" s="33" t="s">
-        <v>379</v>
       </c>
       <c r="Z81" s="28" t="s">
         <v>1</v>
@@ -18665,16 +19078,16 @@
         <v>82</v>
       </c>
       <c r="B82" s="47" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="C82" s="48" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="D82" s="28" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="E82" s="32" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="F82" s="28" t="s">
         <v>1</v>
@@ -18704,7 +19117,7 @@
         <v>72</v>
       </c>
       <c r="O82" s="33" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="P82" s="29" t="s">
         <v>1</v>
@@ -18725,16 +19138,16 @@
         <v>1</v>
       </c>
       <c r="V82" s="29" t="s">
+        <v>364</v>
+      </c>
+      <c r="W82" s="33" t="s">
+        <v>365</v>
+      </c>
+      <c r="X82" s="29" t="s">
+        <v>366</v>
+      </c>
+      <c r="Y82" s="33" t="s">
         <v>371</v>
-      </c>
-      <c r="W82" s="33" t="s">
-        <v>372</v>
-      </c>
-      <c r="X82" s="29" t="s">
-        <v>373</v>
-      </c>
-      <c r="Y82" s="33" t="s">
-        <v>378</v>
       </c>
       <c r="Z82" s="28" t="s">
         <v>1</v>
@@ -18814,10 +19227,10 @@
         <v>119</v>
       </c>
       <c r="P83" s="29" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="Q83" s="33" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="R83" s="29" t="s">
         <v>1</v>
@@ -18832,16 +19245,16 @@
         <v>1</v>
       </c>
       <c r="V83" s="29" t="s">
+        <v>364</v>
+      </c>
+      <c r="W83" s="33" t="s">
+        <v>365</v>
+      </c>
+      <c r="X83" s="29" t="s">
+        <v>366</v>
+      </c>
+      <c r="Y83" s="33" t="s">
         <v>371</v>
-      </c>
-      <c r="W83" s="33" t="s">
-        <v>372</v>
-      </c>
-      <c r="X83" s="29" t="s">
-        <v>373</v>
-      </c>
-      <c r="Y83" s="33" t="s">
-        <v>378</v>
       </c>
       <c r="Z83" s="28" t="s">
         <v>1</v>
@@ -18921,10 +19334,10 @@
         <v>119</v>
       </c>
       <c r="P84" s="29" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="Q84" s="33" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="R84" s="29" t="s">
         <v>1</v>
@@ -18939,16 +19352,16 @@
         <v>1</v>
       </c>
       <c r="V84" s="29" t="s">
+        <v>364</v>
+      </c>
+      <c r="W84" s="33" t="s">
+        <v>365</v>
+      </c>
+      <c r="X84" s="29" t="s">
+        <v>366</v>
+      </c>
+      <c r="Y84" s="33" t="s">
         <v>371</v>
-      </c>
-      <c r="W84" s="33" t="s">
-        <v>372</v>
-      </c>
-      <c r="X84" s="29" t="s">
-        <v>373</v>
-      </c>
-      <c r="Y84" s="33" t="s">
-        <v>378</v>
       </c>
       <c r="Z84" s="28" t="s">
         <v>1</v>
@@ -18986,10 +19399,10 @@
         <v>85</v>
       </c>
       <c r="B85" s="71" t="s">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="C85" s="79" t="s">
-        <v>553</v>
+        <v>546</v>
       </c>
       <c r="D85" s="28" t="s">
         <v>1</v>
@@ -19025,7 +19438,7 @@
         <v>72</v>
       </c>
       <c r="O85" s="73" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="P85" s="29" t="s">
         <v>1</v>
@@ -19038,7 +19451,7 @@
         <v>método.revit</v>
       </c>
       <c r="S85" s="76" t="s">
-        <v>524</v>
+        <v>517</v>
       </c>
       <c r="T85" s="29" t="s">
         <v>1</v>
@@ -19047,16 +19460,16 @@
         <v>1</v>
       </c>
       <c r="V85" s="72" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="W85" s="73" t="s">
-        <v>521</v>
+        <v>514</v>
       </c>
       <c r="X85" s="72" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="Y85" s="73" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
       <c r="Z85" s="28" t="s">
         <v>1</v>
@@ -19094,10 +19507,10 @@
         <v>86</v>
       </c>
       <c r="B86" s="71" t="s">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="C86" s="79" t="s">
-        <v>553</v>
+        <v>546</v>
       </c>
       <c r="D86" s="28" t="s">
         <v>1</v>
@@ -19133,7 +19546,7 @@
         <v>72</v>
       </c>
       <c r="O86" s="73" t="s">
-        <v>527</v>
+        <v>520</v>
       </c>
       <c r="P86" s="29" t="s">
         <v>1</v>
@@ -19146,7 +19559,7 @@
         <v>método.revit</v>
       </c>
       <c r="S86" s="76" t="s">
-        <v>528</v>
+        <v>521</v>
       </c>
       <c r="T86" s="29" t="s">
         <v>1</v>
@@ -19155,16 +19568,16 @@
         <v>1</v>
       </c>
       <c r="V86" s="72" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="W86" s="73" t="s">
-        <v>521</v>
+        <v>514</v>
       </c>
       <c r="X86" s="72" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="Y86" s="73" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="Z86" s="28" t="s">
         <v>1</v>
@@ -19202,10 +19615,10 @@
         <v>87</v>
       </c>
       <c r="B87" s="71" t="s">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="C87" s="79" t="s">
-        <v>553</v>
+        <v>546</v>
       </c>
       <c r="D87" s="28" t="s">
         <v>1</v>
@@ -19241,7 +19654,7 @@
         <v>72</v>
       </c>
       <c r="O87" s="73" t="s">
-        <v>531</v>
+        <v>524</v>
       </c>
       <c r="P87" s="29" t="s">
         <v>1</v>
@@ -19254,7 +19667,7 @@
         <v>método.revit</v>
       </c>
       <c r="S87" s="76" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
       <c r="T87" s="29" t="s">
         <v>1</v>
@@ -19263,16 +19676,16 @@
         <v>1</v>
       </c>
       <c r="V87" s="72" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="W87" s="73" t="s">
-        <v>521</v>
+        <v>514</v>
       </c>
       <c r="X87" s="72" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="Y87" s="73" t="s">
-        <v>530</v>
+        <v>523</v>
       </c>
       <c r="Z87" s="28" t="s">
         <v>1</v>
@@ -19310,10 +19723,10 @@
         <v>88</v>
       </c>
       <c r="B88" s="71" t="s">
-        <v>533</v>
+        <v>526</v>
       </c>
       <c r="C88" s="79" t="s">
-        <v>553</v>
+        <v>546</v>
       </c>
       <c r="D88" s="28" t="s">
         <v>1</v>
@@ -19349,7 +19762,7 @@
         <v>72</v>
       </c>
       <c r="O88" s="73" t="s">
-        <v>535</v>
+        <v>528</v>
       </c>
       <c r="P88" s="29" t="s">
         <v>1</v>
@@ -19362,7 +19775,7 @@
         <v>método.revit</v>
       </c>
       <c r="S88" s="76" t="s">
-        <v>536</v>
+        <v>529</v>
       </c>
       <c r="T88" s="29" t="s">
         <v>1</v>
@@ -19371,16 +19784,16 @@
         <v>1</v>
       </c>
       <c r="V88" s="72" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="W88" s="73" t="s">
-        <v>521</v>
+        <v>514</v>
       </c>
       <c r="X88" s="72" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="Y88" s="73" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="Z88" s="28" t="s">
         <v>1</v>
@@ -19418,10 +19831,10 @@
         <v>89</v>
       </c>
       <c r="B89" s="71" t="s">
-        <v>537</v>
+        <v>530</v>
       </c>
       <c r="C89" s="79" t="s">
-        <v>553</v>
+        <v>546</v>
       </c>
       <c r="D89" s="28" t="s">
         <v>1</v>
@@ -19457,7 +19870,7 @@
         <v>72</v>
       </c>
       <c r="O89" s="73" t="s">
-        <v>539</v>
+        <v>532</v>
       </c>
       <c r="P89" s="29" t="s">
         <v>1</v>
@@ -19470,7 +19883,7 @@
         <v>método.revit</v>
       </c>
       <c r="S89" s="76" t="s">
-        <v>540</v>
+        <v>533</v>
       </c>
       <c r="T89" s="29" t="s">
         <v>1</v>
@@ -19479,16 +19892,16 @@
         <v>1</v>
       </c>
       <c r="V89" s="72" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="W89" s="73" t="s">
-        <v>521</v>
+        <v>514</v>
       </c>
       <c r="X89" s="72" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="Y89" s="73" t="s">
-        <v>538</v>
+        <v>531</v>
       </c>
       <c r="Z89" s="28" t="s">
         <v>1</v>
@@ -19527,35 +19940,35 @@
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="B1 B34:B35 B38:B78">
-    <cfRule type="duplicateValues" dxfId="17" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B84 B90:B1048576">
-    <cfRule type="duplicateValues" dxfId="16" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B76">
-    <cfRule type="duplicateValues" dxfId="13" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B79">
-    <cfRule type="duplicateValues" dxfId="12" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B80:B81">
-    <cfRule type="duplicateValues" dxfId="11" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B82:B84">
-    <cfRule type="duplicateValues" dxfId="10" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B85:B89">
-    <cfRule type="duplicateValues" dxfId="9" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C43">
-    <cfRule type="duplicateValues" dxfId="7" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G6:G7">
-    <cfRule type="duplicateValues" dxfId="5" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
